--- a/cuadros/ABRIL/ABRIL_BOSQUE_NAGUANAGUA_TUCACAS.xlsx
+++ b/cuadros/ABRIL/ABRIL_BOSQUE_NAGUANAGUA_TUCACAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Equipo\Documents\REDOBLE\CUADRO DE INCIDENCIAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\FISCALIZACION\cuadros\ABRIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13299FCF-9723-44EF-ACED-0D8D4EB08682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAABD187-B258-4472-9F07-50D4C2A7A5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,23 @@
     <sheet name="REFERENCIA" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="110">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -112,9 +124,6 @@
   </si>
   <si>
     <t>TUCACAS</t>
-  </si>
-  <si>
-    <t>EL BOSQUE</t>
   </si>
   <si>
     <t>NAGUANAGUA</t>
@@ -13956,22 +13965,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K503"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="2" width="40.85546875" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.15234375" customWidth="1"/>
+    <col min="2" max="2" width="40.84375" customWidth="1"/>
+    <col min="3" max="3" width="16.3828125" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="37.85546875" customWidth="1"/>
+    <col min="6" max="6" width="37.84375" customWidth="1"/>
     <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" customWidth="1"/>
-    <col min="9" max="9" width="69.5703125" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" customWidth="1"/>
-    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="21.3828125" customWidth="1"/>
+    <col min="9" max="9" width="69.53515625" customWidth="1"/>
+    <col min="10" max="10" width="14.15234375" customWidth="1"/>
+    <col min="11" max="11" width="16.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14003,15 +14012,15 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3">
         <v>13335</v>
@@ -14020,10 +14029,10 @@
         <v>46113</v>
       </c>
       <c r="E2" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>60</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>61</v>
       </c>
       <c r="G2" s="29" t="s">
         <v>27</v>
@@ -14033,17 +14042,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J2" s="15"/>
       <c r="K2" s="29"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3">
         <v>9271</v>
@@ -14052,10 +14061,10 @@
         <v>46113</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3" s="29" t="s">
         <v>10</v>
@@ -14065,17 +14074,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J3" s="15"/>
       <c r="K3" s="29"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3">
         <v>13327</v>
@@ -14084,10 +14093,10 @@
         <v>46113</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>21</v>
@@ -14097,19 +14106,19 @@
         <v>TIPO C</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J4" s="28">
         <v>3.9</v>
       </c>
       <c r="K4" s="29"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3">
         <v>246</v>
@@ -14118,10 +14127,10 @@
         <v>46113</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5" s="29" t="s">
         <v>21</v>
@@ -14131,19 +14140,19 @@
         <v>TIPO C</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J5" s="28">
         <v>1.69</v>
       </c>
       <c r="K5" s="29"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3">
         <v>12706</v>
@@ -14152,10 +14161,10 @@
         <v>46113</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" s="29" t="s">
         <v>26</v>
@@ -14165,19 +14174,19 @@
         <v>TIPO D</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J6" s="28">
         <v>57.1</v>
       </c>
       <c r="K6" s="29"/>
     </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3">
         <v>13335</v>
@@ -14186,10 +14195,10 @@
         <v>46113</v>
       </c>
       <c r="E7" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>60</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>61</v>
       </c>
       <c r="G7" s="29" t="s">
         <v>23</v>
@@ -14199,19 +14208,19 @@
         <v>TIPO C</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J7" s="28">
         <v>86.86</v>
       </c>
       <c r="K7" s="29"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3">
         <v>2966</v>
@@ -14220,10 +14229,10 @@
         <v>46114</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8" s="29" t="s">
         <v>26</v>
@@ -14233,7 +14242,7 @@
         <v>TIPO D</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J8" s="21">
         <v>4.3499999999999996</v>
@@ -14242,12 +14251,12 @@
         <v>133503</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="3">
         <v>345</v>
@@ -14256,10 +14265,10 @@
         <v>46114</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9" s="29" t="s">
         <v>23</v>
@@ -14269,19 +14278,19 @@
         <v>TIPO C</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J9" s="28">
         <v>167.04</v>
       </c>
       <c r="K9" s="29"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3">
         <v>222162</v>
@@ -14290,10 +14299,10 @@
         <v>46115</v>
       </c>
       <c r="E10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="G10" s="29" t="s">
         <v>27</v>
@@ -14303,17 +14312,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="29"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="3">
         <v>871</v>
@@ -14322,10 +14331,10 @@
         <v>46115</v>
       </c>
       <c r="E11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="G11" s="29" t="s">
         <v>27</v>
@@ -14335,17 +14344,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="29"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="4">
         <v>30426</v>
@@ -14354,10 +14363,10 @@
         <v>46115</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" s="29" t="s">
         <v>27</v>
@@ -14367,17 +14376,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="29"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3">
         <v>6067</v>
@@ -14386,10 +14395,10 @@
         <v>46115</v>
       </c>
       <c r="E13" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>60</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>61</v>
       </c>
       <c r="G13" s="29" t="s">
         <v>27</v>
@@ -14399,17 +14408,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="29"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3">
         <v>6040</v>
@@ -14418,10 +14427,10 @@
         <v>46115</v>
       </c>
       <c r="E14" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>60</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>61</v>
       </c>
       <c r="G14" s="29" t="s">
         <v>27</v>
@@ -14431,17 +14440,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="29"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="3">
         <v>6040</v>
@@ -14450,27 +14459,27 @@
         <v>46115</v>
       </c>
       <c r="E15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>60</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>61</v>
       </c>
       <c r="G15" s="29" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="29"/>
       <c r="I15" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="29"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="4">
         <v>36561</v>
@@ -14479,10 +14488,10 @@
         <v>46120</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G16" s="29" t="s">
         <v>16</v>
@@ -14492,17 +14501,17 @@
         <v>TIPO B</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="29"/>
     </row>
-    <row r="17" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="4">
         <v>2646</v>
@@ -14511,10 +14520,10 @@
         <v>46120</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G17" s="29" t="s">
         <v>16</v>
@@ -14524,17 +14533,17 @@
         <v>TIPO B</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="29"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="3">
         <v>8031304345</v>
@@ -14543,10 +14552,10 @@
         <v>46120</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="29" t="s">
         <v>16</v>
@@ -14556,17 +14565,17 @@
         <v>TIPO B</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="29"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="3">
         <v>3000011999</v>
@@ -14575,10 +14584,10 @@
         <v>46120</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G19" s="29" t="s">
         <v>16</v>
@@ -14588,29 +14597,29 @@
         <v>TIPO B</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="29"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="17">
         <v>46120</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G20" s="29" t="s">
         <v>16</v>
@@ -14620,29 +14629,29 @@
         <v>TIPO B</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="29"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" s="17">
         <v>46120</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="29" t="s">
         <v>16</v>
@@ -14652,29 +14661,29 @@
         <v>TIPO B</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="29"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D22" s="17">
         <v>46120</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G22" s="29" t="s">
         <v>16</v>
@@ -14684,17 +14693,17 @@
         <v>TIPO B</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="29"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="4">
         <v>50985</v>
@@ -14703,10 +14712,10 @@
         <v>46120</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G23" s="29" t="s">
         <v>16</v>
@@ -14716,17 +14725,17 @@
         <v>TIPO B</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="29"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="3">
         <v>4747</v>
@@ -14735,10 +14744,10 @@
         <v>46120</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G24" s="29" t="s">
         <v>16</v>
@@ -14748,17 +14757,17 @@
         <v>TIPO B</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="29"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" s="3">
         <v>320</v>
@@ -14767,10 +14776,10 @@
         <v>46121</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G25" s="29" t="s">
         <v>27</v>
@@ -14780,19 +14789,19 @@
         <v>TIPO E</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J25" s="20">
         <v>1913.1</v>
       </c>
       <c r="K25" s="29"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="3">
         <v>2958</v>
@@ -14801,10 +14810,10 @@
         <v>46125</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G26" s="29" t="s">
         <v>17</v>
@@ -14814,17 +14823,17 @@
         <v>TIPO B</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J26" s="10"/>
       <c r="K26" s="29"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="3">
         <v>8031306009</v>
@@ -14833,10 +14842,10 @@
         <v>46127</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G27" s="29" t="s">
         <v>27</v>
@@ -14846,17 +14855,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="29"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3">
         <v>8031306005</v>
@@ -14865,10 +14874,10 @@
         <v>46127</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G28" s="29" t="s">
         <v>27</v>
@@ -14878,17 +14887,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="29"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C29" s="6">
         <v>8031306007</v>
@@ -14897,10 +14906,10 @@
         <v>46127</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G29" s="29" t="s">
         <v>27</v>
@@ -14910,17 +14919,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I29" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J29" s="10"/>
       <c r="K29" s="29"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" s="6">
         <v>8031306008</v>
@@ -14929,10 +14938,10 @@
         <v>46127</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G30" s="29" t="s">
         <v>27</v>
@@ -14942,17 +14951,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I30" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J30" s="10"/>
       <c r="K30" s="29"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="6">
         <v>8031306006</v>
@@ -14961,10 +14970,10 @@
         <v>46127</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G31" s="29" t="s">
         <v>27</v>
@@ -14974,29 +14983,29 @@
         <v>TIPO E</v>
       </c>
       <c r="I31" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J31" s="10"/>
       <c r="K31" s="29"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D32" s="7">
         <v>46127</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G32" s="29" t="s">
         <v>10</v>
@@ -15006,17 +15015,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J32" s="10"/>
       <c r="K32" s="29"/>
     </row>
-    <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" s="4">
         <v>18352</v>
@@ -15025,10 +15034,10 @@
         <v>46128</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G33" s="29" t="s">
         <v>10</v>
@@ -15038,17 +15047,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="29"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="4">
         <v>125346</v>
@@ -15057,10 +15066,10 @@
         <v>46132</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G34" s="29" t="s">
         <v>10</v>
@@ -15070,17 +15079,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I34" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J34" s="15"/>
       <c r="K34" s="29"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35" s="5">
         <v>6067</v>
@@ -15089,10 +15098,10 @@
         <v>46132</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G35" s="29" t="s">
         <v>10</v>
@@ -15102,17 +15111,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J35" s="15"/>
       <c r="K35" s="29"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36" s="5">
         <v>23975</v>
@@ -15121,10 +15130,10 @@
         <v>46133</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G36" s="29" t="s">
         <v>26</v>
@@ -15134,7 +15143,7 @@
         <v>TIPO D</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J36" s="21">
         <v>15.03</v>
@@ -15143,12 +15152,12 @@
         <v>91458</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="5">
         <v>529</v>
@@ -15157,10 +15166,10 @@
         <v>46134</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G37" s="29" t="s">
         <v>26</v>
@@ -15170,7 +15179,7 @@
         <v>TIPO D</v>
       </c>
       <c r="I37" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J37" s="21">
         <v>13</v>
@@ -15179,24 +15188,24 @@
         <v>199055</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" s="5">
         <v>804</v>
       </c>
       <c r="D38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="F38" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G38" s="29" t="s">
         <v>26</v>
@@ -15206,7 +15215,7 @@
         <v>TIPO D</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J38" s="21">
         <v>8.89</v>
@@ -15215,12 +15224,12 @@
         <v>199170</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C39" s="5">
         <v>773</v>
@@ -15229,10 +15238,10 @@
         <v>46135</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G39" s="29" t="s">
         <v>27</v>
@@ -15242,17 +15251,17 @@
         <v>TIPO E</v>
       </c>
       <c r="I39" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J39" s="15"/>
       <c r="K39" s="29"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C40" s="5">
         <v>773</v>
@@ -15261,10 +15270,10 @@
         <v>46135</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G40" s="29" t="s">
         <v>26</v>
@@ -15274,7 +15283,7 @@
         <v>TIPO D</v>
       </c>
       <c r="I40" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J40" s="21">
         <v>1.89</v>
@@ -15283,12 +15292,12 @@
         <v>138956</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C41" s="3">
         <v>339</v>
@@ -15297,10 +15306,10 @@
         <v>46135</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G41" s="29" t="s">
         <v>16</v>
@@ -15310,17 +15319,17 @@
         <v>TIPO B</v>
       </c>
       <c r="I41" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J41" s="15"/>
       <c r="K41" s="29"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C42" s="3">
         <v>339</v>
@@ -15329,10 +15338,10 @@
         <v>46135</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G42" s="29" t="s">
         <v>13</v>
@@ -15347,12 +15356,12 @@
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C43" s="29">
         <v>27822</v>
@@ -15361,10 +15370,10 @@
         <v>46136</v>
       </c>
       <c r="E43" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G43" s="29" t="s">
         <v>26</v>
@@ -15374,7 +15383,7 @@
         <v>TIPO D</v>
       </c>
       <c r="I43" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J43" s="32">
         <v>1.23</v>
@@ -15383,12 +15392,12 @@
         <v>252597</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" s="29">
         <v>2247070507</v>
@@ -15397,10 +15406,10 @@
         <v>46136</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G44" s="29" t="s">
         <v>26</v>
@@ -15409,7 +15418,7 @@
         <v>25</v>
       </c>
       <c r="I44" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J44" s="32">
         <v>57.52</v>
@@ -15418,12 +15427,12 @@
         <v>63805</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="29" t="s">
         <v>31</v>
-      </c>
-      <c r="B45" s="29" t="s">
-        <v>32</v>
       </c>
       <c r="C45" s="29">
         <v>13503</v>
@@ -15432,10 +15441,10 @@
         <v>46136</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G45" s="29" t="s">
         <v>22</v>
@@ -15445,17 +15454,17 @@
         <v>TIPO C</v>
       </c>
       <c r="I45" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A46" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" s="29">
         <v>125449</v>
@@ -15464,10 +15473,10 @@
         <v>46136</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G46" s="29" t="s">
         <v>26</v>
@@ -15476,31 +15485,31 @@
         <v>25</v>
       </c>
       <c r="I46" s="31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J46" s="33">
         <v>92</v>
       </c>
       <c r="K46" s="29"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" s="29" t="s">
         <v>29</v>
       </c>
       <c r="B47" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="29" t="s">
         <v>94</v>
-      </c>
-      <c r="C47" s="29" t="s">
-        <v>95</v>
       </c>
       <c r="D47" s="30">
         <v>46140</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G47" s="29" t="s">
         <v>10</v>
@@ -15510,17 +15519,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I47" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C48" s="29">
         <v>31173</v>
@@ -15529,10 +15538,10 @@
         <v>46140</v>
       </c>
       <c r="E48" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" s="29" t="s">
         <v>99</v>
-      </c>
-      <c r="F48" s="29" t="s">
-        <v>100</v>
       </c>
       <c r="G48" s="29" t="s">
         <v>22</v>
@@ -15541,29 +15550,29 @@
         <v>20</v>
       </c>
       <c r="I48" s="29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" s="29" t="s">
         <v>29</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D49" s="30">
         <v>46140</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G49" s="29" t="s">
         <v>10</v>
@@ -15573,17 +15582,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I49" s="29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A50" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" s="29" t="s">
         <v>31</v>
-      </c>
-      <c r="B50" s="29" t="s">
-        <v>32</v>
       </c>
       <c r="C50" s="29">
         <v>13540</v>
@@ -15592,10 +15601,10 @@
         <v>46141</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G50" s="29" t="s">
         <v>17</v>
@@ -15605,17 +15614,17 @@
         <v>TIPO B</v>
       </c>
       <c r="I50" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J50" s="29"/>
       <c r="K50" s="29"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A51" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C51" s="29">
         <v>860</v>
@@ -15624,10 +15633,10 @@
         <v>46142</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G51" s="29" t="s">
         <v>10</v>
@@ -15637,17 +15646,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I51" s="29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J51" s="29"/>
       <c r="K51" s="29"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C52" s="29">
         <v>2351</v>
@@ -15656,10 +15665,10 @@
         <v>46142</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G52" s="29" t="s">
         <v>12</v>
@@ -15669,17 +15678,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J52" s="29"/>
       <c r="K52" s="29"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A53" s="29" t="s">
         <v>29</v>
       </c>
       <c r="B53" s="29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C53" s="29">
         <v>2347</v>
@@ -15688,10 +15697,10 @@
         <v>46142</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F53" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G53" s="29" t="s">
         <v>12</v>
@@ -15701,17 +15710,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I53" s="29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J53" s="29"/>
       <c r="K53" s="29"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B54" s="29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C54" s="29">
         <v>57</v>
@@ -15720,10 +15729,10 @@
         <v>46142</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G54" s="29" t="s">
         <v>14</v>
@@ -15733,17 +15742,17 @@
         <v>TIPO B</v>
       </c>
       <c r="I54" s="29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J54" s="29"/>
       <c r="K54" s="29"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A55" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B55" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C55" s="29">
         <v>20110664</v>
@@ -15752,10 +15761,10 @@
         <v>46142</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G55" s="29" t="s">
         <v>12</v>
@@ -15765,17 +15774,17 @@
         <v>TIPO A</v>
       </c>
       <c r="I55" s="29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J55" s="29"/>
       <c r="K55" s="29"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A56" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C56" s="29"/>
       <c r="D56" s="29"/>
@@ -15790,7 +15799,7 @@
       <c r="J56" s="29"/>
       <c r="K56" s="29"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A57" s="29"/>
       <c r="B57" s="29"/>
       <c r="C57" s="29"/>
@@ -15806,7 +15815,7 @@
       <c r="J57" s="29"/>
       <c r="K57" s="29"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A58" s="29"/>
       <c r="B58" s="29"/>
       <c r="C58" s="29"/>
@@ -15822,7 +15831,7 @@
       <c r="J58" s="29"/>
       <c r="K58" s="29"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A59" s="29"/>
       <c r="B59" s="29"/>
       <c r="C59" s="29"/>
@@ -15838,7 +15847,7 @@
       <c r="J59" s="29"/>
       <c r="K59" s="29"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A60" s="29"/>
       <c r="B60" s="29"/>
       <c r="C60" s="29"/>
@@ -15854,2659 +15863,2659 @@
       <c r="J60" s="29"/>
       <c r="K60" s="29"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H61" t="str">
         <f>IF(G61="","",VLOOKUP(G61,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H62" t="str">
         <f>IF(G62="","",VLOOKUP(G62,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H63" t="str">
         <f>IF(G63="","",VLOOKUP(G63,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H64" t="str">
         <f>IF(G64="","",VLOOKUP(G64,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H65" t="str">
         <f>IF(G65="","",VLOOKUP(G65,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H66" t="str">
         <f>IF(G66="","",VLOOKUP(G66,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H67" t="str">
         <f>IF(G67="","",VLOOKUP(G67,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H68" t="str">
         <f>IF(G68="","",VLOOKUP(G68,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H69" t="str">
         <f>IF(G69="","",VLOOKUP(G69,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H70" t="str">
         <f>IF(G70="","",VLOOKUP(G70,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H71" t="str">
         <f>IF(G71="","",VLOOKUP(G71,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H72" t="str">
         <f>IF(G72="","",VLOOKUP(G72,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H73" t="str">
         <f>IF(G73="","",VLOOKUP(G73,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H74" t="str">
         <f>IF(G74="","",VLOOKUP(G74,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H75" t="str">
         <f>IF(G75="","",VLOOKUP(G75,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H76" t="str">
         <f>IF(G76="","",VLOOKUP(G76,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H77" t="str">
         <f>IF(G77="","",VLOOKUP(G77,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H78" t="str">
         <f>IF(G78="","",VLOOKUP(G78,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H79" t="str">
         <f>IF(G79="","",VLOOKUP(G79,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H80" t="str">
         <f>IF(G80="","",VLOOKUP(G80,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H81" t="str">
         <f>IF(G81="","",VLOOKUP(G81,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H82" t="str">
         <f>IF(G82="","",VLOOKUP(G82,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H83" t="str">
         <f>IF(G83="","",VLOOKUP(G83,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H84" t="str">
         <f>IF(G84="","",VLOOKUP(G84,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H85" t="str">
         <f>IF(G85="","",VLOOKUP(G85,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H86" t="str">
         <f>IF(G86="","",VLOOKUP(G86,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H87" t="str">
         <f>IF(G87="","",VLOOKUP(G87,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H88" t="str">
         <f>IF(G88="","",VLOOKUP(G88,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H89" t="str">
         <f>IF(G89="","",VLOOKUP(G89,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H90" t="str">
         <f>IF(G90="","",VLOOKUP(G90,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H91" t="str">
         <f>IF(G91="","",VLOOKUP(G91,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H92" t="str">
         <f>IF(G92="","",VLOOKUP(G92,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H93" t="str">
         <f>IF(G93="","",VLOOKUP(G93,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H94" t="str">
         <f>IF(G94="","",VLOOKUP(G94,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H95" t="str">
         <f>IF(G95="","",VLOOKUP(G95,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H96" t="str">
         <f>IF(G96="","",VLOOKUP(G96,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H97" t="str">
         <f>IF(G97="","",VLOOKUP(G97,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H98" t="str">
         <f>IF(G98="","",VLOOKUP(G98,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H99" t="str">
         <f>IF(G99="","",VLOOKUP(G99,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H100" t="str">
         <f>IF(G100="","",VLOOKUP(G100,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H101" t="str">
         <f>IF(G101="","",VLOOKUP(G101,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H102" t="str">
         <f>IF(G102="","",VLOOKUP(G102,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H103" t="str">
         <f>IF(G103="","",VLOOKUP(G103,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H104" t="str">
         <f>IF(G104="","",VLOOKUP(G104,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="105" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H105" t="str">
         <f>IF(G105="","",VLOOKUP(G105,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H106" t="str">
         <f>IF(G106="","",VLOOKUP(G106,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="107" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H107" t="str">
         <f>IF(G107="","",VLOOKUP(G107,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="108" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H108" t="str">
         <f>IF(G108="","",VLOOKUP(G108,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="109" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H109" t="str">
         <f>IF(G109="","",VLOOKUP(G109,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="110" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H110" t="str">
         <f>IF(G110="","",VLOOKUP(G110,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="111" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H111" t="str">
         <f>IF(G111="","",VLOOKUP(G111,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="112" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H112" t="str">
         <f>IF(G112="","",VLOOKUP(G112,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H113" t="str">
         <f>IF(G113="","",VLOOKUP(G113,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H114" t="str">
         <f>IF(G114="","",VLOOKUP(G114,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H115" t="str">
         <f>IF(G115="","",VLOOKUP(G115,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="116" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H116" t="str">
         <f>IF(G116="","",VLOOKUP(G116,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="117" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H117" t="str">
         <f>IF(G117="","",VLOOKUP(G117,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="118" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H118" t="str">
         <f>IF(G118="","",VLOOKUP(G118,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="119" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H119" t="str">
         <f>IF(G119="","",VLOOKUP(G119,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="120" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H120" t="str">
         <f>IF(G120="","",VLOOKUP(G120,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="121" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H121" t="str">
         <f>IF(G121="","",VLOOKUP(G121,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="122" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H122" t="str">
         <f>IF(G122="","",VLOOKUP(G122,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="123" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H123" t="str">
         <f>IF(G123="","",VLOOKUP(G123,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="124" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H124" t="str">
         <f>IF(G124="","",VLOOKUP(G124,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H125" t="str">
         <f>IF(G125="","",VLOOKUP(G125,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H126" t="str">
         <f>IF(G126="","",VLOOKUP(G126,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H127" t="str">
         <f>IF(G127="","",VLOOKUP(G127,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H128" t="str">
         <f>IF(G128="","",VLOOKUP(G128,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H129" t="str">
         <f>IF(G129="","",VLOOKUP(G129,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H130" t="str">
         <f>IF(G130="","",VLOOKUP(G130,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H131" t="str">
         <f>IF(G131="","",VLOOKUP(G131,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="132" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H132" t="str">
         <f>IF(G132="","",VLOOKUP(G132,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="133" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H133" t="str">
         <f>IF(G133="","",VLOOKUP(G133,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="134" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H134" t="str">
         <f>IF(G134="","",VLOOKUP(G134,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="135" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H135" t="str">
         <f>IF(G135="","",VLOOKUP(G135,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H136" t="str">
         <f>IF(G136="","",VLOOKUP(G136,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="137" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H137" t="str">
         <f>IF(G137="","",VLOOKUP(G137,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="138" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H138" t="str">
         <f>IF(G138="","",VLOOKUP(G138,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="139" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H139" t="str">
         <f>IF(G139="","",VLOOKUP(G139,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H140" t="str">
         <f>IF(G140="","",VLOOKUP(G140,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H141" t="str">
         <f>IF(G141="","",VLOOKUP(G141,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="142" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H142" t="str">
         <f>IF(G142="","",VLOOKUP(G142,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="143" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H143" t="str">
         <f>IF(G143="","",VLOOKUP(G143,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="144" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H144" t="str">
         <f>IF(G144="","",VLOOKUP(G144,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H145" t="str">
         <f>IF(G145="","",VLOOKUP(G145,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="146" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H146" t="str">
         <f>IF(G146="","",VLOOKUP(G146,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="147" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H147" t="str">
         <f>IF(G147="","",VLOOKUP(G147,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H148" t="str">
         <f>IF(G148="","",VLOOKUP(G148,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H149" t="str">
         <f>IF(G149="","",VLOOKUP(G149,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="150" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H150" t="str">
         <f>IF(G150="","",VLOOKUP(G150,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="151" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H151" t="str">
         <f>IF(G151="","",VLOOKUP(G151,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="152" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H152" t="str">
         <f>IF(G152="","",VLOOKUP(G152,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H153" t="str">
         <f>IF(G153="","",VLOOKUP(G153,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="154" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H154" t="str">
         <f>IF(G154="","",VLOOKUP(G154,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="155" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H155" t="str">
         <f>IF(G155="","",VLOOKUP(G155,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H156" t="str">
         <f>IF(G156="","",VLOOKUP(G156,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H157" t="str">
         <f>IF(G157="","",VLOOKUP(G157,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="158" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H158" t="str">
         <f>IF(G158="","",VLOOKUP(G158,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="159" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H159" t="str">
         <f>IF(G159="","",VLOOKUP(G159,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="160" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H160" t="str">
         <f>IF(G160="","",VLOOKUP(G160,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H161" t="str">
         <f>IF(G161="","",VLOOKUP(G161,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="162" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H162" t="str">
         <f>IF(G162="","",VLOOKUP(G162,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="163" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H163" t="str">
         <f>IF(G163="","",VLOOKUP(G163,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H164" t="str">
         <f>IF(G164="","",VLOOKUP(G164,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H165" t="str">
         <f>IF(G165="","",VLOOKUP(G165,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="166" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H166" t="str">
         <f>IF(G166="","",VLOOKUP(G166,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="167" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H167" t="str">
         <f>IF(G167="","",VLOOKUP(G167,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="168" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H168" t="str">
         <f>IF(G168="","",VLOOKUP(G168,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H169" t="str">
         <f>IF(G169="","",VLOOKUP(G169,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="170" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H170" t="str">
         <f>IF(G170="","",VLOOKUP(G170,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="171" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H171" t="str">
         <f>IF(G171="","",VLOOKUP(G171,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="172" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H172" t="str">
         <f>IF(G172="","",VLOOKUP(G172,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="173" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H173" t="str">
         <f>IF(G173="","",VLOOKUP(G173,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="174" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H174" t="str">
         <f>IF(G174="","",VLOOKUP(G174,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="175" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H175" t="str">
         <f>IF(G175="","",VLOOKUP(G175,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="176" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H176" t="str">
         <f>IF(G176="","",VLOOKUP(G176,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H177" t="str">
         <f>IF(G177="","",VLOOKUP(G177,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H178" t="str">
         <f>IF(G178="","",VLOOKUP(G178,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H179" t="str">
         <f>IF(G179="","",VLOOKUP(G179,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H180" t="str">
         <f>IF(G180="","",VLOOKUP(G180,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H181" t="str">
         <f>IF(G181="","",VLOOKUP(G181,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H182" t="str">
         <f>IF(G182="","",VLOOKUP(G182,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H183" t="str">
         <f>IF(G183="","",VLOOKUP(G183,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H184" t="str">
         <f>IF(G184="","",VLOOKUP(G184,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H185" t="str">
         <f>IF(G185="","",VLOOKUP(G185,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H186" t="str">
         <f>IF(G186="","",VLOOKUP(G186,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H187" t="str">
         <f>IF(G187="","",VLOOKUP(G187,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H188" t="str">
         <f>IF(G188="","",VLOOKUP(G188,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H189" t="str">
         <f>IF(G189="","",VLOOKUP(G189,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H190" t="str">
         <f>IF(G190="","",VLOOKUP(G190,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H191" t="str">
         <f>IF(G191="","",VLOOKUP(G191,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H192" t="str">
         <f>IF(G192="","",VLOOKUP(G192,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="193" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H193" t="str">
         <f>IF(G193="","",VLOOKUP(G193,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="194" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H194" t="str">
         <f>IF(G194="","",VLOOKUP(G194,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="195" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H195" t="str">
         <f>IF(G195="","",VLOOKUP(G195,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="196" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H196" t="str">
         <f>IF(G196="","",VLOOKUP(G196,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="197" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H197" t="str">
         <f>IF(G197="","",VLOOKUP(G197,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="198" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H198" t="str">
         <f>IF(G198="","",VLOOKUP(G198,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="199" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H199" t="str">
         <f>IF(G199="","",VLOOKUP(G199,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="200" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H200" t="str">
         <f>IF(G200="","",VLOOKUP(G200,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="201" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H201" t="str">
         <f>IF(G201="","",VLOOKUP(G201,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="202" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H202" t="str">
         <f>IF(G202="","",VLOOKUP(G202,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="203" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H203" t="str">
         <f>IF(G203="","",VLOOKUP(G203,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="204" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H204" t="str">
         <f>IF(G204="","",VLOOKUP(G204,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="205" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H205" t="str">
         <f>IF(G205="","",VLOOKUP(G205,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="206" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H206" t="str">
         <f>IF(G206="","",VLOOKUP(G206,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="207" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H207" t="str">
         <f>IF(G207="","",VLOOKUP(G207,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="208" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H208" t="str">
         <f>IF(G208="","",VLOOKUP(G208,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H209" t="str">
         <f>IF(G209="","",VLOOKUP(G209,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H210" t="str">
         <f>IF(G210="","",VLOOKUP(G210,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H211" t="str">
         <f>IF(G211="","",VLOOKUP(G211,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H212" t="str">
         <f>IF(G212="","",VLOOKUP(G212,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H213" t="str">
         <f>IF(G213="","",VLOOKUP(G213,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="214" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H214" t="str">
         <f>IF(G214="","",VLOOKUP(G214,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="215" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H215" t="str">
         <f>IF(G215="","",VLOOKUP(G215,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="216" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H216" t="str">
         <f>IF(G216="","",VLOOKUP(G216,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="217" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H217" t="str">
         <f>IF(G217="","",VLOOKUP(G217,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="218" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H218" t="str">
         <f>IF(G218="","",VLOOKUP(G218,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="219" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H219" t="str">
         <f>IF(G219="","",VLOOKUP(G219,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="220" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H220" t="str">
         <f>IF(G220="","",VLOOKUP(G220,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="221" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H221" t="str">
         <f>IF(G221="","",VLOOKUP(G221,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="222" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H222" t="str">
         <f>IF(G222="","",VLOOKUP(G222,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="223" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H223" t="str">
         <f>IF(G223="","",VLOOKUP(G223,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="224" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H224" t="str">
         <f>IF(G224="","",VLOOKUP(G224,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="225" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H225" t="str">
         <f>IF(G225="","",VLOOKUP(G225,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="226" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H226" t="str">
         <f>IF(G226="","",VLOOKUP(G226,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="227" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H227" t="str">
         <f>IF(G227="","",VLOOKUP(G227,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="228" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H228" t="str">
         <f>IF(G228="","",VLOOKUP(G228,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="229" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H229" t="str">
         <f>IF(G229="","",VLOOKUP(G229,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="230" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H230" t="str">
         <f>IF(G230="","",VLOOKUP(G230,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="231" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H231" t="str">
         <f>IF(G231="","",VLOOKUP(G231,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="232" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H232" t="str">
         <f>IF(G232="","",VLOOKUP(G232,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="233" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H233" t="str">
         <f>IF(G233="","",VLOOKUP(G233,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="234" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H234" t="str">
         <f>IF(G234="","",VLOOKUP(G234,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="235" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H235" t="str">
         <f>IF(G235="","",VLOOKUP(G235,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="236" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H236" t="str">
         <f>IF(G236="","",VLOOKUP(G236,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="237" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H237" t="str">
         <f>IF(G237="","",VLOOKUP(G237,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="238" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H238" t="str">
         <f>IF(G238="","",VLOOKUP(G238,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="239" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H239" t="str">
         <f>IF(G239="","",VLOOKUP(G239,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="240" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H240" t="str">
         <f>IF(G240="","",VLOOKUP(G240,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="241" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H241" t="str">
         <f>IF(G241="","",VLOOKUP(G241,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="242" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H242" t="str">
         <f>IF(G242="","",VLOOKUP(G242,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="243" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H243" t="str">
         <f>IF(G243="","",VLOOKUP(G243,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="244" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H244" t="str">
         <f>IF(G244="","",VLOOKUP(G244,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="245" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H245" t="str">
         <f>IF(G245="","",VLOOKUP(G245,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="246" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H246" t="str">
         <f>IF(G246="","",VLOOKUP(G246,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="247" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H247" t="str">
         <f>IF(G247="","",VLOOKUP(G247,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="248" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H248" t="str">
         <f>IF(G248="","",VLOOKUP(G248,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="249" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H249" t="str">
         <f>IF(G249="","",VLOOKUP(G249,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="250" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H250" t="str">
         <f>IF(G250="","",VLOOKUP(G250,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="251" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H251" t="str">
         <f>IF(G251="","",VLOOKUP(G251,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="252" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H252" t="str">
         <f>IF(G252="","",VLOOKUP(G252,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="253" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H253" t="str">
         <f>IF(G253="","",VLOOKUP(G253,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="254" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H254" t="str">
         <f>IF(G254="","",VLOOKUP(G254,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="255" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H255" t="str">
         <f>IF(G255="","",VLOOKUP(G255,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="256" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H256" t="str">
         <f>IF(G256="","",VLOOKUP(G256,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="257" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H257" t="str">
         <f>IF(G257="","",VLOOKUP(G257,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="258" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H258" t="str">
         <f>IF(G258="","",VLOOKUP(G258,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="259" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H259" t="str">
         <f>IF(G259="","",VLOOKUP(G259,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="260" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H260" t="str">
         <f>IF(G260="","",VLOOKUP(G260,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="261" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H261" t="str">
         <f>IF(G261="","",VLOOKUP(G261,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="262" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H262" t="str">
         <f>IF(G262="","",VLOOKUP(G262,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="263" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H263" t="str">
         <f>IF(G263="","",VLOOKUP(G263,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="264" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H264" t="str">
         <f>IF(G264="","",VLOOKUP(G264,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="265" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H265" t="str">
         <f>IF(G265="","",VLOOKUP(G265,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="266" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H266" t="str">
         <f>IF(G266="","",VLOOKUP(G266,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="267" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H267" t="str">
         <f>IF(G267="","",VLOOKUP(G267,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="268" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H268" t="str">
         <f>IF(G268="","",VLOOKUP(G268,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="269" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H269" t="str">
         <f>IF(G269="","",VLOOKUP(G269,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="270" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H270" t="str">
         <f>IF(G270="","",VLOOKUP(G270,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="271" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H271" t="str">
         <f>IF(G271="","",VLOOKUP(G271,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="272" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H272" t="str">
         <f>IF(G272="","",VLOOKUP(G272,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="273" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H273" t="str">
         <f>IF(G273="","",VLOOKUP(G273,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="274" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H274" t="str">
         <f>IF(G274="","",VLOOKUP(G274,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="275" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H275" t="str">
         <f>IF(G275="","",VLOOKUP(G275,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="276" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H276" t="str">
         <f>IF(G276="","",VLOOKUP(G276,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="277" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H277" t="str">
         <f>IF(G277="","",VLOOKUP(G277,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="278" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H278" t="str">
         <f>IF(G278="","",VLOOKUP(G278,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="279" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H279" t="str">
         <f>IF(G279="","",VLOOKUP(G279,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="280" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H280" t="str">
         <f>IF(G280="","",VLOOKUP(G280,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="281" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H281" t="str">
         <f>IF(G281="","",VLOOKUP(G281,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="282" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H282" t="str">
         <f>IF(G282="","",VLOOKUP(G282,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="283" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H283" t="str">
         <f>IF(G283="","",VLOOKUP(G283,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="284" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H284" t="str">
         <f>IF(G284="","",VLOOKUP(G284,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="285" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H285" t="str">
         <f>IF(G285="","",VLOOKUP(G285,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="286" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H286" t="str">
         <f>IF(G286="","",VLOOKUP(G286,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="287" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H287" t="str">
         <f>IF(G287="","",VLOOKUP(G287,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="288" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H288" t="str">
         <f>IF(G288="","",VLOOKUP(G288,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="289" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H289" t="str">
         <f>IF(G289="","",VLOOKUP(G289,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="290" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H290" t="str">
         <f>IF(G290="","",VLOOKUP(G290,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="291" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H291" t="str">
         <f>IF(G291="","",VLOOKUP(G291,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="292" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H292" t="str">
         <f>IF(G292="","",VLOOKUP(G292,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="293" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H293" t="str">
         <f>IF(G293="","",VLOOKUP(G293,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="294" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H294" t="str">
         <f>IF(G294="","",VLOOKUP(G294,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="295" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H295" t="str">
         <f>IF(G295="","",VLOOKUP(G295,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="296" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H296" t="str">
         <f>IF(G296="","",VLOOKUP(G296,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="297" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H297" t="str">
         <f>IF(G297="","",VLOOKUP(G297,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="298" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H298" t="str">
         <f>IF(G298="","",VLOOKUP(G298,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="299" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H299" t="str">
         <f>IF(G299="","",VLOOKUP(G299,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="300" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H300" t="str">
         <f>IF(G300="","",VLOOKUP(G300,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="301" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H301" t="str">
         <f>IF(G301="","",VLOOKUP(G301,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="302" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H302" t="str">
         <f>IF(G302="","",VLOOKUP(G302,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="303" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H303" t="str">
         <f>IF(G303="","",VLOOKUP(G303,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="304" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H304" t="str">
         <f>IF(G304="","",VLOOKUP(G304,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="305" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H305" t="str">
         <f>IF(G305="","",VLOOKUP(G305,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="306" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H306" t="str">
         <f>IF(G306="","",VLOOKUP(G306,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="307" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H307" t="str">
         <f>IF(G307="","",VLOOKUP(G307,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="308" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H308" t="str">
         <f>IF(G308="","",VLOOKUP(G308,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="309" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H309" t="str">
         <f>IF(G309="","",VLOOKUP(G309,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="310" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H310" t="str">
         <f>IF(G310="","",VLOOKUP(G310,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="311" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H311" t="str">
         <f>IF(G311="","",VLOOKUP(G311,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="312" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H312" t="str">
         <f>IF(G312="","",VLOOKUP(G312,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="313" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H313" t="str">
         <f>IF(G313="","",VLOOKUP(G313,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="314" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H314" t="str">
         <f>IF(G314="","",VLOOKUP(G314,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="315" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H315" t="str">
         <f>IF(G315="","",VLOOKUP(G315,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="316" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H316" t="str">
         <f>IF(G316="","",VLOOKUP(G316,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="317" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H317" t="str">
         <f>IF(G317="","",VLOOKUP(G317,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="318" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H318" t="str">
         <f>IF(G318="","",VLOOKUP(G318,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="319" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H319" t="str">
         <f>IF(G319="","",VLOOKUP(G319,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="320" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H320" t="str">
         <f>IF(G320="","",VLOOKUP(G320,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="321" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H321" t="str">
         <f>IF(G321="","",VLOOKUP(G321,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="322" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H322" t="str">
         <f>IF(G322="","",VLOOKUP(G322,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="323" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H323" t="str">
         <f>IF(G323="","",VLOOKUP(G323,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="324" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H324" t="str">
         <f>IF(G324="","",VLOOKUP(G324,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="325" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H325" t="str">
         <f>IF(G325="","",VLOOKUP(G325,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="326" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H326" t="str">
         <f>IF(G326="","",VLOOKUP(G326,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="327" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H327" t="str">
         <f>IF(G327="","",VLOOKUP(G327,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="328" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H328" t="str">
         <f>IF(G328="","",VLOOKUP(G328,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="329" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H329" t="str">
         <f>IF(G329="","",VLOOKUP(G329,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="330" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H330" t="str">
         <f>IF(G330="","",VLOOKUP(G330,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="331" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H331" t="str">
         <f>IF(G331="","",VLOOKUP(G331,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="332" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H332" t="str">
         <f>IF(G332="","",VLOOKUP(G332,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="333" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H333" t="str">
         <f>IF(G333="","",VLOOKUP(G333,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="334" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H334" t="str">
         <f>IF(G334="","",VLOOKUP(G334,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="335" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H335" t="str">
         <f>IF(G335="","",VLOOKUP(G335,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="336" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H336" t="str">
         <f>IF(G336="","",VLOOKUP(G336,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="337" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H337" t="str">
         <f>IF(G337="","",VLOOKUP(G337,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="338" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H338" t="str">
         <f>IF(G338="","",VLOOKUP(G338,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="339" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H339" t="str">
         <f>IF(G339="","",VLOOKUP(G339,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="340" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H340" t="str">
         <f>IF(G340="","",VLOOKUP(G340,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H341" t="str">
         <f>IF(G341="","",VLOOKUP(G341,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H342" t="str">
         <f>IF(G342="","",VLOOKUP(G342,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="343" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H343" t="str">
         <f>IF(G343="","",VLOOKUP(G343,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="344" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H344" t="str">
         <f>IF(G344="","",VLOOKUP(G344,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="345" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H345" t="str">
         <f>IF(G345="","",VLOOKUP(G345,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="346" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H346" t="str">
         <f>IF(G346="","",VLOOKUP(G346,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="347" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H347" t="str">
         <f>IF(G347="","",VLOOKUP(G347,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="348" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H348" t="str">
         <f>IF(G348="","",VLOOKUP(G348,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="349" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H349" t="str">
         <f>IF(G349="","",VLOOKUP(G349,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="350" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H350" t="str">
         <f>IF(G350="","",VLOOKUP(G350,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="351" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H351" t="str">
         <f>IF(G351="","",VLOOKUP(G351,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="352" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H352" t="str">
         <f>IF(G352="","",VLOOKUP(G352,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="353" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H353" t="str">
         <f>IF(G353="","",VLOOKUP(G353,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="354" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H354" t="str">
         <f>IF(G354="","",VLOOKUP(G354,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="355" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H355" t="str">
         <f>IF(G355="","",VLOOKUP(G355,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="356" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H356" t="str">
         <f>IF(G356="","",VLOOKUP(G356,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="357" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H357" t="str">
         <f>IF(G357="","",VLOOKUP(G357,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="358" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H358" t="str">
         <f>IF(G358="","",VLOOKUP(G358,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="359" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H359" t="str">
         <f>IF(G359="","",VLOOKUP(G359,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="360" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H360" t="str">
         <f>IF(G360="","",VLOOKUP(G360,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="361" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H361" t="str">
         <f>IF(G361="","",VLOOKUP(G361,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="362" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H362" t="str">
         <f>IF(G362="","",VLOOKUP(G362,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="363" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H363" t="str">
         <f>IF(G363="","",VLOOKUP(G363,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="364" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H364" t="str">
         <f>IF(G364="","",VLOOKUP(G364,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="365" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H365" t="str">
         <f>IF(G365="","",VLOOKUP(G365,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="366" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H366" t="str">
         <f>IF(G366="","",VLOOKUP(G366,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="367" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H367" t="str">
         <f>IF(G367="","",VLOOKUP(G367,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="368" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H368" t="str">
         <f>IF(G368="","",VLOOKUP(G368,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="369" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H369" t="str">
         <f>IF(G369="","",VLOOKUP(G369,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="370" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H370" t="str">
         <f>IF(G370="","",VLOOKUP(G370,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="371" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H371" t="str">
         <f>IF(G371="","",VLOOKUP(G371,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="372" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H372" t="str">
         <f>IF(G372="","",VLOOKUP(G372,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="373" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H373" t="str">
         <f>IF(G373="","",VLOOKUP(G373,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="374" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H374" t="str">
         <f>IF(G374="","",VLOOKUP(G374,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="375" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H375" t="str">
         <f>IF(G375="","",VLOOKUP(G375,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="376" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H376" t="str">
         <f>IF(G376="","",VLOOKUP(G376,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="377" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H377" t="str">
         <f>IF(G377="","",VLOOKUP(G377,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="378" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H378" t="str">
         <f>IF(G378="","",VLOOKUP(G378,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="379" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H379" t="str">
         <f>IF(G379="","",VLOOKUP(G379,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="380" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H380" t="str">
         <f>IF(G380="","",VLOOKUP(G380,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="381" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H381" t="str">
         <f>IF(G381="","",VLOOKUP(G381,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="382" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H382" t="str">
         <f>IF(G382="","",VLOOKUP(G382,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="383" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H383" t="str">
         <f>IF(G383="","",VLOOKUP(G383,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="384" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H384" t="str">
         <f>IF(G384="","",VLOOKUP(G384,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="385" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H385" t="str">
         <f>IF(G385="","",VLOOKUP(G385,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="386" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H386" t="str">
         <f>IF(G386="","",VLOOKUP(G386,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="387" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H387" t="str">
         <f>IF(G387="","",VLOOKUP(G387,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="388" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H388" t="str">
         <f>IF(G388="","",VLOOKUP(G388,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="389" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H389" t="str">
         <f>IF(G389="","",VLOOKUP(G389,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="390" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H390" t="str">
         <f>IF(G390="","",VLOOKUP(G390,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="391" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H391" t="str">
         <f>IF(G391="","",VLOOKUP(G391,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="392" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H392" t="str">
         <f>IF(G392="","",VLOOKUP(G392,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="393" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H393" t="str">
         <f>IF(G393="","",VLOOKUP(G393,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="394" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H394" t="str">
         <f>IF(G394="","",VLOOKUP(G394,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="395" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H395" t="str">
         <f>IF(G395="","",VLOOKUP(G395,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="396" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H396" t="str">
         <f>IF(G396="","",VLOOKUP(G396,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="397" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H397" t="str">
         <f>IF(G397="","",VLOOKUP(G397,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="398" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H398" t="str">
         <f>IF(G398="","",VLOOKUP(G398,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="399" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H399" t="str">
         <f>IF(G399="","",VLOOKUP(G399,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="400" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H400" t="str">
         <f>IF(G400="","",VLOOKUP(G400,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="401" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H401" t="str">
         <f>IF(G401="","",VLOOKUP(G401,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="402" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H402" t="str">
         <f>IF(G402="","",VLOOKUP(G402,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="403" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H403" t="str">
         <f>IF(G403="","",VLOOKUP(G403,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="404" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H404" t="str">
         <f>IF(G404="","",VLOOKUP(G404,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="405" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H405" t="str">
         <f>IF(G405="","",VLOOKUP(G405,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="406" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H406" t="str">
         <f>IF(G406="","",VLOOKUP(G406,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="407" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H407" t="str">
         <f>IF(G407="","",VLOOKUP(G407,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="408" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H408" t="str">
         <f>IF(G408="","",VLOOKUP(G408,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="409" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="409" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H409" t="str">
         <f>IF(G409="","",VLOOKUP(G409,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="410" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="410" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H410" t="str">
         <f>IF(G410="","",VLOOKUP(G410,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="411" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="411" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H411" t="str">
         <f>IF(G411="","",VLOOKUP(G411,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="412" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="412" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H412" t="str">
         <f>IF(G412="","",VLOOKUP(G412,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="413" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H413" t="str">
         <f>IF(G413="","",VLOOKUP(G413,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="414" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H414" t="str">
         <f>IF(G414="","",VLOOKUP(G414,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="415" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="415" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H415" t="str">
         <f>IF(G415="","",VLOOKUP(G415,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="416" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="416" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H416" t="str">
         <f>IF(G416="","",VLOOKUP(G416,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="417" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="417" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H417" t="str">
         <f>IF(G417="","",VLOOKUP(G417,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="418" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="418" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H418" t="str">
         <f>IF(G418="","",VLOOKUP(G418,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="419" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="419" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H419" t="str">
         <f>IF(G419="","",VLOOKUP(G419,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="420" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="420" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H420" t="str">
         <f>IF(G420="","",VLOOKUP(G420,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="421" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="421" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H421" t="str">
         <f>IF(G421="","",VLOOKUP(G421,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="422" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="422" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H422" t="str">
         <f>IF(G422="","",VLOOKUP(G422,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="423" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="423" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H423" t="str">
         <f>IF(G423="","",VLOOKUP(G423,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="424" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="424" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H424" t="str">
         <f>IF(G424="","",VLOOKUP(G424,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="425" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="425" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H425" t="str">
         <f>IF(G425="","",VLOOKUP(G425,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="426" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="426" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H426" t="str">
         <f>IF(G426="","",VLOOKUP(G426,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="427" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="427" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H427" t="str">
         <f>IF(G427="","",VLOOKUP(G427,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="428" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="428" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H428" t="str">
         <f>IF(G428="","",VLOOKUP(G428,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="429" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="429" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H429" t="str">
         <f>IF(G429="","",VLOOKUP(G429,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="430" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="430" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H430" t="str">
         <f>IF(G430="","",VLOOKUP(G430,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="431" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="431" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H431" t="str">
         <f>IF(G431="","",VLOOKUP(G431,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="432" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="432" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H432" t="str">
         <f>IF(G432="","",VLOOKUP(G432,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="433" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="433" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H433" t="str">
         <f>IF(G433="","",VLOOKUP(G433,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="434" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="434" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H434" t="str">
         <f>IF(G434="","",VLOOKUP(G434,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="435" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="435" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H435" t="str">
         <f>IF(G435="","",VLOOKUP(G435,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="436" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="436" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H436" t="str">
         <f>IF(G436="","",VLOOKUP(G436,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="437" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="437" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H437" t="str">
         <f>IF(G437="","",VLOOKUP(G437,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="438" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="438" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H438" t="str">
         <f>IF(G438="","",VLOOKUP(G438,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="439" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="439" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H439" t="str">
         <f>IF(G439="","",VLOOKUP(G439,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="440" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="440" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H440" t="str">
         <f>IF(G440="","",VLOOKUP(G440,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="441" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="441" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H441" t="str">
         <f>IF(G441="","",VLOOKUP(G441,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="442" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="442" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H442" t="str">
         <f>IF(G442="","",VLOOKUP(G442,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="443" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="443" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H443" t="str">
         <f>IF(G443="","",VLOOKUP(G443,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="444" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="444" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H444" t="str">
         <f>IF(G444="","",VLOOKUP(G444,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="445" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="445" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H445" t="str">
         <f>IF(G445="","",VLOOKUP(G445,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="446" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="446" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H446" t="str">
         <f>IF(G446="","",VLOOKUP(G446,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="447" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="447" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H447" t="str">
         <f>IF(G447="","",VLOOKUP(G447,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="448" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="448" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H448" t="str">
         <f>IF(G448="","",VLOOKUP(G448,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="449" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="449" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H449" t="str">
         <f>IF(G449="","",VLOOKUP(G449,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="450" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="450" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H450" t="str">
         <f>IF(G450="","",VLOOKUP(G450,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="451" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="451" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H451" t="str">
         <f>IF(G451="","",VLOOKUP(G451,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="452" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="452" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H452" t="str">
         <f>IF(G452="","",VLOOKUP(G452,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="453" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="453" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H453" t="str">
         <f>IF(G453="","",VLOOKUP(G453,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="454" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="454" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H454" t="str">
         <f>IF(G454="","",VLOOKUP(G454,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="455" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="455" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H455" t="str">
         <f>IF(G455="","",VLOOKUP(G455,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="456" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="456" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H456" t="str">
         <f>IF(G456="","",VLOOKUP(G456,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="457" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="457" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H457" t="str">
         <f>IF(G457="","",VLOOKUP(G457,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="458" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="458" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H458" t="str">
         <f>IF(G458="","",VLOOKUP(G458,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="459" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="459" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H459" t="str">
         <f>IF(G459="","",VLOOKUP(G459,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="460" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="460" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H460" t="str">
         <f>IF(G460="","",VLOOKUP(G460,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="461" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="461" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H461" t="str">
         <f>IF(G461="","",VLOOKUP(G461,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="462" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="462" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H462" t="str">
         <f>IF(G462="","",VLOOKUP(G462,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="463" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="463" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H463" t="str">
         <f>IF(G463="","",VLOOKUP(G463,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="464" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="464" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H464" t="str">
         <f>IF(G464="","",VLOOKUP(G464,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="465" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="465" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H465" t="str">
         <f>IF(G465="","",VLOOKUP(G465,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="466" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="466" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H466" t="str">
         <f>IF(G466="","",VLOOKUP(G466,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="467" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="467" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H467" t="str">
         <f>IF(G467="","",VLOOKUP(G467,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="468" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="468" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H468" t="str">
         <f>IF(G468="","",VLOOKUP(G468,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="469" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="469" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H469" t="str">
         <f>IF(G469="","",VLOOKUP(G469,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="470" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="470" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H470" t="str">
         <f>IF(G470="","",VLOOKUP(G470,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="471" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="471" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H471" t="str">
         <f>IF(G471="","",VLOOKUP(G471,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="472" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="472" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H472" t="str">
         <f>IF(G472="","",VLOOKUP(G472,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="473" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="473" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H473" t="str">
         <f>IF(G473="","",VLOOKUP(G473,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="474" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="474" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H474" t="str">
         <f>IF(G474="","",VLOOKUP(G474,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="475" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="475" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H475" t="str">
         <f>IF(G475="","",VLOOKUP(G475,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="476" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="476" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H476" t="str">
         <f>IF(G476="","",VLOOKUP(G476,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="477" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="477" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H477" t="str">
         <f>IF(G477="","",VLOOKUP(G477,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="478" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="478" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H478" t="str">
         <f>IF(G478="","",VLOOKUP(G478,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="479" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="479" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H479" t="str">
         <f>IF(G479="","",VLOOKUP(G479,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="480" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="480" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H480" t="str">
         <f>IF(G480="","",VLOOKUP(G480,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="481" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H481" t="str">
         <f>IF(G481="","",VLOOKUP(G481,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="482" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H482" t="str">
         <f>IF(G482="","",VLOOKUP(G482,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="483" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H483" t="str">
         <f>IF(G483="","",VLOOKUP(G483,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="484" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H484" t="str">
         <f>IF(G484="","",VLOOKUP(G484,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="485" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H485" t="str">
         <f>IF(G485="","",VLOOKUP(G485,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="486" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H486" t="str">
         <f>IF(G486="","",VLOOKUP(G486,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="487" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H487" t="str">
         <f>IF(G487="","",VLOOKUP(G487,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="488" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H488" t="str">
         <f>IF(G488="","",VLOOKUP(G488,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="489" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="489" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H489" t="str">
         <f>IF(G489="","",VLOOKUP(G489,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="490" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H490" t="str">
         <f>IF(G490="","",VLOOKUP(G490,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="491" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H491" t="str">
         <f>IF(G491="","",VLOOKUP(G491,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="492" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H492" t="str">
         <f>IF(G492="","",VLOOKUP(G492,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="493" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="493" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H493" t="str">
         <f>IF(G493="","",VLOOKUP(G493,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="494" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H494" t="str">
         <f>IF(G494="","",VLOOKUP(G494,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="495" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H495" t="str">
         <f>IF(G495="","",VLOOKUP(G495,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="496" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="496" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H496" t="str">
         <f>IF(G496="","",VLOOKUP(G496,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="497" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H497" t="str">
         <f>IF(G497="","",VLOOKUP(G497,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="498" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H498" t="str">
         <f>IF(G498="","",VLOOKUP(G498,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="499" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="499" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H499" t="str">
         <f>IF(G499="","",VLOOKUP(G499,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="500" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H500" t="str">
         <f>IF(G500="","",VLOOKUP(G500,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="501" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H501" t="str">
         <f>IF(G501="","",VLOOKUP(G501,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="502" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H502" t="str">
         <f>IF(G502="","",VLOOKUP(G502,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="503" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H503" t="str">
         <f>IF(G503="","",VLOOKUP(G503,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
@@ -18547,7 +18556,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B22A23F-25BB-4234-8337-3463AF2CD81E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18556,9 +18565,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -18566,7 +18575,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -18574,7 +18583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -18582,7 +18591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -18590,7 +18599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -18598,7 +18607,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -18606,7 +18615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -18614,7 +18623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -18622,7 +18631,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -18630,7 +18639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -18638,7 +18647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -18646,7 +18655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -18654,7 +18663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -18662,7 +18671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>27</v>
       </c>

--- a/cuadros/ABRIL/ABRIL_BOSQUE_NAGUANAGUA_TUCACAS.xlsx
+++ b/cuadros/ABRIL/ABRIL_BOSQUE_NAGUANAGUA_TUCACAS.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\FISCALIZACION\cuadros\ABRIL\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAABD187-B258-4472-9F07-50D4C2A7A5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="3" r:id="rId2"/>
     <sheet name="REFERENCIA" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="109">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -210,9 +204,6 @@
     <t>D-000117245</t>
   </si>
   <si>
-    <t>23/04/026</t>
-  </si>
-  <si>
     <t>RECEPCION</t>
   </si>
   <si>
@@ -369,7 +360,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -430,12 +421,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF59487"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -448,7 +433,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,9 +533,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -563,7 +551,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -575,11 +563,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -654,7 +645,7 @@
         <xdr:cNvPr id="2" name="CuadroTexto 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF7994D-742B-48FD-B7B5-8CD0D7157A89}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2CF7994D-742B-48FD-B7B5-8CD0D7157A89}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -709,7 +700,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74A68D58-0208-44DC-9A5B-0A7362DCF02F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{74A68D58-0208-44DC-9A5B-0A7362DCF02F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -764,7 +755,7 @@
         <xdr:cNvPr id="4" name="CuadroTexto 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D78C8955-286A-4032-BBD8-1E3AD59801DC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D78C8955-286A-4032-BBD8-1E3AD59801DC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -819,7 +810,7 @@
         <xdr:cNvPr id="5" name="CuadroTexto 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E02734A2-DBB5-429C-84FA-A8881F65B24E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E02734A2-DBB5-429C-84FA-A8881F65B24E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -874,7 +865,7 @@
         <xdr:cNvPr id="6" name="CuadroTexto 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B282FD55-A400-4F94-BD32-E707B41920E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B282FD55-A400-4F94-BD32-E707B41920E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -929,7 +920,7 @@
         <xdr:cNvPr id="7" name="CuadroTexto 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB6DCE26-2AE6-4CD0-B3C8-F254B6F4BF9F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EB6DCE26-2AE6-4CD0-B3C8-F254B6F4BF9F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -984,7 +975,7 @@
         <xdr:cNvPr id="8" name="CuadroTexto 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{946E5772-59EE-4ED0-B781-DDB81A05A2B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{946E5772-59EE-4ED0-B781-DDB81A05A2B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1039,7 +1030,7 @@
         <xdr:cNvPr id="9" name="CuadroTexto 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{319F6DFD-8AA2-4306-AD21-1F969B3631FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{319F6DFD-8AA2-4306-AD21-1F969B3631FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1094,7 +1085,7 @@
         <xdr:cNvPr id="10" name="CuadroTexto 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92FDC34C-AB70-4614-8FFF-4078C9774050}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{92FDC34C-AB70-4614-8FFF-4078C9774050}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1149,7 +1140,7 @@
         <xdr:cNvPr id="11" name="CuadroTexto 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A692607E-FF5D-4CFD-B4BF-35FE01F89C0F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A692607E-FF5D-4CFD-B4BF-35FE01F89C0F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1204,7 +1195,7 @@
         <xdr:cNvPr id="12" name="CuadroTexto 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB3B7DEC-1ABA-47DF-B794-BF259B68EFE0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CB3B7DEC-1ABA-47DF-B794-BF259B68EFE0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1259,7 +1250,7 @@
         <xdr:cNvPr id="13" name="CuadroTexto 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA931F8B-C805-425A-BE48-C5F59B744A64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AA931F8B-C805-425A-BE48-C5F59B744A64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1314,7 +1305,7 @@
         <xdr:cNvPr id="14" name="CuadroTexto 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C66CAB09-DAF3-4A2C-9E93-076CCB98C0C7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C66CAB09-DAF3-4A2C-9E93-076CCB98C0C7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1369,7 +1360,7 @@
         <xdr:cNvPr id="15" name="CuadroTexto 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9472583B-924A-4841-A8B4-1DCBE9FE9AE7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9472583B-924A-4841-A8B4-1DCBE9FE9AE7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1424,7 +1415,7 @@
         <xdr:cNvPr id="16" name="CuadroTexto 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C50F45A-C171-47A0-BA67-28EE21BFEB49}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C50F45A-C171-47A0-BA67-28EE21BFEB49}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1479,7 +1470,7 @@
         <xdr:cNvPr id="17" name="CuadroTexto 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECE6D0E3-4F6A-4F80-9B0F-70F8AE57D458}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ECE6D0E3-4F6A-4F80-9B0F-70F8AE57D458}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1534,7 +1525,7 @@
         <xdr:cNvPr id="18" name="CuadroTexto 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A742941-6488-413B-92A1-C6F0F0D5CCBC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9A742941-6488-413B-92A1-C6F0F0D5CCBC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1589,7 +1580,7 @@
         <xdr:cNvPr id="19" name="CuadroTexto 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C77A68E8-BD46-40A2-9A45-A660F791A789}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C77A68E8-BD46-40A2-9A45-A660F791A789}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1644,7 +1635,7 @@
         <xdr:cNvPr id="20" name="CuadroTexto 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{079B9A57-60DE-4B30-8C63-00AE002452B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{079B9A57-60DE-4B30-8C63-00AE002452B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1699,7 +1690,7 @@
         <xdr:cNvPr id="21" name="CuadroTexto 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A95FFDC-7DAA-4FD3-B2C1-A2A79ED11255}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8A95FFDC-7DAA-4FD3-B2C1-A2A79ED11255}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1754,7 +1745,7 @@
         <xdr:cNvPr id="22" name="CuadroTexto 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5172AA03-AB32-45F7-BA1D-91EAB8EEC9EE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5172AA03-AB32-45F7-BA1D-91EAB8EEC9EE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1809,7 +1800,7 @@
         <xdr:cNvPr id="23" name="CuadroTexto 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2EB0AF3-4F33-43D7-9DD6-D8B8F7AE28E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F2EB0AF3-4F33-43D7-9DD6-D8B8F7AE28E0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1864,7 +1855,7 @@
         <xdr:cNvPr id="24" name="CuadroTexto 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{550E8AF9-8E12-4B09-BB88-3D25B55D8918}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{550E8AF9-8E12-4B09-BB88-3D25B55D8918}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1919,7 +1910,7 @@
         <xdr:cNvPr id="25" name="CuadroTexto 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F76666FE-3951-4A31-8690-35AE31698F34}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F76666FE-3951-4A31-8690-35AE31698F34}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1974,7 +1965,7 @@
         <xdr:cNvPr id="26" name="CuadroTexto 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C9513C8-D382-4AE3-B196-AAF1DD3ECD94}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8C9513C8-D382-4AE3-B196-AAF1DD3ECD94}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2029,7 +2020,7 @@
         <xdr:cNvPr id="27" name="CuadroTexto 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B366EA3-A855-4C2B-89E5-DD13EE486125}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7B366EA3-A855-4C2B-89E5-DD13EE486125}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2084,7 +2075,7 @@
         <xdr:cNvPr id="28" name="CuadroTexto 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28384F2D-13D1-4D87-80AC-449A2D69AF85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{28384F2D-13D1-4D87-80AC-449A2D69AF85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2139,7 +2130,7 @@
         <xdr:cNvPr id="29" name="CuadroTexto 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D75F71D9-EF60-47DC-9C5F-9D1BB2D31B6A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D75F71D9-EF60-47DC-9C5F-9D1BB2D31B6A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2194,7 +2185,7 @@
         <xdr:cNvPr id="30" name="CuadroTexto 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0A3C5DC-5C4C-4344-A76A-FCD8B807D148}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C0A3C5DC-5C4C-4344-A76A-FCD8B807D148}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2249,7 +2240,7 @@
         <xdr:cNvPr id="31" name="CuadroTexto 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8181737E-6237-41AD-B840-1A915CC8673C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8181737E-6237-41AD-B840-1A915CC8673C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2304,7 +2295,7 @@
         <xdr:cNvPr id="32" name="CuadroTexto 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC194ADA-EF53-4FD0-8D2D-908BB0B65937}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CC194ADA-EF53-4FD0-8D2D-908BB0B65937}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2359,7 +2350,7 @@
         <xdr:cNvPr id="33" name="CuadroTexto 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{360F2ED5-FD7F-438F-9DA1-D7CE86FD4351}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{360F2ED5-FD7F-438F-9DA1-D7CE86FD4351}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2414,7 +2405,7 @@
         <xdr:cNvPr id="34" name="CuadroTexto 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98852F2C-94A9-4D40-BF8A-696C85F76BD0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{98852F2C-94A9-4D40-BF8A-696C85F76BD0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2469,7 +2460,7 @@
         <xdr:cNvPr id="35" name="CuadroTexto 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{235DDB15-3729-4049-902A-C14B06D56C17}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{235DDB15-3729-4049-902A-C14B06D56C17}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2524,7 +2515,7 @@
         <xdr:cNvPr id="36" name="CuadroTexto 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0503350D-1299-4D1F-AF47-558215D36FFD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0503350D-1299-4D1F-AF47-558215D36FFD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2579,7 +2570,7 @@
         <xdr:cNvPr id="37" name="CuadroTexto 36">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04C62AD9-1F8B-4453-8D09-D0056E05FB8A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{04C62AD9-1F8B-4453-8D09-D0056E05FB8A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2634,7 +2625,7 @@
         <xdr:cNvPr id="38" name="CuadroTexto 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9159DE10-3E5C-419F-BAA3-FF32D8413265}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9159DE10-3E5C-419F-BAA3-FF32D8413265}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2689,7 +2680,7 @@
         <xdr:cNvPr id="39" name="CuadroTexto 38">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07369E6A-8AAB-4A1B-B452-2270A0377B7C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07369E6A-8AAB-4A1B-B452-2270A0377B7C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2744,7 +2735,7 @@
         <xdr:cNvPr id="40" name="CuadroTexto 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA630C4E-F4B2-45AC-AFF1-F2E291807CDA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CA630C4E-F4B2-45AC-AFF1-F2E291807CDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2799,7 +2790,7 @@
         <xdr:cNvPr id="41" name="CuadroTexto 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7599229-D1EA-4074-90DF-4E7FA701C3F5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A7599229-D1EA-4074-90DF-4E7FA701C3F5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2854,7 +2845,7 @@
         <xdr:cNvPr id="42" name="CuadroTexto 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F98FF8AF-CD99-43F0-A0FB-7B00781C9178}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F98FF8AF-CD99-43F0-A0FB-7B00781C9178}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2909,7 +2900,7 @@
         <xdr:cNvPr id="43" name="CuadroTexto 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D1A8947-711E-4387-ADEE-C57AAB3B1C33}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3D1A8947-711E-4387-ADEE-C57AAB3B1C33}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2964,7 +2955,7 @@
         <xdr:cNvPr id="44" name="CuadroTexto 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5628EE06-E86C-49B5-9666-D0E336CD9FAE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5628EE06-E86C-49B5-9666-D0E336CD9FAE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3019,7 +3010,7 @@
         <xdr:cNvPr id="45" name="CuadroTexto 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1922209F-CB4A-455B-800B-021E2A7211C2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1922209F-CB4A-455B-800B-021E2A7211C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3074,7 +3065,7 @@
         <xdr:cNvPr id="46" name="CuadroTexto 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E066125-2A3E-4381-8C3B-7A6F98AB34B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4E066125-2A3E-4381-8C3B-7A6F98AB34B1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3129,7 +3120,7 @@
         <xdr:cNvPr id="47" name="CuadroTexto 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A397DE42-D4C0-4B94-91E6-6E375170A71D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A397DE42-D4C0-4B94-91E6-6E375170A71D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3184,7 +3175,7 @@
         <xdr:cNvPr id="48" name="CuadroTexto 47">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E01FAFB9-3D22-4F88-8B4E-2F421EECCC77}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E01FAFB9-3D22-4F88-8B4E-2F421EECCC77}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3239,7 +3230,7 @@
         <xdr:cNvPr id="49" name="CuadroTexto 48">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1951815-32AD-4B89-BEDA-7520D8F1DFEB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A1951815-32AD-4B89-BEDA-7520D8F1DFEB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3294,7 +3285,7 @@
         <xdr:cNvPr id="50" name="CuadroTexto 49">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD8E1159-271A-4D02-AE97-4D75882EFCB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CD8E1159-271A-4D02-AE97-4D75882EFCB6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3349,7 +3340,7 @@
         <xdr:cNvPr id="51" name="CuadroTexto 50">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53A18A23-701D-400B-B012-EFA93EBBCAD0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{53A18A23-701D-400B-B012-EFA93EBBCAD0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3404,7 +3395,7 @@
         <xdr:cNvPr id="52" name="CuadroTexto 51">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FB61393-DF39-4749-8214-EA09AABC3605}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FB61393-DF39-4749-8214-EA09AABC3605}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3459,7 +3450,7 @@
         <xdr:cNvPr id="53" name="CuadroTexto 52">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3522D01-824C-4695-9DF1-F0A5B55E6C57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C3522D01-824C-4695-9DF1-F0A5B55E6C57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3514,7 +3505,7 @@
         <xdr:cNvPr id="54" name="CuadroTexto 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4214B2DA-AC82-49CA-8E61-AB9018A557FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4214B2DA-AC82-49CA-8E61-AB9018A557FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3569,7 +3560,7 @@
         <xdr:cNvPr id="55" name="CuadroTexto 54">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF515DC3-CA73-47AA-A1F0-C585C5F64DBA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DF515DC3-CA73-47AA-A1F0-C585C5F64DBA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3624,7 +3615,7 @@
         <xdr:cNvPr id="56" name="CuadroTexto 55">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49D08C5C-D84D-4EA3-9621-C8E48C6C9855}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{49D08C5C-D84D-4EA3-9621-C8E48C6C9855}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3679,7 +3670,7 @@
         <xdr:cNvPr id="57" name="CuadroTexto 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40A008F3-40CC-46E2-8DB4-4DFD278D36B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{40A008F3-40CC-46E2-8DB4-4DFD278D36B5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3734,7 +3725,7 @@
         <xdr:cNvPr id="58" name="CuadroTexto 57">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED92FBC4-F061-4DF2-8653-2128DE278B77}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED92FBC4-F061-4DF2-8653-2128DE278B77}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3789,7 +3780,7 @@
         <xdr:cNvPr id="59" name="CuadroTexto 58">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7DE0A94-4935-446F-8BB4-B789C2188B98}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A7DE0A94-4935-446F-8BB4-B789C2188B98}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3844,7 +3835,7 @@
         <xdr:cNvPr id="60" name="CuadroTexto 59">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF5EA534-64E6-497F-B310-F200BEF6E0CF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BF5EA534-64E6-497F-B310-F200BEF6E0CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3899,7 +3890,7 @@
         <xdr:cNvPr id="61" name="CuadroTexto 60">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F734C56-CB0D-4C1B-8A04-734089772648}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2F734C56-CB0D-4C1B-8A04-734089772648}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3954,7 +3945,7 @@
         <xdr:cNvPr id="62" name="CuadroTexto 61">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9710101E-C6E4-4643-87D8-9AA5ECB9E8DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9710101E-C6E4-4643-87D8-9AA5ECB9E8DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4009,7 +4000,7 @@
         <xdr:cNvPr id="63" name="CuadroTexto 62">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62DDE8F2-D913-4E62-90BD-A8A0AB4CA483}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{62DDE8F2-D913-4E62-90BD-A8A0AB4CA483}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4064,7 +4055,7 @@
         <xdr:cNvPr id="64" name="CuadroTexto 63">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDB93E1F-EC2D-46DC-9B21-29C923DC7CF9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DDB93E1F-EC2D-46DC-9B21-29C923DC7CF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4119,7 +4110,7 @@
         <xdr:cNvPr id="65" name="CuadroTexto 64">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79A9AD84-BE33-4B2C-AFC8-47A59E733AD2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{79A9AD84-BE33-4B2C-AFC8-47A59E733AD2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4174,7 +4165,7 @@
         <xdr:cNvPr id="66" name="CuadroTexto 65">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF85121F-EE53-437B-848D-A81400E38741}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FF85121F-EE53-437B-848D-A81400E38741}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4229,7 +4220,7 @@
         <xdr:cNvPr id="67" name="CuadroTexto 66">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12502C8C-3921-44FA-A3D2-44D45D06992D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{12502C8C-3921-44FA-A3D2-44D45D06992D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4284,7 +4275,7 @@
         <xdr:cNvPr id="68" name="CuadroTexto 67">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CB4EDBE-85AF-4F3C-AC39-BF53ED98D242}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5CB4EDBE-85AF-4F3C-AC39-BF53ED98D242}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4339,7 +4330,7 @@
         <xdr:cNvPr id="69" name="CuadroTexto 68">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CB00B36-E5B9-48D2-B2B9-E8F10256BB71}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3CB00B36-E5B9-48D2-B2B9-E8F10256BB71}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4394,7 +4385,7 @@
         <xdr:cNvPr id="70" name="CuadroTexto 69">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E44F5BD-9E02-4EE0-BEF1-E7DBF143C3A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4E44F5BD-9E02-4EE0-BEF1-E7DBF143C3A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4449,7 +4440,7 @@
         <xdr:cNvPr id="71" name="CuadroTexto 70">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6686B2E8-44CB-4FBD-A7E1-250118A96F85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6686B2E8-44CB-4FBD-A7E1-250118A96F85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4504,7 +4495,7 @@
         <xdr:cNvPr id="72" name="CuadroTexto 71">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16EFCBB6-2C19-43FA-8872-F7A40F59CFF4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{16EFCBB6-2C19-43FA-8872-F7A40F59CFF4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4559,7 +4550,7 @@
         <xdr:cNvPr id="73" name="CuadroTexto 72">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54524EFF-081E-455D-91B0-1D5F1B89129E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{54524EFF-081E-455D-91B0-1D5F1B89129E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4614,7 +4605,7 @@
         <xdr:cNvPr id="74" name="CuadroTexto 73">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4167024-169A-43CD-8D32-972924154C91}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C4167024-169A-43CD-8D32-972924154C91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4669,7 +4660,7 @@
         <xdr:cNvPr id="75" name="CuadroTexto 74">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15F4D81E-E7C8-426B-BF69-F8BD10CD037E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{15F4D81E-E7C8-426B-BF69-F8BD10CD037E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4724,7 +4715,7 @@
         <xdr:cNvPr id="76" name="CuadroTexto 75">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{603DBD74-7730-4E6A-99F0-497884C528C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{603DBD74-7730-4E6A-99F0-497884C528C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4779,7 +4770,7 @@
         <xdr:cNvPr id="77" name="CuadroTexto 76">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FBDC636-78FB-44E4-9EC0-19F8AC372646}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1FBDC636-78FB-44E4-9EC0-19F8AC372646}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4834,7 +4825,7 @@
         <xdr:cNvPr id="78" name="CuadroTexto 77">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7A9EDCC-3AD2-4271-B043-22D3EAC3D878}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F7A9EDCC-3AD2-4271-B043-22D3EAC3D878}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4889,7 +4880,7 @@
         <xdr:cNvPr id="79" name="CuadroTexto 78">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A05508AC-4F90-4DB5-821F-D72E86108E50}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A05508AC-4F90-4DB5-821F-D72E86108E50}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4944,7 +4935,7 @@
         <xdr:cNvPr id="80" name="CuadroTexto 79">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97A1FC03-9278-457F-AFE3-4C92DB15B728}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{97A1FC03-9278-457F-AFE3-4C92DB15B728}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4999,7 +4990,7 @@
         <xdr:cNvPr id="81" name="CuadroTexto 80">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F17BF97A-A652-4C5C-80BC-467E8FAF7F62}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F17BF97A-A652-4C5C-80BC-467E8FAF7F62}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5054,7 +5045,7 @@
         <xdr:cNvPr id="82" name="CuadroTexto 81">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{811ABB08-2508-482C-8EB3-0FB9C0B259CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{811ABB08-2508-482C-8EB3-0FB9C0B259CA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5109,7 +5100,7 @@
         <xdr:cNvPr id="83" name="CuadroTexto 82">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5FD72CD-9321-4ABA-9F25-CFCF27FD5F79}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E5FD72CD-9321-4ABA-9F25-CFCF27FD5F79}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5164,7 +5155,7 @@
         <xdr:cNvPr id="84" name="CuadroTexto 83">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE5F92B2-9E1D-4900-8DE6-FA831732390C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EE5F92B2-9E1D-4900-8DE6-FA831732390C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5219,7 +5210,7 @@
         <xdr:cNvPr id="85" name="CuadroTexto 84">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76EBF101-5224-428F-B958-FC3C60442A38}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76EBF101-5224-428F-B958-FC3C60442A38}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5274,7 +5265,7 @@
         <xdr:cNvPr id="86" name="CuadroTexto 85">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E12363C7-F598-45F2-AA8D-59E0905FEFFE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E12363C7-F598-45F2-AA8D-59E0905FEFFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5329,7 +5320,7 @@
         <xdr:cNvPr id="87" name="CuadroTexto 86">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DBF8150-9C5A-4740-9841-2E4584E0F99A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3DBF8150-9C5A-4740-9841-2E4584E0F99A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5384,7 +5375,7 @@
         <xdr:cNvPr id="88" name="CuadroTexto 87">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13E0F143-BA32-4656-BA82-FA5F7612715A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{13E0F143-BA32-4656-BA82-FA5F7612715A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5439,7 +5430,7 @@
         <xdr:cNvPr id="89" name="CuadroTexto 88">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7219173A-543F-4ECE-A402-6CB2FAE4AAA1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7219173A-543F-4ECE-A402-6CB2FAE4AAA1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5494,7 +5485,7 @@
         <xdr:cNvPr id="90" name="CuadroTexto 89">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DB1A3A9-C613-46FC-B996-735F07E5DE4E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3DB1A3A9-C613-46FC-B996-735F07E5DE4E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5549,7 +5540,7 @@
         <xdr:cNvPr id="91" name="CuadroTexto 90">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{523FBB43-1A07-4ADE-BB1A-FCEBFA6B8369}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{523FBB43-1A07-4ADE-BB1A-FCEBFA6B8369}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5604,7 +5595,7 @@
         <xdr:cNvPr id="92" name="CuadroTexto 91">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF80933-94D4-4CA0-884D-40423998C4C9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EFF80933-94D4-4CA0-884D-40423998C4C9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5659,7 +5650,7 @@
         <xdr:cNvPr id="93" name="CuadroTexto 92">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{901506A4-A90D-4200-89BB-AD779D37BFDF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{901506A4-A90D-4200-89BB-AD779D37BFDF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5714,7 +5705,7 @@
         <xdr:cNvPr id="94" name="CuadroTexto 93">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4E8208A-58BE-48C9-82E4-B2638ACAA54C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A4E8208A-58BE-48C9-82E4-B2638ACAA54C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5769,7 +5760,7 @@
         <xdr:cNvPr id="95" name="CuadroTexto 94">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58AACC08-670B-49AF-9907-9988995B5BF4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{58AACC08-670B-49AF-9907-9988995B5BF4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5824,7 +5815,7 @@
         <xdr:cNvPr id="96" name="CuadroTexto 95">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E167A9D-DF3B-4206-9E4C-EAC0EDB2E151}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9E167A9D-DF3B-4206-9E4C-EAC0EDB2E151}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5879,7 +5870,7 @@
         <xdr:cNvPr id="97" name="CuadroTexto 96">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{651BE143-7217-4BE5-9A5A-64C47F111387}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{651BE143-7217-4BE5-9A5A-64C47F111387}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5934,7 +5925,7 @@
         <xdr:cNvPr id="98" name="CuadroTexto 97">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6277F7C7-44BA-48D7-A550-DC61E0673A9C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6277F7C7-44BA-48D7-A550-DC61E0673A9C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5989,7 +5980,7 @@
         <xdr:cNvPr id="99" name="CuadroTexto 98">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E267271C-4E05-4B7F-9958-C487030C853E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E267271C-4E05-4B7F-9958-C487030C853E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6044,7 +6035,7 @@
         <xdr:cNvPr id="100" name="CuadroTexto 99">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{649883DD-04CE-47D8-AC55-609550B1B439}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{649883DD-04CE-47D8-AC55-609550B1B439}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6099,7 +6090,7 @@
         <xdr:cNvPr id="101" name="CuadroTexto 100">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06306A5D-BC59-4294-B11D-489BA4119393}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{06306A5D-BC59-4294-B11D-489BA4119393}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6154,7 +6145,7 @@
         <xdr:cNvPr id="102" name="CuadroTexto 101">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AC28CB5-32C8-4D67-B7B0-735CB189D222}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5AC28CB5-32C8-4D67-B7B0-735CB189D222}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6209,7 +6200,7 @@
         <xdr:cNvPr id="103" name="CuadroTexto 102">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC5C0587-38FD-4A42-9022-C28E02FD0EC2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CC5C0587-38FD-4A42-9022-C28E02FD0EC2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6264,7 +6255,7 @@
         <xdr:cNvPr id="104" name="CuadroTexto 103">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22D3ADD5-E733-49BC-80A9-79011235E6C8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{22D3ADD5-E733-49BC-80A9-79011235E6C8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6319,7 +6310,7 @@
         <xdr:cNvPr id="105" name="CuadroTexto 104">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0743BF41-9D6C-419D-9B5A-A670921002DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0743BF41-9D6C-419D-9B5A-A670921002DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6374,7 +6365,7 @@
         <xdr:cNvPr id="106" name="CuadroTexto 105">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54BEB9BE-879C-45B9-B6C2-1666AD7AA7E4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{54BEB9BE-879C-45B9-B6C2-1666AD7AA7E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6429,7 +6420,7 @@
         <xdr:cNvPr id="107" name="CuadroTexto 106">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3508F6BA-D87F-42C1-8E17-510E6D967638}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3508F6BA-D87F-42C1-8E17-510E6D967638}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6484,7 +6475,7 @@
         <xdr:cNvPr id="108" name="CuadroTexto 107">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB12ED58-21EC-4F28-9C83-9CB152B776A8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AB12ED58-21EC-4F28-9C83-9CB152B776A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6539,7 +6530,7 @@
         <xdr:cNvPr id="109" name="CuadroTexto 108">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB2E665D-0E8C-42E9-9C5F-B3EC4E1399B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AB2E665D-0E8C-42E9-9C5F-B3EC4E1399B9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6594,7 +6585,7 @@
         <xdr:cNvPr id="110" name="CuadroTexto 109">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8D26B6E-B843-4475-BAD2-586229D7C909}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D8D26B6E-B843-4475-BAD2-586229D7C909}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6649,7 +6640,7 @@
         <xdr:cNvPr id="111" name="CuadroTexto 110">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3C7B05A-E963-4E59-B4D8-13542D731233}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D3C7B05A-E963-4E59-B4D8-13542D731233}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6704,7 +6695,7 @@
         <xdr:cNvPr id="112" name="CuadroTexto 111">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B82C59CB-AC76-4268-992F-5A8BEAF3360A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B82C59CB-AC76-4268-992F-5A8BEAF3360A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6759,7 +6750,7 @@
         <xdr:cNvPr id="113" name="CuadroTexto 112">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB0756B6-0EB7-412E-B2D0-6AE091F63E2A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AB0756B6-0EB7-412E-B2D0-6AE091F63E2A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6814,7 +6805,7 @@
         <xdr:cNvPr id="114" name="CuadroTexto 113">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{308E02E7-4A63-4ADA-B4AB-897979E49E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{308E02E7-4A63-4ADA-B4AB-897979E49E64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6869,7 +6860,7 @@
         <xdr:cNvPr id="115" name="CuadroTexto 114">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F78AC69-72C0-4EEF-B7E6-CE413BF2E82C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6F78AC69-72C0-4EEF-B7E6-CE413BF2E82C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6924,7 +6915,7 @@
         <xdr:cNvPr id="116" name="CuadroTexto 115">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FE6A5BD-BA16-4A09-B2E9-6464884C57C7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4FE6A5BD-BA16-4A09-B2E9-6464884C57C7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6979,7 +6970,7 @@
         <xdr:cNvPr id="117" name="CuadroTexto 116">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A70B9AA-68A3-4BE6-8F45-C48DF20390EF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2A70B9AA-68A3-4BE6-8F45-C48DF20390EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7034,7 +7025,7 @@
         <xdr:cNvPr id="118" name="CuadroTexto 117">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D07BAF3-8E9D-4B50-9CAD-2435486998E1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0D07BAF3-8E9D-4B50-9CAD-2435486998E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7089,7 +7080,7 @@
         <xdr:cNvPr id="119" name="CuadroTexto 118">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E5AA600-E351-4CED-9F8B-B5778BC2445A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0E5AA600-E351-4CED-9F8B-B5778BC2445A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7144,7 +7135,7 @@
         <xdr:cNvPr id="120" name="CuadroTexto 119">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68C57233-AEAF-43D1-80B9-BEB9F5F0CFB4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68C57233-AEAF-43D1-80B9-BEB9F5F0CFB4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7199,7 +7190,7 @@
         <xdr:cNvPr id="121" name="CuadroTexto 120">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C135E95D-9C71-4202-AEC4-1976C797C1DE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C135E95D-9C71-4202-AEC4-1976C797C1DE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7254,7 +7245,7 @@
         <xdr:cNvPr id="122" name="CuadroTexto 121">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCB0625B-189B-41BA-90AD-33F6677D7662}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BCB0625B-189B-41BA-90AD-33F6677D7662}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7309,7 +7300,7 @@
         <xdr:cNvPr id="123" name="CuadroTexto 122">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88170135-FBC7-4533-9531-C3D0A2688D1A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{88170135-FBC7-4533-9531-C3D0A2688D1A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7364,7 +7355,7 @@
         <xdr:cNvPr id="124" name="CuadroTexto 123">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C6957C5-D7AC-4AF7-9507-4416696E51E4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8C6957C5-D7AC-4AF7-9507-4416696E51E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7419,7 +7410,7 @@
         <xdr:cNvPr id="125" name="CuadroTexto 124">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BA11865-D6FB-4A63-85D0-FE617BC2FAEA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6BA11865-D6FB-4A63-85D0-FE617BC2FAEA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7474,7 +7465,7 @@
         <xdr:cNvPr id="126" name="CuadroTexto 125">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC7A6B31-1EA8-497D-B452-1C251D6846CE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CC7A6B31-1EA8-497D-B452-1C251D6846CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7529,7 +7520,7 @@
         <xdr:cNvPr id="127" name="CuadroTexto 126">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6404FFFC-3413-4CB0-BFFC-A209C79574CC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6404FFFC-3413-4CB0-BFFC-A209C79574CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7584,7 +7575,7 @@
         <xdr:cNvPr id="128" name="CuadroTexto 127">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A490AAD-DD4E-4C0C-BC19-9E3F5E1DAD4C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4A490AAD-DD4E-4C0C-BC19-9E3F5E1DAD4C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7639,7 +7630,7 @@
         <xdr:cNvPr id="129" name="CuadroTexto 128">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84A2E528-10F5-4A54-9A55-D77A5770811D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{84A2E528-10F5-4A54-9A55-D77A5770811D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7694,7 +7685,7 @@
         <xdr:cNvPr id="130" name="CuadroTexto 129">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7D5450C-31F6-44FD-8A65-CB6E4D41DED2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E7D5450C-31F6-44FD-8A65-CB6E4D41DED2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7749,7 +7740,7 @@
         <xdr:cNvPr id="131" name="CuadroTexto 130">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21A1D7EC-4426-4D63-B304-40A97E4DB9DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{21A1D7EC-4426-4D63-B304-40A97E4DB9DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7804,7 +7795,7 @@
         <xdr:cNvPr id="132" name="CuadroTexto 131">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20537B2E-F39B-4B44-A294-286B18CD574A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{20537B2E-F39B-4B44-A294-286B18CD574A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7859,7 +7850,7 @@
         <xdr:cNvPr id="133" name="CuadroTexto 132">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7183B09F-BC5E-4DA9-976D-0F9251CF94B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7183B09F-BC5E-4DA9-976D-0F9251CF94B1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7914,7 +7905,7 @@
         <xdr:cNvPr id="134" name="CuadroTexto 133">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A367D10E-0B6B-44F7-A93C-508A61CA8B93}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A367D10E-0B6B-44F7-A93C-508A61CA8B93}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7969,7 +7960,7 @@
         <xdr:cNvPr id="135" name="CuadroTexto 134">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FDA1DEB-0494-4380-8691-78F570F47FA3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6FDA1DEB-0494-4380-8691-78F570F47FA3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8024,7 +8015,7 @@
         <xdr:cNvPr id="136" name="CuadroTexto 135">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAEE1BCA-13EC-4067-96F1-8B4A68C0C1A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FAEE1BCA-13EC-4067-96F1-8B4A68C0C1A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8079,7 +8070,7 @@
         <xdr:cNvPr id="137" name="CuadroTexto 136">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99743484-9EA9-493D-B39D-6809D113663F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{99743484-9EA9-493D-B39D-6809D113663F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8134,7 +8125,7 @@
         <xdr:cNvPr id="138" name="CuadroTexto 137">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E14D6C95-0BAB-44E1-9713-D3D795F211A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E14D6C95-0BAB-44E1-9713-D3D795F211A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8189,7 +8180,7 @@
         <xdr:cNvPr id="139" name="CuadroTexto 138">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAFD1C8F-17C2-4810-9400-62A6CEF1F566}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BAFD1C8F-17C2-4810-9400-62A6CEF1F566}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8244,7 +8235,7 @@
         <xdr:cNvPr id="140" name="CuadroTexto 139">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A121FB1B-2FFB-4A12-8A39-A80BA055C731}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A121FB1B-2FFB-4A12-8A39-A80BA055C731}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8299,7 +8290,7 @@
         <xdr:cNvPr id="141" name="CuadroTexto 140">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AF7FD40-6F13-4794-9BCB-63128599798F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6AF7FD40-6F13-4794-9BCB-63128599798F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8354,7 +8345,7 @@
         <xdr:cNvPr id="142" name="CuadroTexto 141">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A76CBE2-501B-47CB-B121-943F5AC087AB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5A76CBE2-501B-47CB-B121-943F5AC087AB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8409,7 +8400,7 @@
         <xdr:cNvPr id="143" name="CuadroTexto 142">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85EFD972-4F55-4686-8238-8F8FEFE8895F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{85EFD972-4F55-4686-8238-8F8FEFE8895F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8464,7 +8455,7 @@
         <xdr:cNvPr id="144" name="CuadroTexto 143">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14F2CDA7-A9B6-4885-97F8-2FF5863808EF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{14F2CDA7-A9B6-4885-97F8-2FF5863808EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8519,7 +8510,7 @@
         <xdr:cNvPr id="145" name="CuadroTexto 144">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CA9A2CA-C34D-47D5-9E2B-3627EFF7CE6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8CA9A2CA-C34D-47D5-9E2B-3627EFF7CE6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8574,7 +8565,7 @@
         <xdr:cNvPr id="146" name="CuadroTexto 145">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6FF19F6-F353-4595-9CE6-0BE7119233BE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F6FF19F6-F353-4595-9CE6-0BE7119233BE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8629,7 +8620,7 @@
         <xdr:cNvPr id="147" name="CuadroTexto 146">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED59BC88-899B-44B0-BA67-05600F2C854B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED59BC88-899B-44B0-BA67-05600F2C854B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8684,7 +8675,7 @@
         <xdr:cNvPr id="148" name="CuadroTexto 147">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4C7620F-B3BC-46F8-B4BD-15E7EC7CD830}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C4C7620F-B3BC-46F8-B4BD-15E7EC7CD830}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8739,7 +8730,7 @@
         <xdr:cNvPr id="149" name="CuadroTexto 148">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DABB196-339F-4AEF-AAB0-814C642B0CBE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7DABB196-339F-4AEF-AAB0-814C642B0CBE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8794,7 +8785,7 @@
         <xdr:cNvPr id="150" name="CuadroTexto 149">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91AC526F-4439-4BCC-8868-8C6D78BF23F3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{91AC526F-4439-4BCC-8868-8C6D78BF23F3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8849,7 +8840,7 @@
         <xdr:cNvPr id="151" name="CuadroTexto 150">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D7F2CBA-1971-43AD-8591-CAC7F7EBCB8E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1D7F2CBA-1971-43AD-8591-CAC7F7EBCB8E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8904,7 +8895,7 @@
         <xdr:cNvPr id="152" name="CuadroTexto 151">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2512BFAD-125A-46EA-B862-A50A5924902D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2512BFAD-125A-46EA-B862-A50A5924902D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8959,7 +8950,7 @@
         <xdr:cNvPr id="153" name="CuadroTexto 152">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCE7EEAC-38CB-4F78-8281-D62A4F18CB1E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FCE7EEAC-38CB-4F78-8281-D62A4F18CB1E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9014,7 +9005,7 @@
         <xdr:cNvPr id="154" name="CuadroTexto 153">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5B35305-C9AC-48B3-BEC8-3EEC912B56F4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5B35305-C9AC-48B3-BEC8-3EEC912B56F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9069,7 +9060,7 @@
         <xdr:cNvPr id="155" name="CuadroTexto 154">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA2568B6-D747-45AF-9F38-5CD2AC57D77C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AA2568B6-D747-45AF-9F38-5CD2AC57D77C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9124,7 +9115,7 @@
         <xdr:cNvPr id="156" name="CuadroTexto 155">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E29D74D-1228-4E70-9A95-8962DA99FCE8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3E29D74D-1228-4E70-9A95-8962DA99FCE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9179,7 +9170,7 @@
         <xdr:cNvPr id="157" name="CuadroTexto 156">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BB05535-6CFF-48F9-8978-73697C5C662F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6BB05535-6CFF-48F9-8978-73697C5C662F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9234,7 +9225,7 @@
         <xdr:cNvPr id="158" name="CuadroTexto 157">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC58FB47-4796-413B-AD2B-37C776C8F113}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CC58FB47-4796-413B-AD2B-37C776C8F113}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9289,7 +9280,7 @@
         <xdr:cNvPr id="159" name="CuadroTexto 158">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{862A2DC5-0C0F-413F-ACC2-B58D85501912}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{862A2DC5-0C0F-413F-ACC2-B58D85501912}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9344,7 +9335,7 @@
         <xdr:cNvPr id="160" name="CuadroTexto 159">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E0D0772-AFF5-4A7D-B1CE-F520114957C6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E0D0772-AFF5-4A7D-B1CE-F520114957C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9399,7 +9390,7 @@
         <xdr:cNvPr id="161" name="CuadroTexto 160">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{612CE4B3-B162-48CE-A20D-3D6CC82EE9D5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{612CE4B3-B162-48CE-A20D-3D6CC82EE9D5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9454,7 +9445,7 @@
         <xdr:cNvPr id="162" name="CuadroTexto 161">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF2E0E86-48C2-4108-861D-FC54C2F1679B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EF2E0E86-48C2-4108-861D-FC54C2F1679B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9509,7 +9500,7 @@
         <xdr:cNvPr id="163" name="CuadroTexto 162">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C08F8CBA-306A-4847-88BF-BDB83071A36A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C08F8CBA-306A-4847-88BF-BDB83071A36A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9564,7 +9555,7 @@
         <xdr:cNvPr id="164" name="CuadroTexto 163">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A33BEB48-0D27-4F04-BD09-A5267B336DF8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A33BEB48-0D27-4F04-BD09-A5267B336DF8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9619,7 +9610,7 @@
         <xdr:cNvPr id="165" name="CuadroTexto 164">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B26315C-8502-4A74-967E-E2FACA247903}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3B26315C-8502-4A74-967E-E2FACA247903}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9674,7 +9665,7 @@
         <xdr:cNvPr id="166" name="CuadroTexto 165">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E15570E9-B356-4C6B-AE9D-09F0CC68794D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E15570E9-B356-4C6B-AE9D-09F0CC68794D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9729,7 +9720,7 @@
         <xdr:cNvPr id="167" name="CuadroTexto 166">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA21E28D-5936-42FC-82DC-109919EB2C45}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BA21E28D-5936-42FC-82DC-109919EB2C45}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9784,7 +9775,7 @@
         <xdr:cNvPr id="168" name="CuadroTexto 167">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB08ACE1-4463-4A85-88A9-6012D232EAF5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CB08ACE1-4463-4A85-88A9-6012D232EAF5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9839,7 +9830,7 @@
         <xdr:cNvPr id="169" name="CuadroTexto 168">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D4CB74-BC88-45B2-A09B-371DDC74AF8C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{87D4CB74-BC88-45B2-A09B-371DDC74AF8C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9894,7 +9885,7 @@
         <xdr:cNvPr id="170" name="CuadroTexto 169">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6767991E-1E1A-4369-8F05-5671EC1CACC3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6767991E-1E1A-4369-8F05-5671EC1CACC3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9949,7 +9940,7 @@
         <xdr:cNvPr id="171" name="CuadroTexto 170">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73C7F24C-40A4-45CC-9378-39296DD27127}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{73C7F24C-40A4-45CC-9378-39296DD27127}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10004,7 +9995,7 @@
         <xdr:cNvPr id="172" name="CuadroTexto 171">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E270BEC-9F58-4127-8811-F3DE220E4EB3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3E270BEC-9F58-4127-8811-F3DE220E4EB3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10059,7 +10050,7 @@
         <xdr:cNvPr id="173" name="CuadroTexto 172">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DFD8B6D-EEB1-4202-BA19-99BDF4081839}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9DFD8B6D-EEB1-4202-BA19-99BDF4081839}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10114,7 +10105,7 @@
         <xdr:cNvPr id="174" name="CuadroTexto 173">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC65175A-B483-4BF8-A4FB-DEDB8EF0AAB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AC65175A-B483-4BF8-A4FB-DEDB8EF0AAB7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10169,7 +10160,7 @@
         <xdr:cNvPr id="175" name="CuadroTexto 174">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F864030E-9D52-4387-B2C3-A5CD88174EEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F864030E-9D52-4387-B2C3-A5CD88174EEF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10224,7 +10215,7 @@
         <xdr:cNvPr id="176" name="CuadroTexto 175">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EFEDBCE-CED5-4E73-BED9-4995A7A53C9B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8EFEDBCE-CED5-4E73-BED9-4995A7A53C9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10279,7 +10270,7 @@
         <xdr:cNvPr id="177" name="CuadroTexto 176">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E2C25A5-D1B2-45B2-9E67-2F7C5C4EC9E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4E2C25A5-D1B2-45B2-9E67-2F7C5C4EC9E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10334,7 +10325,7 @@
         <xdr:cNvPr id="178" name="CuadroTexto 177">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C6A0FFF-B04A-46BB-8C6F-16790EE3749F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0C6A0FFF-B04A-46BB-8C6F-16790EE3749F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10389,7 +10380,7 @@
         <xdr:cNvPr id="179" name="CuadroTexto 178">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18AFE296-0690-4A79-AAEC-E7BFBA4DCE33}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{18AFE296-0690-4A79-AAEC-E7BFBA4DCE33}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10444,7 +10435,7 @@
         <xdr:cNvPr id="180" name="CuadroTexto 179">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DC8E58D-588F-4CE1-8D65-1253A8CCE8B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6DC8E58D-588F-4CE1-8D65-1253A8CCE8B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10499,7 +10490,7 @@
         <xdr:cNvPr id="181" name="CuadroTexto 180">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF5E5ADE-75B8-4A50-AD57-BFE464578644}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BF5E5ADE-75B8-4A50-AD57-BFE464578644}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10554,7 +10545,7 @@
         <xdr:cNvPr id="182" name="CuadroTexto 181">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DB98061-6C8B-4413-BA24-04AD70D2B62C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1DB98061-6C8B-4413-BA24-04AD70D2B62C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10609,7 +10600,7 @@
         <xdr:cNvPr id="183" name="CuadroTexto 182">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDAB3488-11F7-49C4-8D51-93D667E6543A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BDAB3488-11F7-49C4-8D51-93D667E6543A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10664,7 +10655,7 @@
         <xdr:cNvPr id="184" name="CuadroTexto 183">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03DD611F-B61A-43DE-AC83-28C3ECFDDDFE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{03DD611F-B61A-43DE-AC83-28C3ECFDDDFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10719,7 +10710,7 @@
         <xdr:cNvPr id="185" name="CuadroTexto 184">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14021916-7E30-4E9B-8E8D-EDA45B99A857}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{14021916-7E30-4E9B-8E8D-EDA45B99A857}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10774,7 +10765,7 @@
         <xdr:cNvPr id="186" name="CuadroTexto 185">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8DC75A7-756C-401A-B735-99E867F9D210}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C8DC75A7-756C-401A-B735-99E867F9D210}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10829,7 +10820,7 @@
         <xdr:cNvPr id="187" name="CuadroTexto 186">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCCE8DBE-4784-486C-9D2A-5A761292C8CB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CCCE8DBE-4784-486C-9D2A-5A761292C8CB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10884,7 +10875,7 @@
         <xdr:cNvPr id="188" name="CuadroTexto 187">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07C5C0D6-38DC-4DF3-BA58-71F1DCB8D3A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07C5C0D6-38DC-4DF3-BA58-71F1DCB8D3A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10939,7 +10930,7 @@
         <xdr:cNvPr id="189" name="CuadroTexto 188">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CAF24D3-9692-4D81-A8F3-0D689F4C98C0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3CAF24D3-9692-4D81-A8F3-0D689F4C98C0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10994,7 +10985,7 @@
         <xdr:cNvPr id="190" name="CuadroTexto 189">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97B155BD-9B5D-44F5-843D-624A8DABEA7E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{97B155BD-9B5D-44F5-843D-624A8DABEA7E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11049,7 +11040,7 @@
         <xdr:cNvPr id="191" name="CuadroTexto 190">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7EE236A-9B11-410A-86A0-D36387CF7DE8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A7EE236A-9B11-410A-86A0-D36387CF7DE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11104,7 +11095,7 @@
         <xdr:cNvPr id="192" name="CuadroTexto 191">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21D700AC-ABA9-4F5B-AB0A-0EE09389930C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{21D700AC-ABA9-4F5B-AB0A-0EE09389930C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11159,7 +11150,7 @@
         <xdr:cNvPr id="193" name="CuadroTexto 192">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92378884-476F-47BC-A7F3-6468ECCD6033}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{92378884-476F-47BC-A7F3-6468ECCD6033}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11214,7 +11205,7 @@
         <xdr:cNvPr id="194" name="CuadroTexto 193">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{837F6DA2-D217-4F24-92D1-0C542971E9D6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{837F6DA2-D217-4F24-92D1-0C542971E9D6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11269,7 +11260,7 @@
         <xdr:cNvPr id="195" name="CuadroTexto 194">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74C8EFBA-DAFF-4F67-99A1-24B35A8FDFFF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{74C8EFBA-DAFF-4F67-99A1-24B35A8FDFFF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11324,7 +11315,7 @@
         <xdr:cNvPr id="196" name="CuadroTexto 195">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4045E83E-1D10-4143-BE41-B07B6CF4E164}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4045E83E-1D10-4143-BE41-B07B6CF4E164}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11379,7 +11370,7 @@
         <xdr:cNvPr id="197" name="CuadroTexto 196">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC9701E5-FCF1-4E95-91A4-A7AAA0F0AD21}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AC9701E5-FCF1-4E95-91A4-A7AAA0F0AD21}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11434,7 +11425,7 @@
         <xdr:cNvPr id="198" name="CuadroTexto 197">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68DB7ABC-3AC6-41E4-B9CC-9D62BD24B254}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68DB7ABC-3AC6-41E4-B9CC-9D62BD24B254}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11489,7 +11480,7 @@
         <xdr:cNvPr id="199" name="CuadroTexto 198">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC39E17A-0C08-4951-87C1-FE16D56C187D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CC39E17A-0C08-4951-87C1-FE16D56C187D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11544,7 +11535,7 @@
         <xdr:cNvPr id="200" name="CuadroTexto 199">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6A54A92-437A-4D3B-B375-697FC453B641}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C6A54A92-437A-4D3B-B375-697FC453B641}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11599,7 +11590,7 @@
         <xdr:cNvPr id="201" name="CuadroTexto 200">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{870633A9-68D5-4677-84D0-7241D4B648F2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{870633A9-68D5-4677-84D0-7241D4B648F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11654,7 +11645,7 @@
         <xdr:cNvPr id="202" name="CuadroTexto 201">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FAD0D50-ABE7-44C6-ABF9-4FC7B848AC66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FAD0D50-ABE7-44C6-ABF9-4FC7B848AC66}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11709,7 +11700,7 @@
         <xdr:cNvPr id="203" name="CuadroTexto 202">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03BB8A77-9190-4C5A-AD49-F973DA4766F8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{03BB8A77-9190-4C5A-AD49-F973DA4766F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11764,7 +11755,7 @@
         <xdr:cNvPr id="204" name="CuadroTexto 203">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07DE3498-EE76-4694-BFC6-B2A095EC9FE0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07DE3498-EE76-4694-BFC6-B2A095EC9FE0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11819,7 +11810,7 @@
         <xdr:cNvPr id="205" name="CuadroTexto 204">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFBA33FB-F378-4CDD-BCCC-A1774355B3B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BFBA33FB-F378-4CDD-BCCC-A1774355B3B3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11874,7 +11865,7 @@
         <xdr:cNvPr id="206" name="CuadroTexto 205">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C739FBE-60E8-49EA-9CD2-33062D0444A7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5C739FBE-60E8-49EA-9CD2-33062D0444A7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11929,7 +11920,7 @@
         <xdr:cNvPr id="207" name="CuadroTexto 206">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EF24E66-1789-45F8-A0B5-A0B93F7E0F75}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8EF24E66-1789-45F8-A0B5-A0B93F7E0F75}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11984,7 +11975,7 @@
         <xdr:cNvPr id="208" name="CuadroTexto 207">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F893CBC-BC82-40AD-976F-4B1644253284}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3F893CBC-BC82-40AD-976F-4B1644253284}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12039,7 +12030,7 @@
         <xdr:cNvPr id="209" name="CuadroTexto 208">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77C5C92-ECF2-421B-84D6-407C8BAE3F0D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B77C5C92-ECF2-421B-84D6-407C8BAE3F0D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12094,7 +12085,7 @@
         <xdr:cNvPr id="210" name="CuadroTexto 209">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F4D6907-D5CF-4AB9-AC81-B2A95FCE7081}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1F4D6907-D5CF-4AB9-AC81-B2A95FCE7081}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12149,7 +12140,7 @@
         <xdr:cNvPr id="211" name="CuadroTexto 210">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0969C759-8D46-4B3D-BE37-BD5D5B3395E2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0969C759-8D46-4B3D-BE37-BD5D5B3395E2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12204,7 +12195,7 @@
         <xdr:cNvPr id="212" name="CuadroTexto 211">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C2FE180-E556-4990-8761-A61CC9F32C45}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C2FE180-E556-4990-8761-A61CC9F32C45}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12259,7 +12250,7 @@
         <xdr:cNvPr id="213" name="CuadroTexto 212">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1038144B-904A-4B95-A704-D841B4AE5543}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1038144B-904A-4B95-A704-D841B4AE5543}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12314,7 +12305,7 @@
         <xdr:cNvPr id="214" name="CuadroTexto 213">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CEF86F6-B7D8-4779-B57A-CE7BBCF461DE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5CEF86F6-B7D8-4779-B57A-CE7BBCF461DE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12369,7 +12360,7 @@
         <xdr:cNvPr id="215" name="CuadroTexto 214">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4F5FACD-1361-47BB-A23D-453927683172}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C4F5FACD-1361-47BB-A23D-453927683172}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12424,7 +12415,7 @@
         <xdr:cNvPr id="216" name="CuadroTexto 215">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{251B65DE-323F-423A-B029-E8B674E22FBE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{251B65DE-323F-423A-B029-E8B674E22FBE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12479,7 +12470,7 @@
         <xdr:cNvPr id="217" name="CuadroTexto 216">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E5F60EA-AE38-4380-A27D-70B17F8B5722}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3E5F60EA-AE38-4380-A27D-70B17F8B5722}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12534,7 +12525,7 @@
         <xdr:cNvPr id="218" name="CuadroTexto 217">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B516498-FF9C-4BD2-AC8D-17DBA2EF707C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8B516498-FF9C-4BD2-AC8D-17DBA2EF707C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12589,7 +12580,7 @@
         <xdr:cNvPr id="219" name="CuadroTexto 218">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6569119-434A-46FD-BC91-CEFAC52D8A7B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E6569119-434A-46FD-BC91-CEFAC52D8A7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12644,7 +12635,7 @@
         <xdr:cNvPr id="220" name="CuadroTexto 219">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AFA7FC9-59FF-485F-89C5-D8FC33624883}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9AFA7FC9-59FF-485F-89C5-D8FC33624883}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12699,7 +12690,7 @@
         <xdr:cNvPr id="221" name="CuadroTexto 220">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14C560E4-88DC-4190-B868-50996C8B3143}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{14C560E4-88DC-4190-B868-50996C8B3143}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12754,7 +12745,7 @@
         <xdr:cNvPr id="222" name="CuadroTexto 221">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0471E6E7-DD7B-44E1-9E92-6C7588E02B86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0471E6E7-DD7B-44E1-9E92-6C7588E02B86}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12809,7 +12800,7 @@
         <xdr:cNvPr id="223" name="CuadroTexto 222">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E280398-9F9D-4A3D-ABD7-C785ACFDF609}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0E280398-9F9D-4A3D-ABD7-C785ACFDF609}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12864,7 +12855,7 @@
         <xdr:cNvPr id="224" name="CuadroTexto 223">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C18E5973-0160-4A80-A584-FD06D2EC003B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C18E5973-0160-4A80-A584-FD06D2EC003B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12919,7 +12910,7 @@
         <xdr:cNvPr id="225" name="CuadroTexto 224">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A1D48BB-21B2-4938-ABA8-3A0EC24A8113}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5A1D48BB-21B2-4938-ABA8-3A0EC24A8113}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12974,7 +12965,7 @@
         <xdr:cNvPr id="226" name="CuadroTexto 225">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CAA6878-4C64-4449-BCD9-1BE5BA2ED00D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4CAA6878-4C64-4449-BCD9-1BE5BA2ED00D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13029,7 +13020,7 @@
         <xdr:cNvPr id="227" name="CuadroTexto 226">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12A4789C-F9CD-4F4D-98F8-1E53BCE1903F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{12A4789C-F9CD-4F4D-98F8-1E53BCE1903F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13084,7 +13075,7 @@
         <xdr:cNvPr id="228" name="CuadroTexto 227">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D85E5FE1-F58F-43B2-89E1-3D6EE840AF97}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D85E5FE1-F58F-43B2-89E1-3D6EE840AF97}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13139,7 +13130,7 @@
         <xdr:cNvPr id="229" name="CuadroTexto 228">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB4F1CE0-870E-4B23-A256-9473C2A3C47E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FB4F1CE0-870E-4B23-A256-9473C2A3C47E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13194,7 +13185,7 @@
         <xdr:cNvPr id="230" name="CuadroTexto 229">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76DD241A-77B5-4C88-AF96-2D6D537BB352}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76DD241A-77B5-4C88-AF96-2D6D537BB352}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13249,7 +13240,7 @@
         <xdr:cNvPr id="231" name="CuadroTexto 230">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{914F8C4E-943A-4241-B8CF-4C0F7ABCABC5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{914F8C4E-943A-4241-B8CF-4C0F7ABCABC5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13304,7 +13295,7 @@
         <xdr:cNvPr id="232" name="CuadroTexto 231">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A20E49F3-A28E-4B93-9152-BDB47686E1EF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A20E49F3-A28E-4B93-9152-BDB47686E1EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13359,7 +13350,7 @@
         <xdr:cNvPr id="233" name="CuadroTexto 232">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7364DEA7-88EE-4C21-9540-FB3D0DF0F0E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7364DEA7-88EE-4C21-9540-FB3D0DF0F0E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13414,7 +13405,7 @@
         <xdr:cNvPr id="234" name="CuadroTexto 233">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09CE9795-53F4-4D85-A042-AF87545B0E20}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09CE9795-53F4-4D85-A042-AF87545B0E20}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13469,7 +13460,7 @@
         <xdr:cNvPr id="235" name="CuadroTexto 234">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7751875-9B6C-43BD-83A0-C320C38567A3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C7751875-9B6C-43BD-83A0-C320C38567A3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13524,7 +13515,7 @@
         <xdr:cNvPr id="236" name="CuadroTexto 235">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E7B170A-D4C6-4205-BAA0-53138B555C5E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E7B170A-D4C6-4205-BAA0-53138B555C5E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13579,7 +13570,7 @@
         <xdr:cNvPr id="237" name="CuadroTexto 236">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01CB7EE5-81AE-47C3-9C04-1C56C80B728A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{01CB7EE5-81AE-47C3-9C04-1C56C80B728A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13634,7 +13625,7 @@
         <xdr:cNvPr id="238" name="CuadroTexto 237">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D56CE73-7018-4DEA-A03E-24B2172D1594}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0D56CE73-7018-4DEA-A03E-24B2172D1594}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13963,24 +13954,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K503"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.15234375" customWidth="1"/>
-    <col min="2" max="2" width="40.84375" customWidth="1"/>
-    <col min="3" max="3" width="16.3828125" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="2" max="2" width="40.88671875" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="37.84375" customWidth="1"/>
+    <col min="6" max="6" width="37.88671875" customWidth="1"/>
     <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="21.3828125" customWidth="1"/>
-    <col min="9" max="9" width="69.53515625" customWidth="1"/>
-    <col min="10" max="10" width="14.15234375" customWidth="1"/>
-    <col min="11" max="11" width="16.3046875" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" customWidth="1"/>
+    <col min="9" max="9" width="69.5546875" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14012,10 +14003,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -14029,27 +14020,27 @@
         <v>46113</v>
       </c>
       <c r="E2" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="29" t="str">
+      <c r="H2" s="28" t="str">
         <f>IF(G2="","",VLOOKUP(G2,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>74</v>
+      <c r="I2" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="J2" s="15"/>
-      <c r="K2" s="29"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K2" s="28"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>32</v>
@@ -14061,27 +14052,27 @@
         <v>46113</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="29" t="str">
+      <c r="H3" s="28" t="str">
         <f>IF(G3="","",VLOOKUP(G3,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I3" s="22" t="s">
-        <v>75</v>
+      <c r="I3" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="J3" s="15"/>
-      <c r="K3" s="29"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K3" s="28"/>
+    </row>
+    <row r="4" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -14093,27 +14084,27 @@
         <v>46113</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="29" t="str">
+      <c r="H4" s="28" t="str">
         <f>IF(G4="","",VLOOKUP(G4,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I4" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="J4" s="28">
+      <c r="I4" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="27">
         <v>3.9</v>
       </c>
-      <c r="K4" s="29"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K4" s="28"/>
+    </row>
+    <row r="5" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -14127,27 +14118,27 @@
         <v>46113</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="29" t="str">
+      <c r="H5" s="28" t="str">
         <f>IF(G5="","",VLOOKUP(G5,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I5" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="J5" s="28">
+      <c r="I5" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" s="27">
         <v>1.69</v>
       </c>
-      <c r="K5" s="29"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K5" s="28"/>
+    </row>
+    <row r="6" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -14161,27 +14152,27 @@
         <v>46113</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="29" t="str">
+      <c r="H6" s="28" t="str">
         <f>IF(G6="","",VLOOKUP(G6,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO D</v>
       </c>
-      <c r="I6" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="J6" s="28">
+      <c r="I6" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="27">
         <v>57.1</v>
       </c>
-      <c r="K6" s="29"/>
-    </row>
-    <row r="7" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="K6" s="28"/>
+    </row>
+    <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -14195,29 +14186,29 @@
         <v>46113</v>
       </c>
       <c r="E7" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="29" t="str">
+      <c r="H7" s="28" t="str">
         <f>IF(G7="","",VLOOKUP(G7,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I7" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="J7" s="28">
+      <c r="I7" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="27">
         <v>86.86</v>
       </c>
-      <c r="K7" s="29"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K7" s="28"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>35</v>
@@ -14229,31 +14220,31 @@
         <v>46114</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="29" t="str">
+      <c r="H8" s="28" t="str">
         <f>IF(G8="","",VLOOKUP(G8,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO D</v>
       </c>
-      <c r="I8" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="21">
+      <c r="I8" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="20">
         <v>4.3499999999999996</v>
       </c>
-      <c r="K8" s="29">
+      <c r="K8" s="28">
         <v>133503</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>36</v>
@@ -14265,27 +14256,27 @@
         <v>46114</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="29" t="str">
+      <c r="H9" s="28" t="str">
         <f>IF(G9="","",VLOOKUP(G9,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I9" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="28">
+      <c r="I9" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="27">
         <v>167.04</v>
       </c>
-      <c r="K9" s="29"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K9" s="28"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
@@ -14299,25 +14290,25 @@
         <v>46115</v>
       </c>
       <c r="E10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="29" t="str">
+      <c r="H10" s="28" t="str">
         <f>IF(G10="","",VLOOKUP(G10,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I10" s="23" t="s">
-        <v>74</v>
+      <c r="I10" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="J10" s="15"/>
-      <c r="K10" s="29"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K10" s="28"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
@@ -14331,25 +14322,25 @@
         <v>46115</v>
       </c>
       <c r="E11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="29" t="str">
+      <c r="H11" s="28" t="str">
         <f>IF(G11="","",VLOOKUP(G11,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I11" s="23" t="s">
-        <v>74</v>
+      <c r="I11" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="J11" s="15"/>
-      <c r="K11" s="29"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K11" s="28"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -14363,25 +14354,25 @@
         <v>46115</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="29" t="str">
+      <c r="H12" s="28" t="str">
         <f>IF(G12="","",VLOOKUP(G12,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I12" s="23" t="s">
-        <v>74</v>
+      <c r="I12" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="J12" s="15"/>
-      <c r="K12" s="29"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K12" s="28"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -14395,25 +14386,25 @@
         <v>46115</v>
       </c>
       <c r="E13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="29" t="str">
+      <c r="H13" s="28" t="str">
         <f>IF(G13="","",VLOOKUP(G13,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I13" s="22" t="s">
-        <v>74</v>
+      <c r="I13" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="J13" s="15"/>
-      <c r="K13" s="29"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K13" s="28"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -14427,25 +14418,25 @@
         <v>46115</v>
       </c>
       <c r="E14" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="29" t="str">
+      <c r="H14" s="28" t="str">
         <f>IF(G14="","",VLOOKUP(G14,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I14" s="22" t="s">
-        <v>74</v>
+      <c r="I14" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="J14" s="15"/>
-      <c r="K14" s="29"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K14" s="28"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
@@ -14459,22 +14450,22 @@
         <v>46115</v>
       </c>
       <c r="E15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="29"/>
-      <c r="I15" s="22" t="s">
-        <v>82</v>
+      <c r="H15" s="28"/>
+      <c r="I15" s="21" t="s">
+        <v>81</v>
       </c>
       <c r="J15" s="15"/>
-      <c r="K15" s="29"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K15" s="28"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
@@ -14488,25 +14479,25 @@
         <v>46120</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="29" t="str">
+      <c r="H16" s="28" t="str">
         <f>IF(G16="","",VLOOKUP(G16,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I16" s="23" t="s">
-        <v>82</v>
+      <c r="I16" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="J16" s="15"/>
-      <c r="K16" s="29"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K16" s="28"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>30</v>
       </c>
@@ -14520,25 +14511,25 @@
         <v>46120</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="29" t="str">
+      <c r="H17" s="28" t="str">
         <f>IF(G17="","",VLOOKUP(G17,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I17" s="23" t="s">
-        <v>82</v>
+      <c r="I17" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="J17" s="15"/>
-      <c r="K17" s="29"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K17" s="28"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
@@ -14552,25 +14543,25 @@
         <v>46120</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="29" t="str">
+      <c r="H18" s="28" t="str">
         <f>IF(G18="","",VLOOKUP(G18,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I18" s="23" t="s">
-        <v>82</v>
+      <c r="I18" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="J18" s="15"/>
-      <c r="K18" s="29"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K18" s="28"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
@@ -14584,25 +14575,25 @@
         <v>46120</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="29" t="str">
+      <c r="H19" s="28" t="str">
         <f>IF(G19="","",VLOOKUP(G19,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I19" s="23" t="s">
-        <v>82</v>
+      <c r="I19" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="J19" s="15"/>
-      <c r="K19" s="29"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K19" s="28"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>30</v>
       </c>
@@ -14616,25 +14607,25 @@
         <v>46120</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="29" t="str">
+      <c r="H20" s="28" t="str">
         <f>IF(G20="","",VLOOKUP(G20,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I20" s="24" t="s">
-        <v>82</v>
+      <c r="I20" s="23" t="s">
+        <v>81</v>
       </c>
       <c r="J20" s="9"/>
-      <c r="K20" s="29"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K20" s="28"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>30</v>
       </c>
@@ -14648,25 +14639,25 @@
         <v>46120</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H21" s="29" t="str">
+      <c r="H21" s="28" t="str">
         <f>IF(G21="","",VLOOKUP(G21,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I21" s="24" t="s">
-        <v>82</v>
+      <c r="I21" s="23" t="s">
+        <v>81</v>
       </c>
       <c r="J21" s="9"/>
-      <c r="K21" s="29"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K21" s="28"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>30</v>
       </c>
@@ -14680,25 +14671,25 @@
         <v>46120</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="29" t="str">
+      <c r="H22" s="28" t="str">
         <f>IF(G22="","",VLOOKUP(G22,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I22" s="24" t="s">
-        <v>82</v>
+      <c r="I22" s="23" t="s">
+        <v>81</v>
       </c>
       <c r="J22" s="9"/>
-      <c r="K22" s="29"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K22" s="28"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>30</v>
       </c>
@@ -14712,25 +14703,25 @@
         <v>46120</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="29" t="str">
+      <c r="H23" s="28" t="str">
         <f>IF(G23="","",VLOOKUP(G23,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I23" s="23" t="s">
-        <v>82</v>
+      <c r="I23" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="J23" s="15"/>
-      <c r="K23" s="29"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K23" s="28"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>30</v>
       </c>
@@ -14744,27 +14735,27 @@
         <v>46120</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H24" s="29" t="str">
+      <c r="H24" s="28" t="str">
         <f>IF(G24="","",VLOOKUP(G24,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I24" s="23" t="s">
-        <v>82</v>
+      <c r="I24" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="J24" s="15"/>
-      <c r="K24" s="29"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K24" s="28"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>33</v>
@@ -14776,29 +14767,29 @@
         <v>46121</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H25" s="29" t="str">
+      <c r="H25" s="28" t="str">
         <f>IF(G25="","",VLOOKUP(G25,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I25" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="J25" s="20">
+      <c r="I25" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="J25" s="33">
         <v>1913.1</v>
       </c>
-      <c r="K25" s="29"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K25" s="28"/>
+    </row>
+    <row r="26" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>35</v>
@@ -14810,25 +14801,25 @@
         <v>46125</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G26" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="29" t="str">
+      <c r="H26" s="28" t="str">
         <f>IF(G26="","",VLOOKUP(G26,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I26" s="25" t="s">
-        <v>84</v>
+      <c r="I26" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="J26" s="10"/>
-      <c r="K26" s="29"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K26" s="28"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
@@ -14842,25 +14833,25 @@
         <v>46127</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H27" s="29" t="str">
+      <c r="H27" s="28" t="str">
         <f>IF(G27="","",VLOOKUP(G27,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I27" s="23" t="s">
-        <v>74</v>
+      <c r="I27" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="J27" s="15"/>
-      <c r="K27" s="29"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K27" s="28"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>29</v>
       </c>
@@ -14874,25 +14865,25 @@
         <v>46127</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H28" s="29" t="str">
+      <c r="H28" s="28" t="str">
         <f>IF(G28="","",VLOOKUP(G28,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>74</v>
+      <c r="I28" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="J28" s="15"/>
-      <c r="K28" s="29"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K28" s="28"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>29</v>
       </c>
@@ -14906,25 +14897,25 @@
         <v>46127</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H29" s="29" t="str">
+      <c r="H29" s="28" t="str">
         <f>IF(G29="","",VLOOKUP(G29,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I29" s="26" t="s">
-        <v>74</v>
+      <c r="I29" s="25" t="s">
+        <v>73</v>
       </c>
       <c r="J29" s="10"/>
-      <c r="K29" s="29"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K29" s="28"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
@@ -14938,25 +14929,25 @@
         <v>46127</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H30" s="29" t="str">
+      <c r="H30" s="28" t="str">
         <f>IF(G30="","",VLOOKUP(G30,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I30" s="26" t="s">
-        <v>74</v>
+      <c r="I30" s="25" t="s">
+        <v>73</v>
       </c>
       <c r="J30" s="10"/>
-      <c r="K30" s="29"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K30" s="28"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
@@ -14970,27 +14961,27 @@
         <v>46127</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H31" s="29" t="str">
+      <c r="H31" s="28" t="str">
         <f>IF(G31="","",VLOOKUP(G31,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I31" s="26" t="s">
-        <v>74</v>
+      <c r="I31" s="25" t="s">
+        <v>73</v>
       </c>
       <c r="J31" s="10"/>
-      <c r="K31" s="29"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K31" s="28"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>47</v>
@@ -15002,25 +14993,25 @@
         <v>46127</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G32" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G32" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H32" s="29" t="str">
+      <c r="H32" s="28" t="str">
         <f>IF(G32="","",VLOOKUP(G32,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I32" s="27" t="s">
-        <v>75</v>
+      <c r="I32" s="26" t="s">
+        <v>74</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="29"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K32" s="28"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>30</v>
       </c>
@@ -15034,27 +15025,27 @@
         <v>46128</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G33" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H33" s="29" t="str">
+      <c r="H33" s="28" t="str">
         <f>IF(G33="","",VLOOKUP(G33,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I33" s="23" t="s">
-        <v>75</v>
+      <c r="I33" s="22" t="s">
+        <v>74</v>
       </c>
       <c r="J33" s="15"/>
-      <c r="K33" s="29"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K33" s="28"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>49</v>
@@ -15066,27 +15057,27 @@
         <v>46132</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G34" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H34" s="29" t="str">
+      <c r="H34" s="28" t="str">
         <f>IF(G34="","",VLOOKUP(G34,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I34" s="23" t="s">
-        <v>75</v>
+      <c r="I34" s="22" t="s">
+        <v>74</v>
       </c>
       <c r="J34" s="15"/>
-      <c r="K34" s="29"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K34" s="28"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>50</v>
@@ -15098,25 +15089,25 @@
         <v>46132</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G35" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H35" s="29" t="str">
+      <c r="H35" s="28" t="str">
         <f>IF(G35="","",VLOOKUP(G35,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I35" s="23" t="s">
-        <v>75</v>
+      <c r="I35" s="22" t="s">
+        <v>74</v>
       </c>
       <c r="J35" s="15"/>
-      <c r="K35" s="29"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K35" s="28"/>
+    </row>
+    <row r="36" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A36" s="3" t="s">
         <v>30</v>
       </c>
@@ -15130,29 +15121,29 @@
         <v>46133</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G36" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G36" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H36" s="29" t="str">
+      <c r="H36" s="28" t="str">
         <f>IF(G36="","",VLOOKUP(G36,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO D</v>
       </c>
-      <c r="I36" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="J36" s="21">
+      <c r="I36" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="J36" s="20">
         <v>15.03</v>
       </c>
-      <c r="K36" s="29">
+      <c r="K36" s="28">
         <v>91458</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A37" s="3" t="s">
         <v>29</v>
       </c>
@@ -15166,29 +15157,29 @@
         <v>46134</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G37" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H37" s="29" t="str">
+      <c r="H37" s="28" t="str">
         <f>IF(G37="","",VLOOKUP(G37,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO D</v>
       </c>
-      <c r="I37" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="J37" s="21">
+      <c r="I37" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="J37" s="20">
         <v>13</v>
       </c>
-      <c r="K37" s="29">
+      <c r="K37" s="28">
         <v>199055</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>29</v>
       </c>
@@ -15198,35 +15189,35 @@
       <c r="C38" s="5">
         <v>804</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="7">
+        <v>46135</v>
+      </c>
+      <c r="E38" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="F38" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="29" t="str">
+      <c r="H38" s="28" t="str">
         <f>IF(G38="","",VLOOKUP(G38,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO D</v>
       </c>
-      <c r="I38" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="J38" s="21">
+      <c r="I38" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="J38" s="20">
         <v>8.89</v>
       </c>
-      <c r="K38" s="29">
+      <c r="K38" s="28">
         <v>199170</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>33</v>
@@ -15238,27 +15229,27 @@
         <v>46135</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G39" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="G39" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H39" s="29" t="str">
+      <c r="H39" s="28" t="str">
         <f>IF(G39="","",VLOOKUP(G39,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO E</v>
       </c>
-      <c r="I39" s="23" t="s">
-        <v>74</v>
+      <c r="I39" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="J39" s="15"/>
-      <c r="K39" s="29"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K39" s="28"/>
+    </row>
+    <row r="40" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>53</v>
@@ -15270,29 +15261,29 @@
         <v>46135</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G40" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="G40" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H40" s="29" t="str">
+      <c r="H40" s="28" t="str">
         <f>IF(G40="","",VLOOKUP(G40,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO D</v>
       </c>
-      <c r="I40" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J40" s="21">
+      <c r="I40" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="J40" s="20">
         <v>1.89</v>
       </c>
-      <c r="K40" s="29">
+      <c r="K40" s="28">
         <v>138956</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>30</v>
       </c>
@@ -15306,25 +15297,25 @@
         <v>46135</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G41" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G41" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H41" s="29" t="str">
+      <c r="H41" s="28" t="str">
         <f>IF(G41="","",VLOOKUP(G41,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I41" s="23" t="s">
-        <v>82</v>
+      <c r="I41" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="J41" s="15"/>
-      <c r="K41" s="29"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K41" s="28"/>
+    </row>
+    <row r="42" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A42" s="3" t="s">
         <v>30</v>
       </c>
@@ -15338,3184 +15329,3184 @@
         <v>46135</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G42" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G42" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="H42" s="29" t="str">
+      <c r="H42" s="28" t="str">
         <f>IF(G42="","",VLOOKUP(G42,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I42" s="23" t="s">
+      <c r="I42" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A43" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B43" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" s="29">
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+    </row>
+    <row r="43" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+      <c r="A43" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="28">
         <v>27822</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="29">
         <v>46136</v>
       </c>
-      <c r="E43" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F43" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="G43" s="29" t="s">
+      <c r="E43" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G43" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H43" s="29" t="str">
+      <c r="H43" s="28" t="str">
         <f>IF(G43="","",VLOOKUP(G43,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO D</v>
       </c>
-      <c r="I43" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="J43" s="32">
+      <c r="I43" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J43" s="31">
         <v>1.23</v>
       </c>
-      <c r="K43" s="29">
+      <c r="K43" s="28">
         <v>252597</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A44" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" s="29" t="s">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="28">
+        <v>2247070507</v>
+      </c>
+      <c r="D44" s="29">
+        <v>46136</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H44" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="29">
-        <v>2247070507</v>
-      </c>
-      <c r="D44" s="30">
+      <c r="J44" s="31">
+        <v>57.52</v>
+      </c>
+      <c r="K44" s="28">
+        <v>63805</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="28">
+        <v>13503</v>
+      </c>
+      <c r="D45" s="29">
         <v>46136</v>
       </c>
-      <c r="E44" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F44" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="G44" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="H44" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="I44" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="J44" s="32">
-        <v>57.52</v>
-      </c>
-      <c r="K44" s="29">
-        <v>63805</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A45" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B45" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="29">
-        <v>13503</v>
-      </c>
-      <c r="D45" s="30">
-        <v>46136</v>
-      </c>
-      <c r="E45" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F45" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="G45" s="29" t="s">
+      <c r="E45" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="G45" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="H45" s="29" t="str">
+      <c r="H45" s="28" t="str">
         <f>IF(G45="","",VLOOKUP(G45,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO C</v>
       </c>
-      <c r="I45" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A46" s="29" t="s">
+      <c r="I45" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+    </row>
+    <row r="46" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+      <c r="A46" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="28">
         <v>125449</v>
       </c>
-      <c r="D46" s="30">
+      <c r="D46" s="29">
         <v>46136</v>
       </c>
-      <c r="E46" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="G46" s="29" t="s">
+      <c r="E46" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H46" s="29" t="s">
+      <c r="H46" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="I46" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="J46" s="33">
+      <c r="I46" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="J46" s="32">
         <v>92</v>
       </c>
-      <c r="K46" s="29"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A47" s="29" t="s">
+      <c r="K46" s="28"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" s="30">
+      <c r="D47" s="29">
         <v>46140</v>
       </c>
-      <c r="E47" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F47" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G47" s="29" t="s">
+      <c r="E47" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G47" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H47" s="29" t="str">
+      <c r="H47" s="28" t="str">
         <f>IF(G47="","",VLOOKUP(G47,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I47" s="31" t="s">
+      <c r="I47" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="28">
+        <v>31173</v>
+      </c>
+      <c r="D48" s="29">
+        <v>46140</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="G48" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="J48" s="28"/>
+      <c r="K48" s="28"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J47" s="29"/>
-      <c r="K47" s="29"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A48" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B48" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" s="29">
-        <v>31173</v>
-      </c>
-      <c r="D48" s="30">
+      <c r="D49" s="29">
         <v>46140</v>
       </c>
-      <c r="E48" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="F48" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="G48" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="I48" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A49" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B49" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C49" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="D49" s="30">
-        <v>46140</v>
-      </c>
-      <c r="E49" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F49" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G49" s="29" t="s">
+      <c r="E49" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G49" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H49" s="29" t="str">
+      <c r="H49" s="28" t="str">
         <f>IF(G49="","",VLOOKUP(G49,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I49" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A50" s="29" t="s">
+      <c r="I49" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+    </row>
+    <row r="50" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+      <c r="A50" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="28">
         <v>13540</v>
       </c>
-      <c r="D50" s="30">
+      <c r="D50" s="29">
         <v>46141</v>
       </c>
-      <c r="E50" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F50" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="G50" s="29" t="s">
+      <c r="E50" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F50" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="G50" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="H50" s="29" t="str">
+      <c r="H50" s="28" t="str">
         <f>IF(G50="","",VLOOKUP(G50,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I50" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="J50" s="29"/>
-      <c r="K50" s="29"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A51" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B51" s="29" t="s">
+      <c r="I50" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="28">
         <v>860</v>
       </c>
-      <c r="D51" s="30">
+      <c r="D51" s="29">
         <v>46142</v>
       </c>
-      <c r="E51" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F51" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="G51" s="29" t="s">
+      <c r="E51" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="G51" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H51" s="29" t="str">
+      <c r="H51" s="28" t="str">
         <f>IF(G51="","",VLOOKUP(G51,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I51" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="J51" s="29"/>
-      <c r="K51" s="29"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A52" s="29" t="s">
+      <c r="I51" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="29">
+      <c r="B52" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="28">
         <v>2351</v>
       </c>
-      <c r="D52" s="30">
+      <c r="D52" s="29">
         <v>46142</v>
       </c>
-      <c r="E52" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F52" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="G52" s="29" t="s">
+      <c r="E52" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="G52" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="29" t="str">
+      <c r="H52" s="28" t="str">
         <f>IF(G52="","",VLOOKUP(G52,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I52" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A53" s="29" t="s">
+      <c r="I52" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B53" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="C53" s="29">
+      <c r="B53" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="28">
         <v>2347</v>
       </c>
-      <c r="D53" s="30">
+      <c r="D53" s="29">
         <v>46142</v>
       </c>
-      <c r="E53" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F53" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="G53" s="29" t="s">
+      <c r="E53" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="G53" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="H53" s="29" t="str">
+      <c r="H53" s="28" t="str">
         <f>IF(G53="","",VLOOKUP(G53,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I53" s="29" t="s">
+      <c r="I53" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="J53" s="28"/>
+      <c r="K53" s="28"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="J53" s="29"/>
-      <c r="K53" s="29"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A54" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B54" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="C54" s="29">
+      <c r="C54" s="28">
         <v>57</v>
       </c>
-      <c r="D54" s="30">
+      <c r="D54" s="29">
         <v>46142</v>
       </c>
-      <c r="E54" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F54" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="G54" s="29" t="s">
+      <c r="E54" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="G54" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="H54" s="29" t="str">
+      <c r="H54" s="28" t="str">
         <f>IF(G54="","",VLOOKUP(G54,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO B</v>
       </c>
-      <c r="I54" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A55" s="29" t="s">
+      <c r="I54" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="J54" s="28"/>
+      <c r="K54" s="28"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B55" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C55" s="29">
+      <c r="B55" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="28">
         <v>20110664</v>
       </c>
-      <c r="D55" s="30">
+      <c r="D55" s="29">
         <v>46142</v>
       </c>
-      <c r="E55" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F55" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="G55" s="29" t="s">
+      <c r="E55" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="G55" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="H55" s="29" t="str">
+      <c r="H55" s="28" t="str">
         <f>IF(G55="","",VLOOKUP(G55,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v>TIPO A</v>
       </c>
-      <c r="I55" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A56" s="29" t="s">
+      <c r="I55" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B56" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29" t="str">
+      <c r="B56" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28" t="str">
         <f>IF(G56="","",VLOOKUP(G56,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
-      <c r="I56" s="29"/>
-      <c r="J56" s="29"/>
-      <c r="K56" s="29"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29" t="str">
+      <c r="I56" s="28"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="28"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="28"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28" t="str">
         <f>IF(G57="","",VLOOKUP(G57,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
-      <c r="I57" s="29"/>
-      <c r="J57" s="29"/>
-      <c r="K57" s="29"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A58" s="29"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29" t="str">
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="28"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28" t="str">
         <f>IF(G58="","",VLOOKUP(G58,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A59" s="29"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
-      <c r="F59" s="29"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="29" t="str">
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28" t="str">
         <f>IF(G59="","",VLOOKUP(G59,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
-      <c r="I59" s="29"/>
-      <c r="J59" s="29"/>
-      <c r="K59" s="29"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A60" s="29"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29" t="str">
+      <c r="I59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="28"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="28"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28" t="str">
         <f>IF(G60="","",VLOOKUP(G60,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="I60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="28"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H61" t="str">
         <f>IF(G61="","",VLOOKUP(G61,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H62" t="str">
         <f>IF(G62="","",VLOOKUP(G62,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H63" t="str">
         <f>IF(G63="","",VLOOKUP(G63,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H64" t="str">
         <f>IF(G64="","",VLOOKUP(G64,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H65" t="str">
         <f>IF(G65="","",VLOOKUP(G65,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H66" t="str">
         <f>IF(G66="","",VLOOKUP(G66,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H67" t="str">
         <f>IF(G67="","",VLOOKUP(G67,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H68" t="str">
         <f>IF(G68="","",VLOOKUP(G68,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H69" t="str">
         <f>IF(G69="","",VLOOKUP(G69,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H70" t="str">
         <f>IF(G70="","",VLOOKUP(G70,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H71" t="str">
         <f>IF(G71="","",VLOOKUP(G71,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H72" t="str">
         <f>IF(G72="","",VLOOKUP(G72,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H73" t="str">
         <f>IF(G73="","",VLOOKUP(G73,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H74" t="str">
         <f>IF(G74="","",VLOOKUP(G74,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H75" t="str">
         <f>IF(G75="","",VLOOKUP(G75,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H76" t="str">
         <f>IF(G76="","",VLOOKUP(G76,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="77" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H77" t="str">
         <f>IF(G77="","",VLOOKUP(G77,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="78" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H78" t="str">
         <f>IF(G78="","",VLOOKUP(G78,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="79" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H79" t="str">
         <f>IF(G79="","",VLOOKUP(G79,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="80" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H80" t="str">
         <f>IF(G80="","",VLOOKUP(G80,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="81" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H81" t="str">
         <f>IF(G81="","",VLOOKUP(G81,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="82" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H82" t="str">
         <f>IF(G82="","",VLOOKUP(G82,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="83" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H83" t="str">
         <f>IF(G83="","",VLOOKUP(G83,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="84" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H84" t="str">
         <f>IF(G84="","",VLOOKUP(G84,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="85" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H85" t="str">
         <f>IF(G85="","",VLOOKUP(G85,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="86" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H86" t="str">
         <f>IF(G86="","",VLOOKUP(G86,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="87" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H87" t="str">
         <f>IF(G87="","",VLOOKUP(G87,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="88" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H88" t="str">
         <f>IF(G88="","",VLOOKUP(G88,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="89" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H89" t="str">
         <f>IF(G89="","",VLOOKUP(G89,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="90" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H90" t="str">
         <f>IF(G90="","",VLOOKUP(G90,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="91" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H91" t="str">
         <f>IF(G91="","",VLOOKUP(G91,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="92" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H92" t="str">
         <f>IF(G92="","",VLOOKUP(G92,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="93" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H93" t="str">
         <f>IF(G93="","",VLOOKUP(G93,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="94" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H94" t="str">
         <f>IF(G94="","",VLOOKUP(G94,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="95" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H95" t="str">
         <f>IF(G95="","",VLOOKUP(G95,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="96" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H96" t="str">
         <f>IF(G96="","",VLOOKUP(G96,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="97" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H97" t="str">
         <f>IF(G97="","",VLOOKUP(G97,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="98" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H98" t="str">
         <f>IF(G98="","",VLOOKUP(G98,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="99" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H99" t="str">
         <f>IF(G99="","",VLOOKUP(G99,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="100" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H100" t="str">
         <f>IF(G100="","",VLOOKUP(G100,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="101" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H101" t="str">
         <f>IF(G101="","",VLOOKUP(G101,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="102" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H102" t="str">
         <f>IF(G102="","",VLOOKUP(G102,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="103" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H103" t="str">
         <f>IF(G103="","",VLOOKUP(G103,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="104" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H104" t="str">
         <f>IF(G104="","",VLOOKUP(G104,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="105" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="105" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H105" t="str">
         <f>IF(G105="","",VLOOKUP(G105,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="106" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H106" t="str">
         <f>IF(G106="","",VLOOKUP(G106,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="107" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="107" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H107" t="str">
         <f>IF(G107="","",VLOOKUP(G107,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="108" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="108" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H108" t="str">
         <f>IF(G108="","",VLOOKUP(G108,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="109" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="109" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H109" t="str">
         <f>IF(G109="","",VLOOKUP(G109,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="110" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="110" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H110" t="str">
         <f>IF(G110="","",VLOOKUP(G110,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="111" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="111" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H111" t="str">
         <f>IF(G111="","",VLOOKUP(G111,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="112" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="112" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H112" t="str">
         <f>IF(G112="","",VLOOKUP(G112,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="113" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H113" t="str">
         <f>IF(G113="","",VLOOKUP(G113,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="114" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H114" t="str">
         <f>IF(G114="","",VLOOKUP(G114,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="115" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H115" t="str">
         <f>IF(G115="","",VLOOKUP(G115,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="116" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="116" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H116" t="str">
         <f>IF(G116="","",VLOOKUP(G116,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="117" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="117" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H117" t="str">
         <f>IF(G117="","",VLOOKUP(G117,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="118" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="118" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H118" t="str">
         <f>IF(G118="","",VLOOKUP(G118,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="119" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="119" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H119" t="str">
         <f>IF(G119="","",VLOOKUP(G119,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="120" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="120" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H120" t="str">
         <f>IF(G120="","",VLOOKUP(G120,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="121" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="121" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H121" t="str">
         <f>IF(G121="","",VLOOKUP(G121,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="122" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="122" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H122" t="str">
         <f>IF(G122="","",VLOOKUP(G122,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="123" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="123" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H123" t="str">
         <f>IF(G123="","",VLOOKUP(G123,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="124" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="124" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H124" t="str">
         <f>IF(G124="","",VLOOKUP(G124,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="125" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H125" t="str">
         <f>IF(G125="","",VLOOKUP(G125,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="126" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H126" t="str">
         <f>IF(G126="","",VLOOKUP(G126,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="127" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H127" t="str">
         <f>IF(G127="","",VLOOKUP(G127,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="128" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H128" t="str">
         <f>IF(G128="","",VLOOKUP(G128,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="129" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H129" t="str">
         <f>IF(G129="","",VLOOKUP(G129,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="130" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H130" t="str">
         <f>IF(G130="","",VLOOKUP(G130,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="131" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H131" t="str">
         <f>IF(G131="","",VLOOKUP(G131,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="132" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="132" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H132" t="str">
         <f>IF(G132="","",VLOOKUP(G132,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="133" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="133" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H133" t="str">
         <f>IF(G133="","",VLOOKUP(G133,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="134" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="134" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H134" t="str">
         <f>IF(G134="","",VLOOKUP(G134,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="135" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="135" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H135" t="str">
         <f>IF(G135="","",VLOOKUP(G135,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="136" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H136" t="str">
         <f>IF(G136="","",VLOOKUP(G136,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="137" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="137" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H137" t="str">
         <f>IF(G137="","",VLOOKUP(G137,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="138" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="138" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H138" t="str">
         <f>IF(G138="","",VLOOKUP(G138,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="139" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="139" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H139" t="str">
         <f>IF(G139="","",VLOOKUP(G139,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="140" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H140" t="str">
         <f>IF(G140="","",VLOOKUP(G140,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="141" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H141" t="str">
         <f>IF(G141="","",VLOOKUP(G141,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="142" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="142" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H142" t="str">
         <f>IF(G142="","",VLOOKUP(G142,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="143" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="143" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H143" t="str">
         <f>IF(G143="","",VLOOKUP(G143,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="144" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="144" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H144" t="str">
         <f>IF(G144="","",VLOOKUP(G144,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="145" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H145" t="str">
         <f>IF(G145="","",VLOOKUP(G145,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="146" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="146" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H146" t="str">
         <f>IF(G146="","",VLOOKUP(G146,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="147" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="147" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H147" t="str">
         <f>IF(G147="","",VLOOKUP(G147,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="148" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H148" t="str">
         <f>IF(G148="","",VLOOKUP(G148,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="149" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H149" t="str">
         <f>IF(G149="","",VLOOKUP(G149,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="150" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="150" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H150" t="str">
         <f>IF(G150="","",VLOOKUP(G150,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="151" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="151" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H151" t="str">
         <f>IF(G151="","",VLOOKUP(G151,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="152" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="152" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H152" t="str">
         <f>IF(G152="","",VLOOKUP(G152,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="153" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H153" t="str">
         <f>IF(G153="","",VLOOKUP(G153,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="154" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="154" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H154" t="str">
         <f>IF(G154="","",VLOOKUP(G154,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="155" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="155" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H155" t="str">
         <f>IF(G155="","",VLOOKUP(G155,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="156" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H156" t="str">
         <f>IF(G156="","",VLOOKUP(G156,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="157" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H157" t="str">
         <f>IF(G157="","",VLOOKUP(G157,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="158" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="158" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H158" t="str">
         <f>IF(G158="","",VLOOKUP(G158,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="159" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="159" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H159" t="str">
         <f>IF(G159="","",VLOOKUP(G159,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="160" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="160" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H160" t="str">
         <f>IF(G160="","",VLOOKUP(G160,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="161" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H161" t="str">
         <f>IF(G161="","",VLOOKUP(G161,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="162" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="162" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H162" t="str">
         <f>IF(G162="","",VLOOKUP(G162,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="163" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="163" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H163" t="str">
         <f>IF(G163="","",VLOOKUP(G163,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="164" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H164" t="str">
         <f>IF(G164="","",VLOOKUP(G164,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="165" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H165" t="str">
         <f>IF(G165="","",VLOOKUP(G165,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="166" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="166" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H166" t="str">
         <f>IF(G166="","",VLOOKUP(G166,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="167" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="167" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H167" t="str">
         <f>IF(G167="","",VLOOKUP(G167,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="168" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="168" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H168" t="str">
         <f>IF(G168="","",VLOOKUP(G168,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="169" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H169" t="str">
         <f>IF(G169="","",VLOOKUP(G169,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="170" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="170" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H170" t="str">
         <f>IF(G170="","",VLOOKUP(G170,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="171" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="171" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H171" t="str">
         <f>IF(G171="","",VLOOKUP(G171,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="172" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="172" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H172" t="str">
         <f>IF(G172="","",VLOOKUP(G172,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="173" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="173" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H173" t="str">
         <f>IF(G173="","",VLOOKUP(G173,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="174" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="174" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H174" t="str">
         <f>IF(G174="","",VLOOKUP(G174,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="175" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="175" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H175" t="str">
         <f>IF(G175="","",VLOOKUP(G175,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="176" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="176" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H176" t="str">
         <f>IF(G176="","",VLOOKUP(G176,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="177" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H177" t="str">
         <f>IF(G177="","",VLOOKUP(G177,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H178" t="str">
         <f>IF(G178="","",VLOOKUP(G178,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H179" t="str">
         <f>IF(G179="","",VLOOKUP(G179,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H180" t="str">
         <f>IF(G180="","",VLOOKUP(G180,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H181" t="str">
         <f>IF(G181="","",VLOOKUP(G181,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H182" t="str">
         <f>IF(G182="","",VLOOKUP(G182,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H183" t="str">
         <f>IF(G183="","",VLOOKUP(G183,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H184" t="str">
         <f>IF(G184="","",VLOOKUP(G184,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H185" t="str">
         <f>IF(G185="","",VLOOKUP(G185,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H186" t="str">
         <f>IF(G186="","",VLOOKUP(G186,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H187" t="str">
         <f>IF(G187="","",VLOOKUP(G187,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H188" t="str">
         <f>IF(G188="","",VLOOKUP(G188,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H189" t="str">
         <f>IF(G189="","",VLOOKUP(G189,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H190" t="str">
         <f>IF(G190="","",VLOOKUP(G190,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H191" t="str">
         <f>IF(G191="","",VLOOKUP(G191,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H192" t="str">
         <f>IF(G192="","",VLOOKUP(G192,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="193" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="193" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H193" t="str">
         <f>IF(G193="","",VLOOKUP(G193,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="194" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="194" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H194" t="str">
         <f>IF(G194="","",VLOOKUP(G194,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="195" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="195" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H195" t="str">
         <f>IF(G195="","",VLOOKUP(G195,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="196" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="196" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H196" t="str">
         <f>IF(G196="","",VLOOKUP(G196,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="197" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="197" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H197" t="str">
         <f>IF(G197="","",VLOOKUP(G197,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="198" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="198" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H198" t="str">
         <f>IF(G198="","",VLOOKUP(G198,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="199" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="199" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H199" t="str">
         <f>IF(G199="","",VLOOKUP(G199,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="200" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="200" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H200" t="str">
         <f>IF(G200="","",VLOOKUP(G200,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="201" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="201" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H201" t="str">
         <f>IF(G201="","",VLOOKUP(G201,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="202" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="202" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H202" t="str">
         <f>IF(G202="","",VLOOKUP(G202,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="203" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="203" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H203" t="str">
         <f>IF(G203="","",VLOOKUP(G203,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="204" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="204" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H204" t="str">
         <f>IF(G204="","",VLOOKUP(G204,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="205" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="205" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H205" t="str">
         <f>IF(G205="","",VLOOKUP(G205,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="206" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="206" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H206" t="str">
         <f>IF(G206="","",VLOOKUP(G206,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="207" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="207" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H207" t="str">
         <f>IF(G207="","",VLOOKUP(G207,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="208" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="208" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H208" t="str">
         <f>IF(G208="","",VLOOKUP(G208,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="209" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H209" t="str">
         <f>IF(G209="","",VLOOKUP(G209,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="210" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H210" t="str">
         <f>IF(G210="","",VLOOKUP(G210,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="211" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H211" t="str">
         <f>IF(G211="","",VLOOKUP(G211,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="212" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H212" t="str">
         <f>IF(G212="","",VLOOKUP(G212,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="213" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H213" t="str">
         <f>IF(G213="","",VLOOKUP(G213,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="214" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="214" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H214" t="str">
         <f>IF(G214="","",VLOOKUP(G214,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="215" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="215" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H215" t="str">
         <f>IF(G215="","",VLOOKUP(G215,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="216" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="216" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H216" t="str">
         <f>IF(G216="","",VLOOKUP(G216,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="217" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="217" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H217" t="str">
         <f>IF(G217="","",VLOOKUP(G217,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="218" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="218" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H218" t="str">
         <f>IF(G218="","",VLOOKUP(G218,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="219" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="219" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H219" t="str">
         <f>IF(G219="","",VLOOKUP(G219,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="220" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="220" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H220" t="str">
         <f>IF(G220="","",VLOOKUP(G220,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="221" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="221" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H221" t="str">
         <f>IF(G221="","",VLOOKUP(G221,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="222" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="222" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H222" t="str">
         <f>IF(G222="","",VLOOKUP(G222,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="223" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="223" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H223" t="str">
         <f>IF(G223="","",VLOOKUP(G223,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="224" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="224" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H224" t="str">
         <f>IF(G224="","",VLOOKUP(G224,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="225" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="225" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H225" t="str">
         <f>IF(G225="","",VLOOKUP(G225,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="226" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="226" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H226" t="str">
         <f>IF(G226="","",VLOOKUP(G226,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="227" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="227" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H227" t="str">
         <f>IF(G227="","",VLOOKUP(G227,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="228" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="228" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H228" t="str">
         <f>IF(G228="","",VLOOKUP(G228,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="229" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="229" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H229" t="str">
         <f>IF(G229="","",VLOOKUP(G229,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="230" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="230" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H230" t="str">
         <f>IF(G230="","",VLOOKUP(G230,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="231" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="231" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H231" t="str">
         <f>IF(G231="","",VLOOKUP(G231,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="232" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="232" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H232" t="str">
         <f>IF(G232="","",VLOOKUP(G232,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="233" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="233" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H233" t="str">
         <f>IF(G233="","",VLOOKUP(G233,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="234" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="234" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H234" t="str">
         <f>IF(G234="","",VLOOKUP(G234,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="235" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="235" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H235" t="str">
         <f>IF(G235="","",VLOOKUP(G235,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="236" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="236" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H236" t="str">
         <f>IF(G236="","",VLOOKUP(G236,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="237" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="237" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H237" t="str">
         <f>IF(G237="","",VLOOKUP(G237,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="238" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="238" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H238" t="str">
         <f>IF(G238="","",VLOOKUP(G238,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="239" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="239" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H239" t="str">
         <f>IF(G239="","",VLOOKUP(G239,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="240" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="240" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H240" t="str">
         <f>IF(G240="","",VLOOKUP(G240,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="241" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="241" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H241" t="str">
         <f>IF(G241="","",VLOOKUP(G241,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="242" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="242" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H242" t="str">
         <f>IF(G242="","",VLOOKUP(G242,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="243" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="243" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H243" t="str">
         <f>IF(G243="","",VLOOKUP(G243,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="244" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="244" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H244" t="str">
         <f>IF(G244="","",VLOOKUP(G244,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="245" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="245" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H245" t="str">
         <f>IF(G245="","",VLOOKUP(G245,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="246" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="246" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H246" t="str">
         <f>IF(G246="","",VLOOKUP(G246,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="247" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="247" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H247" t="str">
         <f>IF(G247="","",VLOOKUP(G247,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="248" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="248" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H248" t="str">
         <f>IF(G248="","",VLOOKUP(G248,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="249" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="249" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H249" t="str">
         <f>IF(G249="","",VLOOKUP(G249,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="250" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="250" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H250" t="str">
         <f>IF(G250="","",VLOOKUP(G250,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="251" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="251" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H251" t="str">
         <f>IF(G251="","",VLOOKUP(G251,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="252" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="252" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H252" t="str">
         <f>IF(G252="","",VLOOKUP(G252,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="253" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="253" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H253" t="str">
         <f>IF(G253="","",VLOOKUP(G253,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="254" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="254" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H254" t="str">
         <f>IF(G254="","",VLOOKUP(G254,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="255" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="255" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H255" t="str">
         <f>IF(G255="","",VLOOKUP(G255,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="256" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="256" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H256" t="str">
         <f>IF(G256="","",VLOOKUP(G256,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="257" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="257" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H257" t="str">
         <f>IF(G257="","",VLOOKUP(G257,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="258" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="258" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H258" t="str">
         <f>IF(G258="","",VLOOKUP(G258,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="259" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="259" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H259" t="str">
         <f>IF(G259="","",VLOOKUP(G259,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="260" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="260" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H260" t="str">
         <f>IF(G260="","",VLOOKUP(G260,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="261" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="261" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H261" t="str">
         <f>IF(G261="","",VLOOKUP(G261,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="262" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="262" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H262" t="str">
         <f>IF(G262="","",VLOOKUP(G262,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="263" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="263" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H263" t="str">
         <f>IF(G263="","",VLOOKUP(G263,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="264" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="264" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H264" t="str">
         <f>IF(G264="","",VLOOKUP(G264,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="265" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="265" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H265" t="str">
         <f>IF(G265="","",VLOOKUP(G265,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="266" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="266" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H266" t="str">
         <f>IF(G266="","",VLOOKUP(G266,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="267" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="267" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H267" t="str">
         <f>IF(G267="","",VLOOKUP(G267,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="268" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="268" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H268" t="str">
         <f>IF(G268="","",VLOOKUP(G268,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="269" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="269" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H269" t="str">
         <f>IF(G269="","",VLOOKUP(G269,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="270" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="270" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H270" t="str">
         <f>IF(G270="","",VLOOKUP(G270,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="271" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="271" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H271" t="str">
         <f>IF(G271="","",VLOOKUP(G271,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="272" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="272" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H272" t="str">
         <f>IF(G272="","",VLOOKUP(G272,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="273" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="273" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H273" t="str">
         <f>IF(G273="","",VLOOKUP(G273,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="274" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="274" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H274" t="str">
         <f>IF(G274="","",VLOOKUP(G274,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="275" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="275" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H275" t="str">
         <f>IF(G275="","",VLOOKUP(G275,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="276" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="276" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H276" t="str">
         <f>IF(G276="","",VLOOKUP(G276,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="277" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="277" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H277" t="str">
         <f>IF(G277="","",VLOOKUP(G277,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="278" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="278" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H278" t="str">
         <f>IF(G278="","",VLOOKUP(G278,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="279" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="279" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H279" t="str">
         <f>IF(G279="","",VLOOKUP(G279,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="280" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="280" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H280" t="str">
         <f>IF(G280="","",VLOOKUP(G280,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="281" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="281" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H281" t="str">
         <f>IF(G281="","",VLOOKUP(G281,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="282" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="282" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H282" t="str">
         <f>IF(G282="","",VLOOKUP(G282,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="283" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="283" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H283" t="str">
         <f>IF(G283="","",VLOOKUP(G283,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="284" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="284" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H284" t="str">
         <f>IF(G284="","",VLOOKUP(G284,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="285" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="285" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H285" t="str">
         <f>IF(G285="","",VLOOKUP(G285,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="286" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="286" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H286" t="str">
         <f>IF(G286="","",VLOOKUP(G286,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="287" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="287" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H287" t="str">
         <f>IF(G287="","",VLOOKUP(G287,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="288" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="288" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H288" t="str">
         <f>IF(G288="","",VLOOKUP(G288,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="289" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="289" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H289" t="str">
         <f>IF(G289="","",VLOOKUP(G289,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="290" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="290" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H290" t="str">
         <f>IF(G290="","",VLOOKUP(G290,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="291" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="291" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H291" t="str">
         <f>IF(G291="","",VLOOKUP(G291,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="292" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="292" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H292" t="str">
         <f>IF(G292="","",VLOOKUP(G292,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="293" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="293" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H293" t="str">
         <f>IF(G293="","",VLOOKUP(G293,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="294" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="294" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H294" t="str">
         <f>IF(G294="","",VLOOKUP(G294,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="295" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="295" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H295" t="str">
         <f>IF(G295="","",VLOOKUP(G295,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="296" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="296" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H296" t="str">
         <f>IF(G296="","",VLOOKUP(G296,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="297" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="297" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H297" t="str">
         <f>IF(G297="","",VLOOKUP(G297,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="298" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="298" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H298" t="str">
         <f>IF(G298="","",VLOOKUP(G298,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="299" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="299" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H299" t="str">
         <f>IF(G299="","",VLOOKUP(G299,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="300" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="300" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H300" t="str">
         <f>IF(G300="","",VLOOKUP(G300,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="301" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="301" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H301" t="str">
         <f>IF(G301="","",VLOOKUP(G301,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="302" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="302" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H302" t="str">
         <f>IF(G302="","",VLOOKUP(G302,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="303" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="303" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H303" t="str">
         <f>IF(G303="","",VLOOKUP(G303,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="304" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="304" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H304" t="str">
         <f>IF(G304="","",VLOOKUP(G304,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="305" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="305" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H305" t="str">
         <f>IF(G305="","",VLOOKUP(G305,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="306" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="306" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H306" t="str">
         <f>IF(G306="","",VLOOKUP(G306,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="307" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="307" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H307" t="str">
         <f>IF(G307="","",VLOOKUP(G307,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="308" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="308" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H308" t="str">
         <f>IF(G308="","",VLOOKUP(G308,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="309" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="309" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H309" t="str">
         <f>IF(G309="","",VLOOKUP(G309,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="310" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="310" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H310" t="str">
         <f>IF(G310="","",VLOOKUP(G310,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="311" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="311" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H311" t="str">
         <f>IF(G311="","",VLOOKUP(G311,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="312" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="312" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H312" t="str">
         <f>IF(G312="","",VLOOKUP(G312,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="313" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="313" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H313" t="str">
         <f>IF(G313="","",VLOOKUP(G313,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="314" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="314" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H314" t="str">
         <f>IF(G314="","",VLOOKUP(G314,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="315" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="315" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H315" t="str">
         <f>IF(G315="","",VLOOKUP(G315,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="316" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="316" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H316" t="str">
         <f>IF(G316="","",VLOOKUP(G316,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="317" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="317" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H317" t="str">
         <f>IF(G317="","",VLOOKUP(G317,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="318" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="318" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H318" t="str">
         <f>IF(G318="","",VLOOKUP(G318,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="319" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="319" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H319" t="str">
         <f>IF(G319="","",VLOOKUP(G319,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="320" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="320" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H320" t="str">
         <f>IF(G320="","",VLOOKUP(G320,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="321" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="321" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H321" t="str">
         <f>IF(G321="","",VLOOKUP(G321,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="322" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="322" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H322" t="str">
         <f>IF(G322="","",VLOOKUP(G322,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="323" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="323" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H323" t="str">
         <f>IF(G323="","",VLOOKUP(G323,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="324" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="324" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H324" t="str">
         <f>IF(G324="","",VLOOKUP(G324,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="325" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="325" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H325" t="str">
         <f>IF(G325="","",VLOOKUP(G325,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="326" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="326" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H326" t="str">
         <f>IF(G326="","",VLOOKUP(G326,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="327" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="327" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H327" t="str">
         <f>IF(G327="","",VLOOKUP(G327,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="328" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="328" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H328" t="str">
         <f>IF(G328="","",VLOOKUP(G328,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="329" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="329" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H329" t="str">
         <f>IF(G329="","",VLOOKUP(G329,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="330" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="330" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H330" t="str">
         <f>IF(G330="","",VLOOKUP(G330,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="331" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="331" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H331" t="str">
         <f>IF(G331="","",VLOOKUP(G331,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="332" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="332" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H332" t="str">
         <f>IF(G332="","",VLOOKUP(G332,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="333" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="333" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H333" t="str">
         <f>IF(G333="","",VLOOKUP(G333,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="334" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="334" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H334" t="str">
         <f>IF(G334="","",VLOOKUP(G334,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="335" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="335" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H335" t="str">
         <f>IF(G335="","",VLOOKUP(G335,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="336" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="336" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H336" t="str">
         <f>IF(G336="","",VLOOKUP(G336,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="337" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="337" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H337" t="str">
         <f>IF(G337="","",VLOOKUP(G337,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="338" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="338" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H338" t="str">
         <f>IF(G338="","",VLOOKUP(G338,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="339" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="339" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H339" t="str">
         <f>IF(G339="","",VLOOKUP(G339,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="340" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="340" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H340" t="str">
         <f>IF(G340="","",VLOOKUP(G340,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="341" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H341" t="str">
         <f>IF(G341="","",VLOOKUP(G341,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H342" t="str">
         <f>IF(G342="","",VLOOKUP(G342,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="343" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="343" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H343" t="str">
         <f>IF(G343="","",VLOOKUP(G343,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="344" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="344" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H344" t="str">
         <f>IF(G344="","",VLOOKUP(G344,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="345" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="345" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H345" t="str">
         <f>IF(G345="","",VLOOKUP(G345,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="346" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="346" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H346" t="str">
         <f>IF(G346="","",VLOOKUP(G346,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="347" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="347" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H347" t="str">
         <f>IF(G347="","",VLOOKUP(G347,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="348" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="348" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H348" t="str">
         <f>IF(G348="","",VLOOKUP(G348,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="349" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="349" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H349" t="str">
         <f>IF(G349="","",VLOOKUP(G349,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="350" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="350" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H350" t="str">
         <f>IF(G350="","",VLOOKUP(G350,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="351" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="351" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H351" t="str">
         <f>IF(G351="","",VLOOKUP(G351,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="352" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="352" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H352" t="str">
         <f>IF(G352="","",VLOOKUP(G352,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="353" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="353" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H353" t="str">
         <f>IF(G353="","",VLOOKUP(G353,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="354" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="354" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H354" t="str">
         <f>IF(G354="","",VLOOKUP(G354,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="355" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="355" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H355" t="str">
         <f>IF(G355="","",VLOOKUP(G355,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="356" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="356" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H356" t="str">
         <f>IF(G356="","",VLOOKUP(G356,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="357" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="357" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H357" t="str">
         <f>IF(G357="","",VLOOKUP(G357,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="358" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="358" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H358" t="str">
         <f>IF(G358="","",VLOOKUP(G358,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="359" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="359" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H359" t="str">
         <f>IF(G359="","",VLOOKUP(G359,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="360" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="360" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H360" t="str">
         <f>IF(G360="","",VLOOKUP(G360,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="361" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="361" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H361" t="str">
         <f>IF(G361="","",VLOOKUP(G361,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="362" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="362" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H362" t="str">
         <f>IF(G362="","",VLOOKUP(G362,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="363" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="363" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H363" t="str">
         <f>IF(G363="","",VLOOKUP(G363,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="364" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="364" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H364" t="str">
         <f>IF(G364="","",VLOOKUP(G364,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="365" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="365" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H365" t="str">
         <f>IF(G365="","",VLOOKUP(G365,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="366" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="366" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H366" t="str">
         <f>IF(G366="","",VLOOKUP(G366,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="367" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="367" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H367" t="str">
         <f>IF(G367="","",VLOOKUP(G367,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="368" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="368" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H368" t="str">
         <f>IF(G368="","",VLOOKUP(G368,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="369" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="369" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H369" t="str">
         <f>IF(G369="","",VLOOKUP(G369,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="370" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="370" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H370" t="str">
         <f>IF(G370="","",VLOOKUP(G370,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="371" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="371" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H371" t="str">
         <f>IF(G371="","",VLOOKUP(G371,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="372" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="372" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H372" t="str">
         <f>IF(G372="","",VLOOKUP(G372,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="373" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="373" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H373" t="str">
         <f>IF(G373="","",VLOOKUP(G373,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="374" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="374" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H374" t="str">
         <f>IF(G374="","",VLOOKUP(G374,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="375" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="375" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H375" t="str">
         <f>IF(G375="","",VLOOKUP(G375,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="376" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="376" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H376" t="str">
         <f>IF(G376="","",VLOOKUP(G376,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="377" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="377" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H377" t="str">
         <f>IF(G377="","",VLOOKUP(G377,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="378" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="378" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H378" t="str">
         <f>IF(G378="","",VLOOKUP(G378,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="379" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="379" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H379" t="str">
         <f>IF(G379="","",VLOOKUP(G379,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="380" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="380" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H380" t="str">
         <f>IF(G380="","",VLOOKUP(G380,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="381" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="381" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H381" t="str">
         <f>IF(G381="","",VLOOKUP(G381,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="382" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="382" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H382" t="str">
         <f>IF(G382="","",VLOOKUP(G382,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="383" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="383" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H383" t="str">
         <f>IF(G383="","",VLOOKUP(G383,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="384" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="384" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H384" t="str">
         <f>IF(G384="","",VLOOKUP(G384,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="385" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="385" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H385" t="str">
         <f>IF(G385="","",VLOOKUP(G385,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="386" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="386" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H386" t="str">
         <f>IF(G386="","",VLOOKUP(G386,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="387" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="387" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H387" t="str">
         <f>IF(G387="","",VLOOKUP(G387,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="388" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="388" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H388" t="str">
         <f>IF(G388="","",VLOOKUP(G388,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="389" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="389" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H389" t="str">
         <f>IF(G389="","",VLOOKUP(G389,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="390" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="390" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H390" t="str">
         <f>IF(G390="","",VLOOKUP(G390,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="391" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="391" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H391" t="str">
         <f>IF(G391="","",VLOOKUP(G391,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="392" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="392" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H392" t="str">
         <f>IF(G392="","",VLOOKUP(G392,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="393" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="393" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H393" t="str">
         <f>IF(G393="","",VLOOKUP(G393,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="394" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="394" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H394" t="str">
         <f>IF(G394="","",VLOOKUP(G394,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="395" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="395" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H395" t="str">
         <f>IF(G395="","",VLOOKUP(G395,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="396" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="396" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H396" t="str">
         <f>IF(G396="","",VLOOKUP(G396,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="397" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="397" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H397" t="str">
         <f>IF(G397="","",VLOOKUP(G397,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="398" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="398" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H398" t="str">
         <f>IF(G398="","",VLOOKUP(G398,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="399" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="399" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H399" t="str">
         <f>IF(G399="","",VLOOKUP(G399,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="400" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="400" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H400" t="str">
         <f>IF(G400="","",VLOOKUP(G400,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="401" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="401" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H401" t="str">
         <f>IF(G401="","",VLOOKUP(G401,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="402" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="402" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H402" t="str">
         <f>IF(G402="","",VLOOKUP(G402,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="403" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="403" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H403" t="str">
         <f>IF(G403="","",VLOOKUP(G403,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="404" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="404" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H404" t="str">
         <f>IF(G404="","",VLOOKUP(G404,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="405" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="405" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H405" t="str">
         <f>IF(G405="","",VLOOKUP(G405,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="406" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="406" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H406" t="str">
         <f>IF(G406="","",VLOOKUP(G406,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="407" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="407" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H407" t="str">
         <f>IF(G407="","",VLOOKUP(G407,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="408" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="408" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H408" t="str">
         <f>IF(G408="","",VLOOKUP(G408,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="409" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="409" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H409" t="str">
         <f>IF(G409="","",VLOOKUP(G409,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="410" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="410" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H410" t="str">
         <f>IF(G410="","",VLOOKUP(G410,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="411" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="411" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H411" t="str">
         <f>IF(G411="","",VLOOKUP(G411,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="412" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="412" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H412" t="str">
         <f>IF(G412="","",VLOOKUP(G412,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="413" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="413" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H413" t="str">
         <f>IF(G413="","",VLOOKUP(G413,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="414" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="414" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H414" t="str">
         <f>IF(G414="","",VLOOKUP(G414,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="415" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="415" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H415" t="str">
         <f>IF(G415="","",VLOOKUP(G415,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="416" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="416" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H416" t="str">
         <f>IF(G416="","",VLOOKUP(G416,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="417" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="417" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H417" t="str">
         <f>IF(G417="","",VLOOKUP(G417,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="418" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="418" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H418" t="str">
         <f>IF(G418="","",VLOOKUP(G418,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="419" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="419" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H419" t="str">
         <f>IF(G419="","",VLOOKUP(G419,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="420" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="420" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H420" t="str">
         <f>IF(G420="","",VLOOKUP(G420,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="421" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="421" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H421" t="str">
         <f>IF(G421="","",VLOOKUP(G421,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="422" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="422" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H422" t="str">
         <f>IF(G422="","",VLOOKUP(G422,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="423" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="423" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H423" t="str">
         <f>IF(G423="","",VLOOKUP(G423,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="424" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="424" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H424" t="str">
         <f>IF(G424="","",VLOOKUP(G424,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="425" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="425" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H425" t="str">
         <f>IF(G425="","",VLOOKUP(G425,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="426" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="426" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H426" t="str">
         <f>IF(G426="","",VLOOKUP(G426,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="427" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="427" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H427" t="str">
         <f>IF(G427="","",VLOOKUP(G427,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="428" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="428" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H428" t="str">
         <f>IF(G428="","",VLOOKUP(G428,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="429" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="429" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H429" t="str">
         <f>IF(G429="","",VLOOKUP(G429,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="430" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="430" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H430" t="str">
         <f>IF(G430="","",VLOOKUP(G430,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="431" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="431" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H431" t="str">
         <f>IF(G431="","",VLOOKUP(G431,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="432" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="432" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H432" t="str">
         <f>IF(G432="","",VLOOKUP(G432,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="433" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="433" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H433" t="str">
         <f>IF(G433="","",VLOOKUP(G433,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="434" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="434" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H434" t="str">
         <f>IF(G434="","",VLOOKUP(G434,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="435" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="435" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H435" t="str">
         <f>IF(G435="","",VLOOKUP(G435,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="436" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="436" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H436" t="str">
         <f>IF(G436="","",VLOOKUP(G436,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="437" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="437" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H437" t="str">
         <f>IF(G437="","",VLOOKUP(G437,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="438" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="438" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H438" t="str">
         <f>IF(G438="","",VLOOKUP(G438,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="439" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="439" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H439" t="str">
         <f>IF(G439="","",VLOOKUP(G439,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="440" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="440" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H440" t="str">
         <f>IF(G440="","",VLOOKUP(G440,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="441" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="441" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H441" t="str">
         <f>IF(G441="","",VLOOKUP(G441,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="442" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="442" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H442" t="str">
         <f>IF(G442="","",VLOOKUP(G442,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="443" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="443" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H443" t="str">
         <f>IF(G443="","",VLOOKUP(G443,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="444" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="444" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H444" t="str">
         <f>IF(G444="","",VLOOKUP(G444,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="445" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="445" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H445" t="str">
         <f>IF(G445="","",VLOOKUP(G445,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="446" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="446" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H446" t="str">
         <f>IF(G446="","",VLOOKUP(G446,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="447" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="447" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H447" t="str">
         <f>IF(G447="","",VLOOKUP(G447,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="448" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="448" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H448" t="str">
         <f>IF(G448="","",VLOOKUP(G448,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="449" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="449" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H449" t="str">
         <f>IF(G449="","",VLOOKUP(G449,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="450" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="450" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H450" t="str">
         <f>IF(G450="","",VLOOKUP(G450,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="451" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="451" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H451" t="str">
         <f>IF(G451="","",VLOOKUP(G451,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="452" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="452" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H452" t="str">
         <f>IF(G452="","",VLOOKUP(G452,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="453" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="453" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H453" t="str">
         <f>IF(G453="","",VLOOKUP(G453,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="454" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="454" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H454" t="str">
         <f>IF(G454="","",VLOOKUP(G454,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="455" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="455" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H455" t="str">
         <f>IF(G455="","",VLOOKUP(G455,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="456" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="456" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H456" t="str">
         <f>IF(G456="","",VLOOKUP(G456,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="457" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="457" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H457" t="str">
         <f>IF(G457="","",VLOOKUP(G457,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="458" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="458" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H458" t="str">
         <f>IF(G458="","",VLOOKUP(G458,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="459" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="459" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H459" t="str">
         <f>IF(G459="","",VLOOKUP(G459,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="460" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="460" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H460" t="str">
         <f>IF(G460="","",VLOOKUP(G460,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="461" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="461" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H461" t="str">
         <f>IF(G461="","",VLOOKUP(G461,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="462" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="462" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H462" t="str">
         <f>IF(G462="","",VLOOKUP(G462,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="463" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="463" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H463" t="str">
         <f>IF(G463="","",VLOOKUP(G463,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="464" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="464" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H464" t="str">
         <f>IF(G464="","",VLOOKUP(G464,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="465" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="465" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H465" t="str">
         <f>IF(G465="","",VLOOKUP(G465,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="466" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="466" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H466" t="str">
         <f>IF(G466="","",VLOOKUP(G466,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="467" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="467" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H467" t="str">
         <f>IF(G467="","",VLOOKUP(G467,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="468" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="468" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H468" t="str">
         <f>IF(G468="","",VLOOKUP(G468,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="469" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="469" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H469" t="str">
         <f>IF(G469="","",VLOOKUP(G469,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="470" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="470" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H470" t="str">
         <f>IF(G470="","",VLOOKUP(G470,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="471" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="471" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H471" t="str">
         <f>IF(G471="","",VLOOKUP(G471,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="472" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="472" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H472" t="str">
         <f>IF(G472="","",VLOOKUP(G472,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="473" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="473" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H473" t="str">
         <f>IF(G473="","",VLOOKUP(G473,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="474" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="474" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H474" t="str">
         <f>IF(G474="","",VLOOKUP(G474,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="475" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="475" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H475" t="str">
         <f>IF(G475="","",VLOOKUP(G475,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="476" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="476" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H476" t="str">
         <f>IF(G476="","",VLOOKUP(G476,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="477" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="477" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H477" t="str">
         <f>IF(G477="","",VLOOKUP(G477,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="478" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="478" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H478" t="str">
         <f>IF(G478="","",VLOOKUP(G478,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="479" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="479" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H479" t="str">
         <f>IF(G479="","",VLOOKUP(G479,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="480" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="480" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H480" t="str">
         <f>IF(G480="","",VLOOKUP(G480,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="481" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="481" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H481" t="str">
         <f>IF(G481="","",VLOOKUP(G481,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="482" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="482" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H482" t="str">
         <f>IF(G482="","",VLOOKUP(G482,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="483" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="483" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H483" t="str">
         <f>IF(G483="","",VLOOKUP(G483,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="484" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="484" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H484" t="str">
         <f>IF(G484="","",VLOOKUP(G484,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="485" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="485" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H485" t="str">
         <f>IF(G485="","",VLOOKUP(G485,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="486" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="486" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H486" t="str">
         <f>IF(G486="","",VLOOKUP(G486,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="487" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="487" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H487" t="str">
         <f>IF(G487="","",VLOOKUP(G487,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="488" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="488" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H488" t="str">
         <f>IF(G488="","",VLOOKUP(G488,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="489" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="489" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H489" t="str">
         <f>IF(G489="","",VLOOKUP(G489,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="490" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="490" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H490" t="str">
         <f>IF(G490="","",VLOOKUP(G490,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="491" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="491" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H491" t="str">
         <f>IF(G491="","",VLOOKUP(G491,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="492" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="492" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H492" t="str">
         <f>IF(G492="","",VLOOKUP(G492,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="493" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="493" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H493" t="str">
         <f>IF(G493="","",VLOOKUP(G493,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="494" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="494" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H494" t="str">
         <f>IF(G494="","",VLOOKUP(G494,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="495" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="495" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H495" t="str">
         <f>IF(G495="","",VLOOKUP(G495,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="496" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="496" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H496" t="str">
         <f>IF(G496="","",VLOOKUP(G496,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="497" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="497" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H497" t="str">
         <f>IF(G497="","",VLOOKUP(G497,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="498" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="498" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H498" t="str">
         <f>IF(G498="","",VLOOKUP(G498,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="499" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="499" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H499" t="str">
         <f>IF(G499="","",VLOOKUP(G499,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="500" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="500" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H500" t="str">
         <f>IF(G500="","",VLOOKUP(G500,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="501" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="501" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H501" t="str">
         <f>IF(G501="","",VLOOKUP(G501,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="502" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="502" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H502" t="str">
         <f>IF(G502="","",VLOOKUP(G502,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="503" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="503" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H503" t="str">
         <f>IF(G503="","",VLOOKUP(G503,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
@@ -18531,7 +18522,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B33:C42 B17:C17 C23 C12" xr:uid="{DD62D525-11D8-49CA-867B-F675E4468EAC}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B33:C42 B17:C17 C23 C12">
       <formula1>22</formula1>
     </dataValidation>
   </dataValidations>
@@ -18541,7 +18532,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1">
           <x14:formula1>
             <xm:f>REFERENCIA!$A$1:$A$14</xm:f>
           </x14:formula1>
@@ -18554,20 +18545,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B22A23F-25BB-4234-8337-3463AF2CD81E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -18575,7 +18566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -18583,7 +18574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -18591,7 +18582,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -18599,7 +18590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -18607,7 +18598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -18615,7 +18606,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -18623,7 +18614,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -18631,7 +18622,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -18639,7 +18630,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -18647,7 +18638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -18655,7 +18646,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -18663,7 +18654,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" ht="14.55" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -18671,7 +18662,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>

--- a/cuadros/ABRIL/ABRIL_BOSQUE_NAGUANAGUA_TUCACAS.xlsx
+++ b/cuadros/ABRIL/ABRIL_BOSQUE_NAGUANAGUA_TUCACAS.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\FISCALIZACION\cuadros\ABRIL\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0BAFB3-2A61-414A-AE39-9FA8AD929205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="3" r:id="rId2"/>
     <sheet name="REFERENCIA" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -360,7 +366,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -406,7 +412,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -434,12 +440,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -471,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -569,9 +569,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -645,7 +642,7 @@
         <xdr:cNvPr id="2" name="CuadroTexto 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2CF7994D-742B-48FD-B7B5-8CD0D7157A89}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF7994D-742B-48FD-B7B5-8CD0D7157A89}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -700,7 +697,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{74A68D58-0208-44DC-9A5B-0A7362DCF02F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74A68D58-0208-44DC-9A5B-0A7362DCF02F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -755,7 +752,7 @@
         <xdr:cNvPr id="4" name="CuadroTexto 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D78C8955-286A-4032-BBD8-1E3AD59801DC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D78C8955-286A-4032-BBD8-1E3AD59801DC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -810,7 +807,7 @@
         <xdr:cNvPr id="5" name="CuadroTexto 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E02734A2-DBB5-429C-84FA-A8881F65B24E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E02734A2-DBB5-429C-84FA-A8881F65B24E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -865,7 +862,7 @@
         <xdr:cNvPr id="6" name="CuadroTexto 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B282FD55-A400-4F94-BD32-E707B41920E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B282FD55-A400-4F94-BD32-E707B41920E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -920,7 +917,7 @@
         <xdr:cNvPr id="7" name="CuadroTexto 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EB6DCE26-2AE6-4CD0-B3C8-F254B6F4BF9F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB6DCE26-2AE6-4CD0-B3C8-F254B6F4BF9F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -975,7 +972,7 @@
         <xdr:cNvPr id="8" name="CuadroTexto 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{946E5772-59EE-4ED0-B781-DDB81A05A2B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{946E5772-59EE-4ED0-B781-DDB81A05A2B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1030,7 +1027,7 @@
         <xdr:cNvPr id="9" name="CuadroTexto 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{319F6DFD-8AA2-4306-AD21-1F969B3631FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{319F6DFD-8AA2-4306-AD21-1F969B3631FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1085,7 +1082,7 @@
         <xdr:cNvPr id="10" name="CuadroTexto 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{92FDC34C-AB70-4614-8FFF-4078C9774050}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92FDC34C-AB70-4614-8FFF-4078C9774050}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1140,7 +1137,7 @@
         <xdr:cNvPr id="11" name="CuadroTexto 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A692607E-FF5D-4CFD-B4BF-35FE01F89C0F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A692607E-FF5D-4CFD-B4BF-35FE01F89C0F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1195,7 +1192,7 @@
         <xdr:cNvPr id="12" name="CuadroTexto 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CB3B7DEC-1ABA-47DF-B794-BF259B68EFE0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB3B7DEC-1ABA-47DF-B794-BF259B68EFE0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1250,7 +1247,7 @@
         <xdr:cNvPr id="13" name="CuadroTexto 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AA931F8B-C805-425A-BE48-C5F59B744A64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA931F8B-C805-425A-BE48-C5F59B744A64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1305,7 +1302,7 @@
         <xdr:cNvPr id="14" name="CuadroTexto 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C66CAB09-DAF3-4A2C-9E93-076CCB98C0C7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C66CAB09-DAF3-4A2C-9E93-076CCB98C0C7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1360,7 +1357,7 @@
         <xdr:cNvPr id="15" name="CuadroTexto 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9472583B-924A-4841-A8B4-1DCBE9FE9AE7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9472583B-924A-4841-A8B4-1DCBE9FE9AE7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1415,7 +1412,7 @@
         <xdr:cNvPr id="16" name="CuadroTexto 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C50F45A-C171-47A0-BA67-28EE21BFEB49}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C50F45A-C171-47A0-BA67-28EE21BFEB49}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1470,7 +1467,7 @@
         <xdr:cNvPr id="17" name="CuadroTexto 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ECE6D0E3-4F6A-4F80-9B0F-70F8AE57D458}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECE6D0E3-4F6A-4F80-9B0F-70F8AE57D458}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1525,7 +1522,7 @@
         <xdr:cNvPr id="18" name="CuadroTexto 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9A742941-6488-413B-92A1-C6F0F0D5CCBC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A742941-6488-413B-92A1-C6F0F0D5CCBC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1580,7 +1577,7 @@
         <xdr:cNvPr id="19" name="CuadroTexto 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C77A68E8-BD46-40A2-9A45-A660F791A789}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C77A68E8-BD46-40A2-9A45-A660F791A789}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1635,7 +1632,7 @@
         <xdr:cNvPr id="20" name="CuadroTexto 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{079B9A57-60DE-4B30-8C63-00AE002452B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{079B9A57-60DE-4B30-8C63-00AE002452B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1690,7 +1687,7 @@
         <xdr:cNvPr id="21" name="CuadroTexto 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8A95FFDC-7DAA-4FD3-B2C1-A2A79ED11255}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A95FFDC-7DAA-4FD3-B2C1-A2A79ED11255}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1745,7 +1742,7 @@
         <xdr:cNvPr id="22" name="CuadroTexto 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5172AA03-AB32-45F7-BA1D-91EAB8EEC9EE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5172AA03-AB32-45F7-BA1D-91EAB8EEC9EE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1800,7 +1797,7 @@
         <xdr:cNvPr id="23" name="CuadroTexto 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F2EB0AF3-4F33-43D7-9DD6-D8B8F7AE28E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2EB0AF3-4F33-43D7-9DD6-D8B8F7AE28E0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1855,7 +1852,7 @@
         <xdr:cNvPr id="24" name="CuadroTexto 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{550E8AF9-8E12-4B09-BB88-3D25B55D8918}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{550E8AF9-8E12-4B09-BB88-3D25B55D8918}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1910,7 +1907,7 @@
         <xdr:cNvPr id="25" name="CuadroTexto 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F76666FE-3951-4A31-8690-35AE31698F34}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F76666FE-3951-4A31-8690-35AE31698F34}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1965,7 +1962,7 @@
         <xdr:cNvPr id="26" name="CuadroTexto 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8C9513C8-D382-4AE3-B196-AAF1DD3ECD94}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C9513C8-D382-4AE3-B196-AAF1DD3ECD94}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2020,7 +2017,7 @@
         <xdr:cNvPr id="27" name="CuadroTexto 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7B366EA3-A855-4C2B-89E5-DD13EE486125}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B366EA3-A855-4C2B-89E5-DD13EE486125}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2075,7 +2072,7 @@
         <xdr:cNvPr id="28" name="CuadroTexto 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{28384F2D-13D1-4D87-80AC-449A2D69AF85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28384F2D-13D1-4D87-80AC-449A2D69AF85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2130,7 +2127,7 @@
         <xdr:cNvPr id="29" name="CuadroTexto 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D75F71D9-EF60-47DC-9C5F-9D1BB2D31B6A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D75F71D9-EF60-47DC-9C5F-9D1BB2D31B6A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2185,7 +2182,7 @@
         <xdr:cNvPr id="30" name="CuadroTexto 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C0A3C5DC-5C4C-4344-A76A-FCD8B807D148}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0A3C5DC-5C4C-4344-A76A-FCD8B807D148}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2240,7 +2237,7 @@
         <xdr:cNvPr id="31" name="CuadroTexto 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8181737E-6237-41AD-B840-1A915CC8673C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8181737E-6237-41AD-B840-1A915CC8673C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2295,7 +2292,7 @@
         <xdr:cNvPr id="32" name="CuadroTexto 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CC194ADA-EF53-4FD0-8D2D-908BB0B65937}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC194ADA-EF53-4FD0-8D2D-908BB0B65937}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2350,7 +2347,7 @@
         <xdr:cNvPr id="33" name="CuadroTexto 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{360F2ED5-FD7F-438F-9DA1-D7CE86FD4351}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{360F2ED5-FD7F-438F-9DA1-D7CE86FD4351}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2405,7 +2402,7 @@
         <xdr:cNvPr id="34" name="CuadroTexto 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{98852F2C-94A9-4D40-BF8A-696C85F76BD0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98852F2C-94A9-4D40-BF8A-696C85F76BD0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2460,7 +2457,7 @@
         <xdr:cNvPr id="35" name="CuadroTexto 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{235DDB15-3729-4049-902A-C14B06D56C17}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{235DDB15-3729-4049-902A-C14B06D56C17}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2515,7 +2512,7 @@
         <xdr:cNvPr id="36" name="CuadroTexto 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0503350D-1299-4D1F-AF47-558215D36FFD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0503350D-1299-4D1F-AF47-558215D36FFD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2570,7 +2567,7 @@
         <xdr:cNvPr id="37" name="CuadroTexto 36">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{04C62AD9-1F8B-4453-8D09-D0056E05FB8A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04C62AD9-1F8B-4453-8D09-D0056E05FB8A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2625,7 +2622,7 @@
         <xdr:cNvPr id="38" name="CuadroTexto 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9159DE10-3E5C-419F-BAA3-FF32D8413265}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9159DE10-3E5C-419F-BAA3-FF32D8413265}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2680,7 +2677,7 @@
         <xdr:cNvPr id="39" name="CuadroTexto 38">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07369E6A-8AAB-4A1B-B452-2270A0377B7C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07369E6A-8AAB-4A1B-B452-2270A0377B7C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2735,7 +2732,7 @@
         <xdr:cNvPr id="40" name="CuadroTexto 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CA630C4E-F4B2-45AC-AFF1-F2E291807CDA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA630C4E-F4B2-45AC-AFF1-F2E291807CDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2790,7 +2787,7 @@
         <xdr:cNvPr id="41" name="CuadroTexto 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A7599229-D1EA-4074-90DF-4E7FA701C3F5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7599229-D1EA-4074-90DF-4E7FA701C3F5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2845,7 +2842,7 @@
         <xdr:cNvPr id="42" name="CuadroTexto 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F98FF8AF-CD99-43F0-A0FB-7B00781C9178}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F98FF8AF-CD99-43F0-A0FB-7B00781C9178}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2900,7 +2897,7 @@
         <xdr:cNvPr id="43" name="CuadroTexto 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3D1A8947-711E-4387-ADEE-C57AAB3B1C33}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D1A8947-711E-4387-ADEE-C57AAB3B1C33}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2955,7 +2952,7 @@
         <xdr:cNvPr id="44" name="CuadroTexto 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5628EE06-E86C-49B5-9666-D0E336CD9FAE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5628EE06-E86C-49B5-9666-D0E336CD9FAE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3010,7 +3007,7 @@
         <xdr:cNvPr id="45" name="CuadroTexto 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1922209F-CB4A-455B-800B-021E2A7211C2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1922209F-CB4A-455B-800B-021E2A7211C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3065,7 +3062,7 @@
         <xdr:cNvPr id="46" name="CuadroTexto 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4E066125-2A3E-4381-8C3B-7A6F98AB34B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E066125-2A3E-4381-8C3B-7A6F98AB34B1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3120,7 +3117,7 @@
         <xdr:cNvPr id="47" name="CuadroTexto 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A397DE42-D4C0-4B94-91E6-6E375170A71D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A397DE42-D4C0-4B94-91E6-6E375170A71D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3175,7 +3172,7 @@
         <xdr:cNvPr id="48" name="CuadroTexto 47">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E01FAFB9-3D22-4F88-8B4E-2F421EECCC77}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E01FAFB9-3D22-4F88-8B4E-2F421EECCC77}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3230,7 +3227,7 @@
         <xdr:cNvPr id="49" name="CuadroTexto 48">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A1951815-32AD-4B89-BEDA-7520D8F1DFEB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1951815-32AD-4B89-BEDA-7520D8F1DFEB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3285,7 +3282,7 @@
         <xdr:cNvPr id="50" name="CuadroTexto 49">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CD8E1159-271A-4D02-AE97-4D75882EFCB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD8E1159-271A-4D02-AE97-4D75882EFCB6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3340,7 +3337,7 @@
         <xdr:cNvPr id="51" name="CuadroTexto 50">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{53A18A23-701D-400B-B012-EFA93EBBCAD0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53A18A23-701D-400B-B012-EFA93EBBCAD0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3395,7 +3392,7 @@
         <xdr:cNvPr id="52" name="CuadroTexto 51">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FB61393-DF39-4749-8214-EA09AABC3605}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FB61393-DF39-4749-8214-EA09AABC3605}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3450,7 +3447,7 @@
         <xdr:cNvPr id="53" name="CuadroTexto 52">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C3522D01-824C-4695-9DF1-F0A5B55E6C57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3522D01-824C-4695-9DF1-F0A5B55E6C57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3505,7 +3502,7 @@
         <xdr:cNvPr id="54" name="CuadroTexto 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4214B2DA-AC82-49CA-8E61-AB9018A557FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4214B2DA-AC82-49CA-8E61-AB9018A557FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3560,7 +3557,7 @@
         <xdr:cNvPr id="55" name="CuadroTexto 54">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DF515DC3-CA73-47AA-A1F0-C585C5F64DBA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF515DC3-CA73-47AA-A1F0-C585C5F64DBA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3615,7 +3612,7 @@
         <xdr:cNvPr id="56" name="CuadroTexto 55">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{49D08C5C-D84D-4EA3-9621-C8E48C6C9855}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49D08C5C-D84D-4EA3-9621-C8E48C6C9855}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3670,7 +3667,7 @@
         <xdr:cNvPr id="57" name="CuadroTexto 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{40A008F3-40CC-46E2-8DB4-4DFD278D36B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40A008F3-40CC-46E2-8DB4-4DFD278D36B5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3725,7 +3722,7 @@
         <xdr:cNvPr id="58" name="CuadroTexto 57">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED92FBC4-F061-4DF2-8653-2128DE278B77}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED92FBC4-F061-4DF2-8653-2128DE278B77}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3780,7 +3777,7 @@
         <xdr:cNvPr id="59" name="CuadroTexto 58">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A7DE0A94-4935-446F-8BB4-B789C2188B98}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7DE0A94-4935-446F-8BB4-B789C2188B98}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3835,7 +3832,7 @@
         <xdr:cNvPr id="60" name="CuadroTexto 59">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BF5EA534-64E6-497F-B310-F200BEF6E0CF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF5EA534-64E6-497F-B310-F200BEF6E0CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3890,7 +3887,7 @@
         <xdr:cNvPr id="61" name="CuadroTexto 60">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2F734C56-CB0D-4C1B-8A04-734089772648}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F734C56-CB0D-4C1B-8A04-734089772648}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3945,7 +3942,7 @@
         <xdr:cNvPr id="62" name="CuadroTexto 61">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9710101E-C6E4-4643-87D8-9AA5ECB9E8DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9710101E-C6E4-4643-87D8-9AA5ECB9E8DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4000,7 +3997,7 @@
         <xdr:cNvPr id="63" name="CuadroTexto 62">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{62DDE8F2-D913-4E62-90BD-A8A0AB4CA483}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62DDE8F2-D913-4E62-90BD-A8A0AB4CA483}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4055,7 +4052,7 @@
         <xdr:cNvPr id="64" name="CuadroTexto 63">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DDB93E1F-EC2D-46DC-9B21-29C923DC7CF9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDB93E1F-EC2D-46DC-9B21-29C923DC7CF9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4110,7 +4107,7 @@
         <xdr:cNvPr id="65" name="CuadroTexto 64">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{79A9AD84-BE33-4B2C-AFC8-47A59E733AD2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79A9AD84-BE33-4B2C-AFC8-47A59E733AD2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4165,7 +4162,7 @@
         <xdr:cNvPr id="66" name="CuadroTexto 65">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FF85121F-EE53-437B-848D-A81400E38741}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF85121F-EE53-437B-848D-A81400E38741}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4220,7 +4217,7 @@
         <xdr:cNvPr id="67" name="CuadroTexto 66">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{12502C8C-3921-44FA-A3D2-44D45D06992D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12502C8C-3921-44FA-A3D2-44D45D06992D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4275,7 +4272,7 @@
         <xdr:cNvPr id="68" name="CuadroTexto 67">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5CB4EDBE-85AF-4F3C-AC39-BF53ED98D242}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CB4EDBE-85AF-4F3C-AC39-BF53ED98D242}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4330,7 +4327,7 @@
         <xdr:cNvPr id="69" name="CuadroTexto 68">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3CB00B36-E5B9-48D2-B2B9-E8F10256BB71}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CB00B36-E5B9-48D2-B2B9-E8F10256BB71}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4385,7 +4382,7 @@
         <xdr:cNvPr id="70" name="CuadroTexto 69">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4E44F5BD-9E02-4EE0-BEF1-E7DBF143C3A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E44F5BD-9E02-4EE0-BEF1-E7DBF143C3A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4440,7 +4437,7 @@
         <xdr:cNvPr id="71" name="CuadroTexto 70">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6686B2E8-44CB-4FBD-A7E1-250118A96F85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6686B2E8-44CB-4FBD-A7E1-250118A96F85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4495,7 +4492,7 @@
         <xdr:cNvPr id="72" name="CuadroTexto 71">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{16EFCBB6-2C19-43FA-8872-F7A40F59CFF4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16EFCBB6-2C19-43FA-8872-F7A40F59CFF4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4550,7 +4547,7 @@
         <xdr:cNvPr id="73" name="CuadroTexto 72">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{54524EFF-081E-455D-91B0-1D5F1B89129E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54524EFF-081E-455D-91B0-1D5F1B89129E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4605,7 +4602,7 @@
         <xdr:cNvPr id="74" name="CuadroTexto 73">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C4167024-169A-43CD-8D32-972924154C91}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4167024-169A-43CD-8D32-972924154C91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4660,7 +4657,7 @@
         <xdr:cNvPr id="75" name="CuadroTexto 74">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{15F4D81E-E7C8-426B-BF69-F8BD10CD037E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15F4D81E-E7C8-426B-BF69-F8BD10CD037E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4715,7 +4712,7 @@
         <xdr:cNvPr id="76" name="CuadroTexto 75">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{603DBD74-7730-4E6A-99F0-497884C528C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{603DBD74-7730-4E6A-99F0-497884C528C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4770,7 +4767,7 @@
         <xdr:cNvPr id="77" name="CuadroTexto 76">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1FBDC636-78FB-44E4-9EC0-19F8AC372646}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FBDC636-78FB-44E4-9EC0-19F8AC372646}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4825,7 +4822,7 @@
         <xdr:cNvPr id="78" name="CuadroTexto 77">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F7A9EDCC-3AD2-4271-B043-22D3EAC3D878}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7A9EDCC-3AD2-4271-B043-22D3EAC3D878}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4880,7 +4877,7 @@
         <xdr:cNvPr id="79" name="CuadroTexto 78">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A05508AC-4F90-4DB5-821F-D72E86108E50}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A05508AC-4F90-4DB5-821F-D72E86108E50}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4935,7 +4932,7 @@
         <xdr:cNvPr id="80" name="CuadroTexto 79">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{97A1FC03-9278-457F-AFE3-4C92DB15B728}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97A1FC03-9278-457F-AFE3-4C92DB15B728}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4990,7 +4987,7 @@
         <xdr:cNvPr id="81" name="CuadroTexto 80">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F17BF97A-A652-4C5C-80BC-467E8FAF7F62}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F17BF97A-A652-4C5C-80BC-467E8FAF7F62}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5045,7 +5042,7 @@
         <xdr:cNvPr id="82" name="CuadroTexto 81">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{811ABB08-2508-482C-8EB3-0FB9C0B259CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{811ABB08-2508-482C-8EB3-0FB9C0B259CA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5100,7 +5097,7 @@
         <xdr:cNvPr id="83" name="CuadroTexto 82">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E5FD72CD-9321-4ABA-9F25-CFCF27FD5F79}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5FD72CD-9321-4ABA-9F25-CFCF27FD5F79}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5155,7 +5152,7 @@
         <xdr:cNvPr id="84" name="CuadroTexto 83">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EE5F92B2-9E1D-4900-8DE6-FA831732390C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE5F92B2-9E1D-4900-8DE6-FA831732390C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5210,7 +5207,7 @@
         <xdr:cNvPr id="85" name="CuadroTexto 84">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76EBF101-5224-428F-B958-FC3C60442A38}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76EBF101-5224-428F-B958-FC3C60442A38}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5265,7 +5262,7 @@
         <xdr:cNvPr id="86" name="CuadroTexto 85">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E12363C7-F598-45F2-AA8D-59E0905FEFFE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E12363C7-F598-45F2-AA8D-59E0905FEFFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5320,7 +5317,7 @@
         <xdr:cNvPr id="87" name="CuadroTexto 86">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3DBF8150-9C5A-4740-9841-2E4584E0F99A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DBF8150-9C5A-4740-9841-2E4584E0F99A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5375,7 +5372,7 @@
         <xdr:cNvPr id="88" name="CuadroTexto 87">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{13E0F143-BA32-4656-BA82-FA5F7612715A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13E0F143-BA32-4656-BA82-FA5F7612715A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5430,7 +5427,7 @@
         <xdr:cNvPr id="89" name="CuadroTexto 88">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7219173A-543F-4ECE-A402-6CB2FAE4AAA1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7219173A-543F-4ECE-A402-6CB2FAE4AAA1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5485,7 +5482,7 @@
         <xdr:cNvPr id="90" name="CuadroTexto 89">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3DB1A3A9-C613-46FC-B996-735F07E5DE4E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DB1A3A9-C613-46FC-B996-735F07E5DE4E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5540,7 +5537,7 @@
         <xdr:cNvPr id="91" name="CuadroTexto 90">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{523FBB43-1A07-4ADE-BB1A-FCEBFA6B8369}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{523FBB43-1A07-4ADE-BB1A-FCEBFA6B8369}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5595,7 +5592,7 @@
         <xdr:cNvPr id="92" name="CuadroTexto 91">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EFF80933-94D4-4CA0-884D-40423998C4C9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF80933-94D4-4CA0-884D-40423998C4C9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5650,7 +5647,7 @@
         <xdr:cNvPr id="93" name="CuadroTexto 92">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{901506A4-A90D-4200-89BB-AD779D37BFDF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{901506A4-A90D-4200-89BB-AD779D37BFDF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5705,7 +5702,7 @@
         <xdr:cNvPr id="94" name="CuadroTexto 93">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A4E8208A-58BE-48C9-82E4-B2638ACAA54C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4E8208A-58BE-48C9-82E4-B2638ACAA54C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5760,7 +5757,7 @@
         <xdr:cNvPr id="95" name="CuadroTexto 94">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{58AACC08-670B-49AF-9907-9988995B5BF4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58AACC08-670B-49AF-9907-9988995B5BF4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5815,7 +5812,7 @@
         <xdr:cNvPr id="96" name="CuadroTexto 95">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9E167A9D-DF3B-4206-9E4C-EAC0EDB2E151}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E167A9D-DF3B-4206-9E4C-EAC0EDB2E151}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5870,7 +5867,7 @@
         <xdr:cNvPr id="97" name="CuadroTexto 96">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{651BE143-7217-4BE5-9A5A-64C47F111387}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{651BE143-7217-4BE5-9A5A-64C47F111387}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5925,7 +5922,7 @@
         <xdr:cNvPr id="98" name="CuadroTexto 97">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6277F7C7-44BA-48D7-A550-DC61E0673A9C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6277F7C7-44BA-48D7-A550-DC61E0673A9C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5980,7 +5977,7 @@
         <xdr:cNvPr id="99" name="CuadroTexto 98">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E267271C-4E05-4B7F-9958-C487030C853E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E267271C-4E05-4B7F-9958-C487030C853E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6035,7 +6032,7 @@
         <xdr:cNvPr id="100" name="CuadroTexto 99">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{649883DD-04CE-47D8-AC55-609550B1B439}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{649883DD-04CE-47D8-AC55-609550B1B439}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6090,7 +6087,7 @@
         <xdr:cNvPr id="101" name="CuadroTexto 100">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{06306A5D-BC59-4294-B11D-489BA4119393}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06306A5D-BC59-4294-B11D-489BA4119393}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6145,7 +6142,7 @@
         <xdr:cNvPr id="102" name="CuadroTexto 101">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5AC28CB5-32C8-4D67-B7B0-735CB189D222}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AC28CB5-32C8-4D67-B7B0-735CB189D222}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6200,7 +6197,7 @@
         <xdr:cNvPr id="103" name="CuadroTexto 102">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CC5C0587-38FD-4A42-9022-C28E02FD0EC2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC5C0587-38FD-4A42-9022-C28E02FD0EC2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6255,7 +6252,7 @@
         <xdr:cNvPr id="104" name="CuadroTexto 103">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{22D3ADD5-E733-49BC-80A9-79011235E6C8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22D3ADD5-E733-49BC-80A9-79011235E6C8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6310,7 +6307,7 @@
         <xdr:cNvPr id="105" name="CuadroTexto 104">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0743BF41-9D6C-419D-9B5A-A670921002DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0743BF41-9D6C-419D-9B5A-A670921002DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6365,7 +6362,7 @@
         <xdr:cNvPr id="106" name="CuadroTexto 105">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{54BEB9BE-879C-45B9-B6C2-1666AD7AA7E4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54BEB9BE-879C-45B9-B6C2-1666AD7AA7E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6420,7 +6417,7 @@
         <xdr:cNvPr id="107" name="CuadroTexto 106">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3508F6BA-D87F-42C1-8E17-510E6D967638}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3508F6BA-D87F-42C1-8E17-510E6D967638}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6475,7 +6472,7 @@
         <xdr:cNvPr id="108" name="CuadroTexto 107">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AB12ED58-21EC-4F28-9C83-9CB152B776A8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB12ED58-21EC-4F28-9C83-9CB152B776A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6530,7 +6527,7 @@
         <xdr:cNvPr id="109" name="CuadroTexto 108">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AB2E665D-0E8C-42E9-9C5F-B3EC4E1399B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB2E665D-0E8C-42E9-9C5F-B3EC4E1399B9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6585,7 +6582,7 @@
         <xdr:cNvPr id="110" name="CuadroTexto 109">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D8D26B6E-B843-4475-BAD2-586229D7C909}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8D26B6E-B843-4475-BAD2-586229D7C909}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6640,7 +6637,7 @@
         <xdr:cNvPr id="111" name="CuadroTexto 110">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D3C7B05A-E963-4E59-B4D8-13542D731233}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3C7B05A-E963-4E59-B4D8-13542D731233}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6695,7 +6692,7 @@
         <xdr:cNvPr id="112" name="CuadroTexto 111">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B82C59CB-AC76-4268-992F-5A8BEAF3360A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B82C59CB-AC76-4268-992F-5A8BEAF3360A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6750,7 +6747,7 @@
         <xdr:cNvPr id="113" name="CuadroTexto 112">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AB0756B6-0EB7-412E-B2D0-6AE091F63E2A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB0756B6-0EB7-412E-B2D0-6AE091F63E2A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6805,7 +6802,7 @@
         <xdr:cNvPr id="114" name="CuadroTexto 113">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{308E02E7-4A63-4ADA-B4AB-897979E49E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{308E02E7-4A63-4ADA-B4AB-897979E49E64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6860,7 +6857,7 @@
         <xdr:cNvPr id="115" name="CuadroTexto 114">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6F78AC69-72C0-4EEF-B7E6-CE413BF2E82C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F78AC69-72C0-4EEF-B7E6-CE413BF2E82C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6915,7 +6912,7 @@
         <xdr:cNvPr id="116" name="CuadroTexto 115">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4FE6A5BD-BA16-4A09-B2E9-6464884C57C7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FE6A5BD-BA16-4A09-B2E9-6464884C57C7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6970,7 +6967,7 @@
         <xdr:cNvPr id="117" name="CuadroTexto 116">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2A70B9AA-68A3-4BE6-8F45-C48DF20390EF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A70B9AA-68A3-4BE6-8F45-C48DF20390EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7025,7 +7022,7 @@
         <xdr:cNvPr id="118" name="CuadroTexto 117">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0D07BAF3-8E9D-4B50-9CAD-2435486998E1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D07BAF3-8E9D-4B50-9CAD-2435486998E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7080,7 +7077,7 @@
         <xdr:cNvPr id="119" name="CuadroTexto 118">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0E5AA600-E351-4CED-9F8B-B5778BC2445A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E5AA600-E351-4CED-9F8B-B5778BC2445A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7135,7 +7132,7 @@
         <xdr:cNvPr id="120" name="CuadroTexto 119">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68C57233-AEAF-43D1-80B9-BEB9F5F0CFB4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68C57233-AEAF-43D1-80B9-BEB9F5F0CFB4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7190,7 +7187,7 @@
         <xdr:cNvPr id="121" name="CuadroTexto 120">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C135E95D-9C71-4202-AEC4-1976C797C1DE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C135E95D-9C71-4202-AEC4-1976C797C1DE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7245,7 +7242,7 @@
         <xdr:cNvPr id="122" name="CuadroTexto 121">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BCB0625B-189B-41BA-90AD-33F6677D7662}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCB0625B-189B-41BA-90AD-33F6677D7662}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7300,7 +7297,7 @@
         <xdr:cNvPr id="123" name="CuadroTexto 122">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{88170135-FBC7-4533-9531-C3D0A2688D1A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88170135-FBC7-4533-9531-C3D0A2688D1A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7355,7 +7352,7 @@
         <xdr:cNvPr id="124" name="CuadroTexto 123">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8C6957C5-D7AC-4AF7-9507-4416696E51E4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C6957C5-D7AC-4AF7-9507-4416696E51E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7410,7 +7407,7 @@
         <xdr:cNvPr id="125" name="CuadroTexto 124">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6BA11865-D6FB-4A63-85D0-FE617BC2FAEA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BA11865-D6FB-4A63-85D0-FE617BC2FAEA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7465,7 +7462,7 @@
         <xdr:cNvPr id="126" name="CuadroTexto 125">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CC7A6B31-1EA8-497D-B452-1C251D6846CE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC7A6B31-1EA8-497D-B452-1C251D6846CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7520,7 +7517,7 @@
         <xdr:cNvPr id="127" name="CuadroTexto 126">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6404FFFC-3413-4CB0-BFFC-A209C79574CC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6404FFFC-3413-4CB0-BFFC-A209C79574CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7575,7 +7572,7 @@
         <xdr:cNvPr id="128" name="CuadroTexto 127">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4A490AAD-DD4E-4C0C-BC19-9E3F5E1DAD4C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A490AAD-DD4E-4C0C-BC19-9E3F5E1DAD4C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7630,7 +7627,7 @@
         <xdr:cNvPr id="129" name="CuadroTexto 128">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{84A2E528-10F5-4A54-9A55-D77A5770811D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84A2E528-10F5-4A54-9A55-D77A5770811D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7685,7 +7682,7 @@
         <xdr:cNvPr id="130" name="CuadroTexto 129">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E7D5450C-31F6-44FD-8A65-CB6E4D41DED2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7D5450C-31F6-44FD-8A65-CB6E4D41DED2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7740,7 +7737,7 @@
         <xdr:cNvPr id="131" name="CuadroTexto 130">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{21A1D7EC-4426-4D63-B304-40A97E4DB9DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21A1D7EC-4426-4D63-B304-40A97E4DB9DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7795,7 +7792,7 @@
         <xdr:cNvPr id="132" name="CuadroTexto 131">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{20537B2E-F39B-4B44-A294-286B18CD574A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20537B2E-F39B-4B44-A294-286B18CD574A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7850,7 +7847,7 @@
         <xdr:cNvPr id="133" name="CuadroTexto 132">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7183B09F-BC5E-4DA9-976D-0F9251CF94B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7183B09F-BC5E-4DA9-976D-0F9251CF94B1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7905,7 +7902,7 @@
         <xdr:cNvPr id="134" name="CuadroTexto 133">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A367D10E-0B6B-44F7-A93C-508A61CA8B93}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A367D10E-0B6B-44F7-A93C-508A61CA8B93}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7960,7 +7957,7 @@
         <xdr:cNvPr id="135" name="CuadroTexto 134">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6FDA1DEB-0494-4380-8691-78F570F47FA3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FDA1DEB-0494-4380-8691-78F570F47FA3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8015,7 +8012,7 @@
         <xdr:cNvPr id="136" name="CuadroTexto 135">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FAEE1BCA-13EC-4067-96F1-8B4A68C0C1A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAEE1BCA-13EC-4067-96F1-8B4A68C0C1A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8070,7 +8067,7 @@
         <xdr:cNvPr id="137" name="CuadroTexto 136">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{99743484-9EA9-493D-B39D-6809D113663F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99743484-9EA9-493D-B39D-6809D113663F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8125,7 +8122,7 @@
         <xdr:cNvPr id="138" name="CuadroTexto 137">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E14D6C95-0BAB-44E1-9713-D3D795F211A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E14D6C95-0BAB-44E1-9713-D3D795F211A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8180,7 +8177,7 @@
         <xdr:cNvPr id="139" name="CuadroTexto 138">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BAFD1C8F-17C2-4810-9400-62A6CEF1F566}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAFD1C8F-17C2-4810-9400-62A6CEF1F566}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8235,7 +8232,7 @@
         <xdr:cNvPr id="140" name="CuadroTexto 139">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A121FB1B-2FFB-4A12-8A39-A80BA055C731}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A121FB1B-2FFB-4A12-8A39-A80BA055C731}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8290,7 +8287,7 @@
         <xdr:cNvPr id="141" name="CuadroTexto 140">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6AF7FD40-6F13-4794-9BCB-63128599798F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AF7FD40-6F13-4794-9BCB-63128599798F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8345,7 +8342,7 @@
         <xdr:cNvPr id="142" name="CuadroTexto 141">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5A76CBE2-501B-47CB-B121-943F5AC087AB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A76CBE2-501B-47CB-B121-943F5AC087AB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8400,7 +8397,7 @@
         <xdr:cNvPr id="143" name="CuadroTexto 142">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{85EFD972-4F55-4686-8238-8F8FEFE8895F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85EFD972-4F55-4686-8238-8F8FEFE8895F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8455,7 +8452,7 @@
         <xdr:cNvPr id="144" name="CuadroTexto 143">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{14F2CDA7-A9B6-4885-97F8-2FF5863808EF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14F2CDA7-A9B6-4885-97F8-2FF5863808EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8510,7 +8507,7 @@
         <xdr:cNvPr id="145" name="CuadroTexto 144">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8CA9A2CA-C34D-47D5-9E2B-3627EFF7CE6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CA9A2CA-C34D-47D5-9E2B-3627EFF7CE6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8565,7 +8562,7 @@
         <xdr:cNvPr id="146" name="CuadroTexto 145">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F6FF19F6-F353-4595-9CE6-0BE7119233BE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6FF19F6-F353-4595-9CE6-0BE7119233BE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8620,7 +8617,7 @@
         <xdr:cNvPr id="147" name="CuadroTexto 146">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED59BC88-899B-44B0-BA67-05600F2C854B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED59BC88-899B-44B0-BA67-05600F2C854B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8675,7 +8672,7 @@
         <xdr:cNvPr id="148" name="CuadroTexto 147">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C4C7620F-B3BC-46F8-B4BD-15E7EC7CD830}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4C7620F-B3BC-46F8-B4BD-15E7EC7CD830}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8730,7 +8727,7 @@
         <xdr:cNvPr id="149" name="CuadroTexto 148">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7DABB196-339F-4AEF-AAB0-814C642B0CBE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DABB196-339F-4AEF-AAB0-814C642B0CBE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8785,7 +8782,7 @@
         <xdr:cNvPr id="150" name="CuadroTexto 149">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{91AC526F-4439-4BCC-8868-8C6D78BF23F3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91AC526F-4439-4BCC-8868-8C6D78BF23F3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8840,7 +8837,7 @@
         <xdr:cNvPr id="151" name="CuadroTexto 150">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1D7F2CBA-1971-43AD-8591-CAC7F7EBCB8E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D7F2CBA-1971-43AD-8591-CAC7F7EBCB8E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8895,7 +8892,7 @@
         <xdr:cNvPr id="152" name="CuadroTexto 151">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2512BFAD-125A-46EA-B862-A50A5924902D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2512BFAD-125A-46EA-B862-A50A5924902D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8950,7 +8947,7 @@
         <xdr:cNvPr id="153" name="CuadroTexto 152">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FCE7EEAC-38CB-4F78-8281-D62A4F18CB1E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCE7EEAC-38CB-4F78-8281-D62A4F18CB1E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9005,7 +9002,7 @@
         <xdr:cNvPr id="154" name="CuadroTexto 153">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C5B35305-C9AC-48B3-BEC8-3EEC912B56F4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5B35305-C9AC-48B3-BEC8-3EEC912B56F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9060,7 +9057,7 @@
         <xdr:cNvPr id="155" name="CuadroTexto 154">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AA2568B6-D747-45AF-9F38-5CD2AC57D77C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA2568B6-D747-45AF-9F38-5CD2AC57D77C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9115,7 +9112,7 @@
         <xdr:cNvPr id="156" name="CuadroTexto 155">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3E29D74D-1228-4E70-9A95-8962DA99FCE8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E29D74D-1228-4E70-9A95-8962DA99FCE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9170,7 +9167,7 @@
         <xdr:cNvPr id="157" name="CuadroTexto 156">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6BB05535-6CFF-48F9-8978-73697C5C662F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BB05535-6CFF-48F9-8978-73697C5C662F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9225,7 +9222,7 @@
         <xdr:cNvPr id="158" name="CuadroTexto 157">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CC58FB47-4796-413B-AD2B-37C776C8F113}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC58FB47-4796-413B-AD2B-37C776C8F113}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9280,7 +9277,7 @@
         <xdr:cNvPr id="159" name="CuadroTexto 158">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{862A2DC5-0C0F-413F-ACC2-B58D85501912}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{862A2DC5-0C0F-413F-ACC2-B58D85501912}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9335,7 +9332,7 @@
         <xdr:cNvPr id="160" name="CuadroTexto 159">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E0D0772-AFF5-4A7D-B1CE-F520114957C6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E0D0772-AFF5-4A7D-B1CE-F520114957C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9390,7 +9387,7 @@
         <xdr:cNvPr id="161" name="CuadroTexto 160">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{612CE4B3-B162-48CE-A20D-3D6CC82EE9D5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{612CE4B3-B162-48CE-A20D-3D6CC82EE9D5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9445,7 +9442,7 @@
         <xdr:cNvPr id="162" name="CuadroTexto 161">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EF2E0E86-48C2-4108-861D-FC54C2F1679B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF2E0E86-48C2-4108-861D-FC54C2F1679B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9500,7 +9497,7 @@
         <xdr:cNvPr id="163" name="CuadroTexto 162">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C08F8CBA-306A-4847-88BF-BDB83071A36A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C08F8CBA-306A-4847-88BF-BDB83071A36A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9555,7 +9552,7 @@
         <xdr:cNvPr id="164" name="CuadroTexto 163">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A33BEB48-0D27-4F04-BD09-A5267B336DF8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A33BEB48-0D27-4F04-BD09-A5267B336DF8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9610,7 +9607,7 @@
         <xdr:cNvPr id="165" name="CuadroTexto 164">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3B26315C-8502-4A74-967E-E2FACA247903}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B26315C-8502-4A74-967E-E2FACA247903}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9665,7 +9662,7 @@
         <xdr:cNvPr id="166" name="CuadroTexto 165">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E15570E9-B356-4C6B-AE9D-09F0CC68794D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E15570E9-B356-4C6B-AE9D-09F0CC68794D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9720,7 +9717,7 @@
         <xdr:cNvPr id="167" name="CuadroTexto 166">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BA21E28D-5936-42FC-82DC-109919EB2C45}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA21E28D-5936-42FC-82DC-109919EB2C45}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9775,7 +9772,7 @@
         <xdr:cNvPr id="168" name="CuadroTexto 167">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CB08ACE1-4463-4A85-88A9-6012D232EAF5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB08ACE1-4463-4A85-88A9-6012D232EAF5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9830,7 +9827,7 @@
         <xdr:cNvPr id="169" name="CuadroTexto 168">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{87D4CB74-BC88-45B2-A09B-371DDC74AF8C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87D4CB74-BC88-45B2-A09B-371DDC74AF8C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9885,7 +9882,7 @@
         <xdr:cNvPr id="170" name="CuadroTexto 169">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6767991E-1E1A-4369-8F05-5671EC1CACC3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6767991E-1E1A-4369-8F05-5671EC1CACC3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9940,7 +9937,7 @@
         <xdr:cNvPr id="171" name="CuadroTexto 170">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{73C7F24C-40A4-45CC-9378-39296DD27127}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73C7F24C-40A4-45CC-9378-39296DD27127}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9995,7 +9992,7 @@
         <xdr:cNvPr id="172" name="CuadroTexto 171">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3E270BEC-9F58-4127-8811-F3DE220E4EB3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E270BEC-9F58-4127-8811-F3DE220E4EB3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10050,7 +10047,7 @@
         <xdr:cNvPr id="173" name="CuadroTexto 172">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9DFD8B6D-EEB1-4202-BA19-99BDF4081839}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DFD8B6D-EEB1-4202-BA19-99BDF4081839}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10105,7 +10102,7 @@
         <xdr:cNvPr id="174" name="CuadroTexto 173">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AC65175A-B483-4BF8-A4FB-DEDB8EF0AAB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC65175A-B483-4BF8-A4FB-DEDB8EF0AAB7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10160,7 +10157,7 @@
         <xdr:cNvPr id="175" name="CuadroTexto 174">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F864030E-9D52-4387-B2C3-A5CD88174EEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F864030E-9D52-4387-B2C3-A5CD88174EEF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10215,7 +10212,7 @@
         <xdr:cNvPr id="176" name="CuadroTexto 175">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8EFEDBCE-CED5-4E73-BED9-4995A7A53C9B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EFEDBCE-CED5-4E73-BED9-4995A7A53C9B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10270,7 +10267,7 @@
         <xdr:cNvPr id="177" name="CuadroTexto 176">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4E2C25A5-D1B2-45B2-9E67-2F7C5C4EC9E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E2C25A5-D1B2-45B2-9E67-2F7C5C4EC9E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10325,7 +10322,7 @@
         <xdr:cNvPr id="178" name="CuadroTexto 177">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0C6A0FFF-B04A-46BB-8C6F-16790EE3749F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C6A0FFF-B04A-46BB-8C6F-16790EE3749F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10380,7 +10377,7 @@
         <xdr:cNvPr id="179" name="CuadroTexto 178">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{18AFE296-0690-4A79-AAEC-E7BFBA4DCE33}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18AFE296-0690-4A79-AAEC-E7BFBA4DCE33}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10435,7 +10432,7 @@
         <xdr:cNvPr id="180" name="CuadroTexto 179">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6DC8E58D-588F-4CE1-8D65-1253A8CCE8B7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DC8E58D-588F-4CE1-8D65-1253A8CCE8B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10490,7 +10487,7 @@
         <xdr:cNvPr id="181" name="CuadroTexto 180">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BF5E5ADE-75B8-4A50-AD57-BFE464578644}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF5E5ADE-75B8-4A50-AD57-BFE464578644}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10545,7 +10542,7 @@
         <xdr:cNvPr id="182" name="CuadroTexto 181">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1DB98061-6C8B-4413-BA24-04AD70D2B62C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DB98061-6C8B-4413-BA24-04AD70D2B62C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10600,7 +10597,7 @@
         <xdr:cNvPr id="183" name="CuadroTexto 182">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BDAB3488-11F7-49C4-8D51-93D667E6543A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDAB3488-11F7-49C4-8D51-93D667E6543A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10655,7 +10652,7 @@
         <xdr:cNvPr id="184" name="CuadroTexto 183">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{03DD611F-B61A-43DE-AC83-28C3ECFDDDFE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03DD611F-B61A-43DE-AC83-28C3ECFDDDFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10710,7 +10707,7 @@
         <xdr:cNvPr id="185" name="CuadroTexto 184">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{14021916-7E30-4E9B-8E8D-EDA45B99A857}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14021916-7E30-4E9B-8E8D-EDA45B99A857}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10765,7 +10762,7 @@
         <xdr:cNvPr id="186" name="CuadroTexto 185">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C8DC75A7-756C-401A-B735-99E867F9D210}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8DC75A7-756C-401A-B735-99E867F9D210}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10820,7 +10817,7 @@
         <xdr:cNvPr id="187" name="CuadroTexto 186">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CCCE8DBE-4784-486C-9D2A-5A761292C8CB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCCE8DBE-4784-486C-9D2A-5A761292C8CB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10875,7 +10872,7 @@
         <xdr:cNvPr id="188" name="CuadroTexto 187">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07C5C0D6-38DC-4DF3-BA58-71F1DCB8D3A9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07C5C0D6-38DC-4DF3-BA58-71F1DCB8D3A9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10930,7 +10927,7 @@
         <xdr:cNvPr id="189" name="CuadroTexto 188">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3CAF24D3-9692-4D81-A8F3-0D689F4C98C0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CAF24D3-9692-4D81-A8F3-0D689F4C98C0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10985,7 +10982,7 @@
         <xdr:cNvPr id="190" name="CuadroTexto 189">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{97B155BD-9B5D-44F5-843D-624A8DABEA7E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97B155BD-9B5D-44F5-843D-624A8DABEA7E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11040,7 +11037,7 @@
         <xdr:cNvPr id="191" name="CuadroTexto 190">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A7EE236A-9B11-410A-86A0-D36387CF7DE8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7EE236A-9B11-410A-86A0-D36387CF7DE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11095,7 +11092,7 @@
         <xdr:cNvPr id="192" name="CuadroTexto 191">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{21D700AC-ABA9-4F5B-AB0A-0EE09389930C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21D700AC-ABA9-4F5B-AB0A-0EE09389930C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11150,7 +11147,7 @@
         <xdr:cNvPr id="193" name="CuadroTexto 192">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{92378884-476F-47BC-A7F3-6468ECCD6033}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92378884-476F-47BC-A7F3-6468ECCD6033}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11205,7 +11202,7 @@
         <xdr:cNvPr id="194" name="CuadroTexto 193">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{837F6DA2-D217-4F24-92D1-0C542971E9D6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{837F6DA2-D217-4F24-92D1-0C542971E9D6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11260,7 +11257,7 @@
         <xdr:cNvPr id="195" name="CuadroTexto 194">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{74C8EFBA-DAFF-4F67-99A1-24B35A8FDFFF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74C8EFBA-DAFF-4F67-99A1-24B35A8FDFFF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11315,7 +11312,7 @@
         <xdr:cNvPr id="196" name="CuadroTexto 195">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4045E83E-1D10-4143-BE41-B07B6CF4E164}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4045E83E-1D10-4143-BE41-B07B6CF4E164}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11370,7 +11367,7 @@
         <xdr:cNvPr id="197" name="CuadroTexto 196">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AC9701E5-FCF1-4E95-91A4-A7AAA0F0AD21}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC9701E5-FCF1-4E95-91A4-A7AAA0F0AD21}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11425,7 +11422,7 @@
         <xdr:cNvPr id="198" name="CuadroTexto 197">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{68DB7ABC-3AC6-41E4-B9CC-9D62BD24B254}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68DB7ABC-3AC6-41E4-B9CC-9D62BD24B254}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11480,7 +11477,7 @@
         <xdr:cNvPr id="199" name="CuadroTexto 198">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CC39E17A-0C08-4951-87C1-FE16D56C187D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC39E17A-0C08-4951-87C1-FE16D56C187D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11535,7 +11532,7 @@
         <xdr:cNvPr id="200" name="CuadroTexto 199">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C6A54A92-437A-4D3B-B375-697FC453B641}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6A54A92-437A-4D3B-B375-697FC453B641}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11590,7 +11587,7 @@
         <xdr:cNvPr id="201" name="CuadroTexto 200">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{870633A9-68D5-4677-84D0-7241D4B648F2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{870633A9-68D5-4677-84D0-7241D4B648F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11645,7 +11642,7 @@
         <xdr:cNvPr id="202" name="CuadroTexto 201">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0FAD0D50-ABE7-44C6-ABF9-4FC7B848AC66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FAD0D50-ABE7-44C6-ABF9-4FC7B848AC66}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11700,7 +11697,7 @@
         <xdr:cNvPr id="203" name="CuadroTexto 202">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{03BB8A77-9190-4C5A-AD49-F973DA4766F8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03BB8A77-9190-4C5A-AD49-F973DA4766F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11755,7 +11752,7 @@
         <xdr:cNvPr id="204" name="CuadroTexto 203">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{07DE3498-EE76-4694-BFC6-B2A095EC9FE0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07DE3498-EE76-4694-BFC6-B2A095EC9FE0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11810,7 +11807,7 @@
         <xdr:cNvPr id="205" name="CuadroTexto 204">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BFBA33FB-F378-4CDD-BCCC-A1774355B3B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFBA33FB-F378-4CDD-BCCC-A1774355B3B3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11865,7 +11862,7 @@
         <xdr:cNvPr id="206" name="CuadroTexto 205">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5C739FBE-60E8-49EA-9CD2-33062D0444A7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C739FBE-60E8-49EA-9CD2-33062D0444A7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11920,7 +11917,7 @@
         <xdr:cNvPr id="207" name="CuadroTexto 206">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8EF24E66-1789-45F8-A0B5-A0B93F7E0F75}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EF24E66-1789-45F8-A0B5-A0B93F7E0F75}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11975,7 +11972,7 @@
         <xdr:cNvPr id="208" name="CuadroTexto 207">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3F893CBC-BC82-40AD-976F-4B1644253284}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F893CBC-BC82-40AD-976F-4B1644253284}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12030,7 +12027,7 @@
         <xdr:cNvPr id="209" name="CuadroTexto 208">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B77C5C92-ECF2-421B-84D6-407C8BAE3F0D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77C5C92-ECF2-421B-84D6-407C8BAE3F0D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12085,7 +12082,7 @@
         <xdr:cNvPr id="210" name="CuadroTexto 209">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1F4D6907-D5CF-4AB9-AC81-B2A95FCE7081}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F4D6907-D5CF-4AB9-AC81-B2A95FCE7081}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12140,7 +12137,7 @@
         <xdr:cNvPr id="211" name="CuadroTexto 210">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0969C759-8D46-4B3D-BE37-BD5D5B3395E2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0969C759-8D46-4B3D-BE37-BD5D5B3395E2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12195,7 +12192,7 @@
         <xdr:cNvPr id="212" name="CuadroTexto 211">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6C2FE180-E556-4990-8761-A61CC9F32C45}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C2FE180-E556-4990-8761-A61CC9F32C45}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12250,7 +12247,7 @@
         <xdr:cNvPr id="213" name="CuadroTexto 212">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1038144B-904A-4B95-A704-D841B4AE5543}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1038144B-904A-4B95-A704-D841B4AE5543}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12305,7 +12302,7 @@
         <xdr:cNvPr id="214" name="CuadroTexto 213">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5CEF86F6-B7D8-4779-B57A-CE7BBCF461DE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CEF86F6-B7D8-4779-B57A-CE7BBCF461DE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12360,7 +12357,7 @@
         <xdr:cNvPr id="215" name="CuadroTexto 214">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C4F5FACD-1361-47BB-A23D-453927683172}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4F5FACD-1361-47BB-A23D-453927683172}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12415,7 +12412,7 @@
         <xdr:cNvPr id="216" name="CuadroTexto 215">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{251B65DE-323F-423A-B029-E8B674E22FBE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{251B65DE-323F-423A-B029-E8B674E22FBE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12470,7 +12467,7 @@
         <xdr:cNvPr id="217" name="CuadroTexto 216">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3E5F60EA-AE38-4380-A27D-70B17F8B5722}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E5F60EA-AE38-4380-A27D-70B17F8B5722}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12525,7 +12522,7 @@
         <xdr:cNvPr id="218" name="CuadroTexto 217">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8B516498-FF9C-4BD2-AC8D-17DBA2EF707C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B516498-FF9C-4BD2-AC8D-17DBA2EF707C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12580,7 +12577,7 @@
         <xdr:cNvPr id="219" name="CuadroTexto 218">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E6569119-434A-46FD-BC91-CEFAC52D8A7B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6569119-434A-46FD-BC91-CEFAC52D8A7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12635,7 +12632,7 @@
         <xdr:cNvPr id="220" name="CuadroTexto 219">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9AFA7FC9-59FF-485F-89C5-D8FC33624883}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AFA7FC9-59FF-485F-89C5-D8FC33624883}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12690,7 +12687,7 @@
         <xdr:cNvPr id="221" name="CuadroTexto 220">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{14C560E4-88DC-4190-B868-50996C8B3143}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14C560E4-88DC-4190-B868-50996C8B3143}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12745,7 +12742,7 @@
         <xdr:cNvPr id="222" name="CuadroTexto 221">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0471E6E7-DD7B-44E1-9E92-6C7588E02B86}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0471E6E7-DD7B-44E1-9E92-6C7588E02B86}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12800,7 +12797,7 @@
         <xdr:cNvPr id="223" name="CuadroTexto 222">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0E280398-9F9D-4A3D-ABD7-C785ACFDF609}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E280398-9F9D-4A3D-ABD7-C785ACFDF609}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12855,7 +12852,7 @@
         <xdr:cNvPr id="224" name="CuadroTexto 223">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C18E5973-0160-4A80-A584-FD06D2EC003B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C18E5973-0160-4A80-A584-FD06D2EC003B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12910,7 +12907,7 @@
         <xdr:cNvPr id="225" name="CuadroTexto 224">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5A1D48BB-21B2-4938-ABA8-3A0EC24A8113}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A1D48BB-21B2-4938-ABA8-3A0EC24A8113}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12965,7 +12962,7 @@
         <xdr:cNvPr id="226" name="CuadroTexto 225">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4CAA6878-4C64-4449-BCD9-1BE5BA2ED00D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CAA6878-4C64-4449-BCD9-1BE5BA2ED00D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13020,7 +13017,7 @@
         <xdr:cNvPr id="227" name="CuadroTexto 226">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{12A4789C-F9CD-4F4D-98F8-1E53BCE1903F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12A4789C-F9CD-4F4D-98F8-1E53BCE1903F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13075,7 +13072,7 @@
         <xdr:cNvPr id="228" name="CuadroTexto 227">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D85E5FE1-F58F-43B2-89E1-3D6EE840AF97}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D85E5FE1-F58F-43B2-89E1-3D6EE840AF97}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13130,7 +13127,7 @@
         <xdr:cNvPr id="229" name="CuadroTexto 228">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FB4F1CE0-870E-4B23-A256-9473C2A3C47E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB4F1CE0-870E-4B23-A256-9473C2A3C47E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13185,7 +13182,7 @@
         <xdr:cNvPr id="230" name="CuadroTexto 229">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{76DD241A-77B5-4C88-AF96-2D6D537BB352}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76DD241A-77B5-4C88-AF96-2D6D537BB352}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13240,7 +13237,7 @@
         <xdr:cNvPr id="231" name="CuadroTexto 230">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{914F8C4E-943A-4241-B8CF-4C0F7ABCABC5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{914F8C4E-943A-4241-B8CF-4C0F7ABCABC5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13295,7 +13292,7 @@
         <xdr:cNvPr id="232" name="CuadroTexto 231">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A20E49F3-A28E-4B93-9152-BDB47686E1EF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A20E49F3-A28E-4B93-9152-BDB47686E1EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13350,7 +13347,7 @@
         <xdr:cNvPr id="233" name="CuadroTexto 232">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7364DEA7-88EE-4C21-9540-FB3D0DF0F0E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7364DEA7-88EE-4C21-9540-FB3D0DF0F0E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13405,7 +13402,7 @@
         <xdr:cNvPr id="234" name="CuadroTexto 233">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09CE9795-53F4-4D85-A042-AF87545B0E20}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09CE9795-53F4-4D85-A042-AF87545B0E20}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13460,7 +13457,7 @@
         <xdr:cNvPr id="235" name="CuadroTexto 234">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C7751875-9B6C-43BD-83A0-C320C38567A3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7751875-9B6C-43BD-83A0-C320C38567A3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13515,7 +13512,7 @@
         <xdr:cNvPr id="236" name="CuadroTexto 235">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7E7B170A-D4C6-4205-BAA0-53138B555C5E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E7B170A-D4C6-4205-BAA0-53138B555C5E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13570,7 +13567,7 @@
         <xdr:cNvPr id="237" name="CuadroTexto 236">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{01CB7EE5-81AE-47C3-9C04-1C56C80B728A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01CB7EE5-81AE-47C3-9C04-1C56C80B728A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13625,7 +13622,7 @@
         <xdr:cNvPr id="238" name="CuadroTexto 237">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0D56CE73-7018-4DEA-A03E-24B2172D1594}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D56CE73-7018-4DEA-A03E-24B2172D1594}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13954,24 +13951,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K503"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.109375" customWidth="1"/>
-    <col min="2" max="2" width="40.88671875" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="22.88671875" customWidth="1"/>
+    <col min="1" max="1" width="19.07421875" customWidth="1"/>
+    <col min="2" max="2" width="40.84375" customWidth="1"/>
+    <col min="3" max="3" width="16.3046875" customWidth="1"/>
+    <col min="4" max="4" width="22.84375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="37.88671875" customWidth="1"/>
+    <col min="6" max="6" width="37.84375" customWidth="1"/>
     <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" customWidth="1"/>
-    <col min="9" max="9" width="69.5546875" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" customWidth="1"/>
+    <col min="8" max="8" width="21.3046875" customWidth="1"/>
+    <col min="9" max="9" width="69.53515625" customWidth="1"/>
+    <col min="10" max="10" width="14.07421875" customWidth="1"/>
+    <col min="11" max="11" width="16.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14006,7 +14003,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -14038,7 +14035,7 @@
       <c r="J2" s="15"/>
       <c r="K2" s="28"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>101</v>
       </c>
@@ -14070,7 +14067,7 @@
       <c r="J3" s="15"/>
       <c r="K3" s="28"/>
     </row>
-    <row r="4" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>101</v>
       </c>
@@ -14104,7 +14101,7 @@
       </c>
       <c r="K4" s="28"/>
     </row>
-    <row r="5" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -14138,7 +14135,7 @@
       </c>
       <c r="K5" s="28"/>
     </row>
-    <row r="6" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -14172,7 +14169,7 @@
       </c>
       <c r="K6" s="28"/>
     </row>
-    <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -14201,12 +14198,12 @@
       <c r="I7" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="21">
         <v>86.86</v>
       </c>
       <c r="K7" s="28"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>101</v>
       </c>
@@ -14242,7 +14239,7 @@
         <v>133503</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>101</v>
       </c>
@@ -14271,12 +14268,12 @@
       <c r="I9" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="21">
         <v>167.04</v>
       </c>
       <c r="K9" s="28"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
@@ -14308,7 +14305,7 @@
       <c r="J10" s="15"/>
       <c r="K10" s="28"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
@@ -14340,7 +14337,7 @@
       <c r="J11" s="15"/>
       <c r="K11" s="28"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -14372,7 +14369,7 @@
       <c r="J12" s="15"/>
       <c r="K12" s="28"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -14404,7 +14401,7 @@
       <c r="J13" s="15"/>
       <c r="K13" s="28"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -14436,7 +14433,7 @@
       <c r="J14" s="15"/>
       <c r="K14" s="28"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
@@ -14465,7 +14462,7 @@
       <c r="J15" s="15"/>
       <c r="K15" s="28"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
@@ -14497,7 +14494,7 @@
       <c r="J16" s="15"/>
       <c r="K16" s="28"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>30</v>
       </c>
@@ -14529,7 +14526,7 @@
       <c r="J17" s="15"/>
       <c r="K17" s="28"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
@@ -14561,7 +14558,7 @@
       <c r="J18" s="15"/>
       <c r="K18" s="28"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
@@ -14593,7 +14590,7 @@
       <c r="J19" s="15"/>
       <c r="K19" s="28"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>30</v>
       </c>
@@ -14625,7 +14622,7 @@
       <c r="J20" s="9"/>
       <c r="K20" s="28"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>30</v>
       </c>
@@ -14657,7 +14654,7 @@
       <c r="J21" s="9"/>
       <c r="K21" s="28"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>30</v>
       </c>
@@ -14689,7 +14686,7 @@
       <c r="J22" s="9"/>
       <c r="K22" s="28"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
         <v>30</v>
       </c>
@@ -14721,7 +14718,7 @@
       <c r="J23" s="15"/>
       <c r="K23" s="28"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
         <v>30</v>
       </c>
@@ -14753,7 +14750,7 @@
       <c r="J24" s="15"/>
       <c r="K24" s="28"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
         <v>101</v>
       </c>
@@ -14782,12 +14779,12 @@
       <c r="I25" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="J25" s="33">
+      <c r="J25" s="21">
         <v>1913.1</v>
       </c>
       <c r="K25" s="28"/>
     </row>
-    <row r="26" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
         <v>101</v>
       </c>
@@ -14819,7 +14816,7 @@
       <c r="J26" s="10"/>
       <c r="K26" s="28"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
@@ -14851,7 +14848,7 @@
       <c r="J27" s="15"/>
       <c r="K27" s="28"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
         <v>29</v>
       </c>
@@ -14883,7 +14880,7 @@
       <c r="J28" s="15"/>
       <c r="K28" s="28"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
         <v>29</v>
       </c>
@@ -14915,7 +14912,7 @@
       <c r="J29" s="10"/>
       <c r="K29" s="28"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
@@ -14947,7 +14944,7 @@
       <c r="J30" s="10"/>
       <c r="K30" s="28"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
@@ -14979,7 +14976,7 @@
       <c r="J31" s="10"/>
       <c r="K31" s="28"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
         <v>101</v>
       </c>
@@ -15011,7 +15008,7 @@
       <c r="J32" s="10"/>
       <c r="K32" s="28"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
         <v>30</v>
       </c>
@@ -15043,7 +15040,7 @@
       <c r="J33" s="15"/>
       <c r="K33" s="28"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
         <v>101</v>
       </c>
@@ -15075,7 +15072,7 @@
       <c r="J34" s="15"/>
       <c r="K34" s="28"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
         <v>101</v>
       </c>
@@ -15107,7 +15104,7 @@
       <c r="J35" s="15"/>
       <c r="K35" s="28"/>
     </row>
-    <row r="36" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" s="3" t="s">
         <v>30</v>
       </c>
@@ -15143,7 +15140,7 @@
         <v>91458</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" s="3" t="s">
         <v>29</v>
       </c>
@@ -15179,7 +15176,7 @@
         <v>199055</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
         <v>29</v>
       </c>
@@ -15215,7 +15212,7 @@
         <v>199170</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
         <v>101</v>
       </c>
@@ -15247,7 +15244,7 @@
       <c r="J39" s="15"/>
       <c r="K39" s="28"/>
     </row>
-    <row r="40" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
         <v>101</v>
       </c>
@@ -15283,7 +15280,7 @@
         <v>138956</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
         <v>30</v>
       </c>
@@ -15315,7 +15312,7 @@
       <c r="J41" s="15"/>
       <c r="K41" s="28"/>
     </row>
-    <row r="42" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" s="3" t="s">
         <v>30</v>
       </c>
@@ -15347,7 +15344,7 @@
       <c r="J42" s="28"/>
       <c r="K42" s="28"/>
     </row>
-    <row r="43" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43" s="28" t="s">
         <v>101</v>
       </c>
@@ -15383,7 +15380,7 @@
         <v>252597</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44" s="28" t="s">
         <v>101</v>
       </c>
@@ -15418,7 +15415,7 @@
         <v>63805</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" s="28" t="s">
         <v>30</v>
       </c>
@@ -15450,7 +15447,7 @@
       <c r="J45" s="28"/>
       <c r="K45" s="28"/>
     </row>
-    <row r="46" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A46" s="28" t="s">
         <v>30</v>
       </c>
@@ -15483,7 +15480,7 @@
       </c>
       <c r="K46" s="28"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" s="28" t="s">
         <v>29</v>
       </c>
@@ -15515,7 +15512,7 @@
       <c r="J47" s="28"/>
       <c r="K47" s="28"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" s="28" t="s">
         <v>30</v>
       </c>
@@ -15546,7 +15543,7 @@
       <c r="J48" s="28"/>
       <c r="K48" s="28"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" s="28" t="s">
         <v>29</v>
       </c>
@@ -15578,7 +15575,7 @@
       <c r="J49" s="28"/>
       <c r="K49" s="28"/>
     </row>
-    <row r="50" spans="1:11" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A50" s="28" t="s">
         <v>30</v>
       </c>
@@ -15610,7 +15607,7 @@
       <c r="J50" s="28"/>
       <c r="K50" s="28"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A51" s="28" t="s">
         <v>101</v>
       </c>
@@ -15642,7 +15639,7 @@
       <c r="J51" s="28"/>
       <c r="K51" s="28"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" s="28" t="s">
         <v>30</v>
       </c>
@@ -15674,7 +15671,7 @@
       <c r="J52" s="28"/>
       <c r="K52" s="28"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A53" s="28" t="s">
         <v>29</v>
       </c>
@@ -15706,7 +15703,7 @@
       <c r="J53" s="28"/>
       <c r="K53" s="28"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" s="28" t="s">
         <v>30</v>
       </c>
@@ -15738,7 +15735,7 @@
       <c r="J54" s="28"/>
       <c r="K54" s="28"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A55" s="28" t="s">
         <v>30</v>
       </c>
@@ -15770,7 +15767,7 @@
       <c r="J55" s="28"/>
       <c r="K55" s="28"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A56" s="28" t="s">
         <v>30</v>
       </c>
@@ -15790,7 +15787,7 @@
       <c r="J56" s="28"/>
       <c r="K56" s="28"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A57" s="28"/>
       <c r="B57" s="28"/>
       <c r="C57" s="28"/>
@@ -15806,7 +15803,7 @@
       <c r="J57" s="28"/>
       <c r="K57" s="28"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A58" s="28"/>
       <c r="B58" s="28"/>
       <c r="C58" s="28"/>
@@ -15822,7 +15819,7 @@
       <c r="J58" s="28"/>
       <c r="K58" s="28"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A59" s="28"/>
       <c r="B59" s="28"/>
       <c r="C59" s="28"/>
@@ -15838,7 +15835,7 @@
       <c r="J59" s="28"/>
       <c r="K59" s="28"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A60" s="28"/>
       <c r="B60" s="28"/>
       <c r="C60" s="28"/>
@@ -15854,2659 +15851,2659 @@
       <c r="J60" s="28"/>
       <c r="K60" s="28"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H61" t="str">
         <f>IF(G61="","",VLOOKUP(G61,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H62" t="str">
         <f>IF(G62="","",VLOOKUP(G62,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H63" t="str">
         <f>IF(G63="","",VLOOKUP(G63,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H64" t="str">
         <f>IF(G64="","",VLOOKUP(G64,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H65" t="str">
         <f>IF(G65="","",VLOOKUP(G65,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H66" t="str">
         <f>IF(G66="","",VLOOKUP(G66,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H67" t="str">
         <f>IF(G67="","",VLOOKUP(G67,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H68" t="str">
         <f>IF(G68="","",VLOOKUP(G68,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H69" t="str">
         <f>IF(G69="","",VLOOKUP(G69,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H70" t="str">
         <f>IF(G70="","",VLOOKUP(G70,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H71" t="str">
         <f>IF(G71="","",VLOOKUP(G71,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H72" t="str">
         <f>IF(G72="","",VLOOKUP(G72,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H73" t="str">
         <f>IF(G73="","",VLOOKUP(G73,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H74" t="str">
         <f>IF(G74="","",VLOOKUP(G74,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H75" t="str">
         <f>IF(G75="","",VLOOKUP(G75,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H76" t="str">
         <f>IF(G76="","",VLOOKUP(G76,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H77" t="str">
         <f>IF(G77="","",VLOOKUP(G77,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H78" t="str">
         <f>IF(G78="","",VLOOKUP(G78,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H79" t="str">
         <f>IF(G79="","",VLOOKUP(G79,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H80" t="str">
         <f>IF(G80="","",VLOOKUP(G80,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H81" t="str">
         <f>IF(G81="","",VLOOKUP(G81,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H82" t="str">
         <f>IF(G82="","",VLOOKUP(G82,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H83" t="str">
         <f>IF(G83="","",VLOOKUP(G83,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H84" t="str">
         <f>IF(G84="","",VLOOKUP(G84,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H85" t="str">
         <f>IF(G85="","",VLOOKUP(G85,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H86" t="str">
         <f>IF(G86="","",VLOOKUP(G86,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H87" t="str">
         <f>IF(G87="","",VLOOKUP(G87,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H88" t="str">
         <f>IF(G88="","",VLOOKUP(G88,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H89" t="str">
         <f>IF(G89="","",VLOOKUP(G89,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H90" t="str">
         <f>IF(G90="","",VLOOKUP(G90,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H91" t="str">
         <f>IF(G91="","",VLOOKUP(G91,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H92" t="str">
         <f>IF(G92="","",VLOOKUP(G92,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H93" t="str">
         <f>IF(G93="","",VLOOKUP(G93,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H94" t="str">
         <f>IF(G94="","",VLOOKUP(G94,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H95" t="str">
         <f>IF(G95="","",VLOOKUP(G95,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H96" t="str">
         <f>IF(G96="","",VLOOKUP(G96,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H97" t="str">
         <f>IF(G97="","",VLOOKUP(G97,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H98" t="str">
         <f>IF(G98="","",VLOOKUP(G98,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H99" t="str">
         <f>IF(G99="","",VLOOKUP(G99,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H100" t="str">
         <f>IF(G100="","",VLOOKUP(G100,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H101" t="str">
         <f>IF(G101="","",VLOOKUP(G101,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H102" t="str">
         <f>IF(G102="","",VLOOKUP(G102,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H103" t="str">
         <f>IF(G103="","",VLOOKUP(G103,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H104" t="str">
         <f>IF(G104="","",VLOOKUP(G104,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="105" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H105" t="str">
         <f>IF(G105="","",VLOOKUP(G105,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H106" t="str">
         <f>IF(G106="","",VLOOKUP(G106,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="107" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H107" t="str">
         <f>IF(G107="","",VLOOKUP(G107,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="108" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H108" t="str">
         <f>IF(G108="","",VLOOKUP(G108,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="109" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H109" t="str">
         <f>IF(G109="","",VLOOKUP(G109,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="110" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H110" t="str">
         <f>IF(G110="","",VLOOKUP(G110,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="111" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H111" t="str">
         <f>IF(G111="","",VLOOKUP(G111,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="112" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H112" t="str">
         <f>IF(G112="","",VLOOKUP(G112,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H113" t="str">
         <f>IF(G113="","",VLOOKUP(G113,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H114" t="str">
         <f>IF(G114="","",VLOOKUP(G114,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H115" t="str">
         <f>IF(G115="","",VLOOKUP(G115,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="116" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H116" t="str">
         <f>IF(G116="","",VLOOKUP(G116,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="117" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H117" t="str">
         <f>IF(G117="","",VLOOKUP(G117,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="118" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H118" t="str">
         <f>IF(G118="","",VLOOKUP(G118,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="119" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H119" t="str">
         <f>IF(G119="","",VLOOKUP(G119,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="120" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H120" t="str">
         <f>IF(G120="","",VLOOKUP(G120,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="121" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H121" t="str">
         <f>IF(G121="","",VLOOKUP(G121,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="122" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H122" t="str">
         <f>IF(G122="","",VLOOKUP(G122,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="123" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H123" t="str">
         <f>IF(G123="","",VLOOKUP(G123,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="124" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H124" t="str">
         <f>IF(G124="","",VLOOKUP(G124,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H125" t="str">
         <f>IF(G125="","",VLOOKUP(G125,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H126" t="str">
         <f>IF(G126="","",VLOOKUP(G126,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H127" t="str">
         <f>IF(G127="","",VLOOKUP(G127,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H128" t="str">
         <f>IF(G128="","",VLOOKUP(G128,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H129" t="str">
         <f>IF(G129="","",VLOOKUP(G129,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H130" t="str">
         <f>IF(G130="","",VLOOKUP(G130,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H131" t="str">
         <f>IF(G131="","",VLOOKUP(G131,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="132" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H132" t="str">
         <f>IF(G132="","",VLOOKUP(G132,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="133" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H133" t="str">
         <f>IF(G133="","",VLOOKUP(G133,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="134" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H134" t="str">
         <f>IF(G134="","",VLOOKUP(G134,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="135" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H135" t="str">
         <f>IF(G135="","",VLOOKUP(G135,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H136" t="str">
         <f>IF(G136="","",VLOOKUP(G136,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="137" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H137" t="str">
         <f>IF(G137="","",VLOOKUP(G137,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="138" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H138" t="str">
         <f>IF(G138="","",VLOOKUP(G138,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="139" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H139" t="str">
         <f>IF(G139="","",VLOOKUP(G139,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H140" t="str">
         <f>IF(G140="","",VLOOKUP(G140,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H141" t="str">
         <f>IF(G141="","",VLOOKUP(G141,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="142" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H142" t="str">
         <f>IF(G142="","",VLOOKUP(G142,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="143" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H143" t="str">
         <f>IF(G143="","",VLOOKUP(G143,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="144" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H144" t="str">
         <f>IF(G144="","",VLOOKUP(G144,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H145" t="str">
         <f>IF(G145="","",VLOOKUP(G145,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="146" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H146" t="str">
         <f>IF(G146="","",VLOOKUP(G146,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="147" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H147" t="str">
         <f>IF(G147="","",VLOOKUP(G147,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H148" t="str">
         <f>IF(G148="","",VLOOKUP(G148,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H149" t="str">
         <f>IF(G149="","",VLOOKUP(G149,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="150" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H150" t="str">
         <f>IF(G150="","",VLOOKUP(G150,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="151" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H151" t="str">
         <f>IF(G151="","",VLOOKUP(G151,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="152" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H152" t="str">
         <f>IF(G152="","",VLOOKUP(G152,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H153" t="str">
         <f>IF(G153="","",VLOOKUP(G153,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="154" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H154" t="str">
         <f>IF(G154="","",VLOOKUP(G154,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="155" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H155" t="str">
         <f>IF(G155="","",VLOOKUP(G155,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H156" t="str">
         <f>IF(G156="","",VLOOKUP(G156,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H157" t="str">
         <f>IF(G157="","",VLOOKUP(G157,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="158" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H158" t="str">
         <f>IF(G158="","",VLOOKUP(G158,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="159" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H159" t="str">
         <f>IF(G159="","",VLOOKUP(G159,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="160" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H160" t="str">
         <f>IF(G160="","",VLOOKUP(G160,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H161" t="str">
         <f>IF(G161="","",VLOOKUP(G161,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="162" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H162" t="str">
         <f>IF(G162="","",VLOOKUP(G162,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="163" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H163" t="str">
         <f>IF(G163="","",VLOOKUP(G163,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H164" t="str">
         <f>IF(G164="","",VLOOKUP(G164,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H165" t="str">
         <f>IF(G165="","",VLOOKUP(G165,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="166" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H166" t="str">
         <f>IF(G166="","",VLOOKUP(G166,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="167" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H167" t="str">
         <f>IF(G167="","",VLOOKUP(G167,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="168" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H168" t="str">
         <f>IF(G168="","",VLOOKUP(G168,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H169" t="str">
         <f>IF(G169="","",VLOOKUP(G169,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="170" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H170" t="str">
         <f>IF(G170="","",VLOOKUP(G170,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="171" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H171" t="str">
         <f>IF(G171="","",VLOOKUP(G171,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="172" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H172" t="str">
         <f>IF(G172="","",VLOOKUP(G172,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="173" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H173" t="str">
         <f>IF(G173="","",VLOOKUP(G173,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="174" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H174" t="str">
         <f>IF(G174="","",VLOOKUP(G174,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="175" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H175" t="str">
         <f>IF(G175="","",VLOOKUP(G175,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="176" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H176" t="str">
         <f>IF(G176="","",VLOOKUP(G176,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H177" t="str">
         <f>IF(G177="","",VLOOKUP(G177,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H178" t="str">
         <f>IF(G178="","",VLOOKUP(G178,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H179" t="str">
         <f>IF(G179="","",VLOOKUP(G179,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H180" t="str">
         <f>IF(G180="","",VLOOKUP(G180,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H181" t="str">
         <f>IF(G181="","",VLOOKUP(G181,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H182" t="str">
         <f>IF(G182="","",VLOOKUP(G182,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H183" t="str">
         <f>IF(G183="","",VLOOKUP(G183,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H184" t="str">
         <f>IF(G184="","",VLOOKUP(G184,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H185" t="str">
         <f>IF(G185="","",VLOOKUP(G185,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H186" t="str">
         <f>IF(G186="","",VLOOKUP(G186,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H187" t="str">
         <f>IF(G187="","",VLOOKUP(G187,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H188" t="str">
         <f>IF(G188="","",VLOOKUP(G188,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H189" t="str">
         <f>IF(G189="","",VLOOKUP(G189,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H190" t="str">
         <f>IF(G190="","",VLOOKUP(G190,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H191" t="str">
         <f>IF(G191="","",VLOOKUP(G191,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H192" t="str">
         <f>IF(G192="","",VLOOKUP(G192,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="193" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H193" t="str">
         <f>IF(G193="","",VLOOKUP(G193,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="194" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H194" t="str">
         <f>IF(G194="","",VLOOKUP(G194,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="195" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H195" t="str">
         <f>IF(G195="","",VLOOKUP(G195,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="196" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H196" t="str">
         <f>IF(G196="","",VLOOKUP(G196,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="197" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H197" t="str">
         <f>IF(G197="","",VLOOKUP(G197,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="198" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H198" t="str">
         <f>IF(G198="","",VLOOKUP(G198,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="199" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H199" t="str">
         <f>IF(G199="","",VLOOKUP(G199,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="200" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H200" t="str">
         <f>IF(G200="","",VLOOKUP(G200,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="201" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H201" t="str">
         <f>IF(G201="","",VLOOKUP(G201,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="202" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H202" t="str">
         <f>IF(G202="","",VLOOKUP(G202,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="203" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H203" t="str">
         <f>IF(G203="","",VLOOKUP(G203,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="204" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H204" t="str">
         <f>IF(G204="","",VLOOKUP(G204,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="205" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H205" t="str">
         <f>IF(G205="","",VLOOKUP(G205,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="206" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H206" t="str">
         <f>IF(G206="","",VLOOKUP(G206,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="207" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H207" t="str">
         <f>IF(G207="","",VLOOKUP(G207,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="208" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H208" t="str">
         <f>IF(G208="","",VLOOKUP(G208,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H209" t="str">
         <f>IF(G209="","",VLOOKUP(G209,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H210" t="str">
         <f>IF(G210="","",VLOOKUP(G210,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H211" t="str">
         <f>IF(G211="","",VLOOKUP(G211,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H212" t="str">
         <f>IF(G212="","",VLOOKUP(G212,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H213" t="str">
         <f>IF(G213="","",VLOOKUP(G213,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="214" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H214" t="str">
         <f>IF(G214="","",VLOOKUP(G214,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="215" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H215" t="str">
         <f>IF(G215="","",VLOOKUP(G215,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="216" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H216" t="str">
         <f>IF(G216="","",VLOOKUP(G216,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="217" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H217" t="str">
         <f>IF(G217="","",VLOOKUP(G217,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="218" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H218" t="str">
         <f>IF(G218="","",VLOOKUP(G218,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="219" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H219" t="str">
         <f>IF(G219="","",VLOOKUP(G219,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="220" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H220" t="str">
         <f>IF(G220="","",VLOOKUP(G220,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="221" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H221" t="str">
         <f>IF(G221="","",VLOOKUP(G221,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="222" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H222" t="str">
         <f>IF(G222="","",VLOOKUP(G222,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="223" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H223" t="str">
         <f>IF(G223="","",VLOOKUP(G223,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="224" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H224" t="str">
         <f>IF(G224="","",VLOOKUP(G224,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="225" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H225" t="str">
         <f>IF(G225="","",VLOOKUP(G225,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="226" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H226" t="str">
         <f>IF(G226="","",VLOOKUP(G226,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="227" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H227" t="str">
         <f>IF(G227="","",VLOOKUP(G227,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="228" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H228" t="str">
         <f>IF(G228="","",VLOOKUP(G228,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="229" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H229" t="str">
         <f>IF(G229="","",VLOOKUP(G229,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="230" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H230" t="str">
         <f>IF(G230="","",VLOOKUP(G230,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="231" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H231" t="str">
         <f>IF(G231="","",VLOOKUP(G231,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="232" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H232" t="str">
         <f>IF(G232="","",VLOOKUP(G232,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="233" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H233" t="str">
         <f>IF(G233="","",VLOOKUP(G233,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="234" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H234" t="str">
         <f>IF(G234="","",VLOOKUP(G234,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="235" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H235" t="str">
         <f>IF(G235="","",VLOOKUP(G235,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="236" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H236" t="str">
         <f>IF(G236="","",VLOOKUP(G236,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="237" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H237" t="str">
         <f>IF(G237="","",VLOOKUP(G237,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="238" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H238" t="str">
         <f>IF(G238="","",VLOOKUP(G238,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="239" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H239" t="str">
         <f>IF(G239="","",VLOOKUP(G239,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="240" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H240" t="str">
         <f>IF(G240="","",VLOOKUP(G240,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="241" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H241" t="str">
         <f>IF(G241="","",VLOOKUP(G241,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="242" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H242" t="str">
         <f>IF(G242="","",VLOOKUP(G242,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="243" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H243" t="str">
         <f>IF(G243="","",VLOOKUP(G243,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="244" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H244" t="str">
         <f>IF(G244="","",VLOOKUP(G244,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="245" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H245" t="str">
         <f>IF(G245="","",VLOOKUP(G245,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="246" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H246" t="str">
         <f>IF(G246="","",VLOOKUP(G246,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="247" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H247" t="str">
         <f>IF(G247="","",VLOOKUP(G247,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="248" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H248" t="str">
         <f>IF(G248="","",VLOOKUP(G248,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="249" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H249" t="str">
         <f>IF(G249="","",VLOOKUP(G249,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="250" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H250" t="str">
         <f>IF(G250="","",VLOOKUP(G250,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="251" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H251" t="str">
         <f>IF(G251="","",VLOOKUP(G251,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="252" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H252" t="str">
         <f>IF(G252="","",VLOOKUP(G252,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="253" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H253" t="str">
         <f>IF(G253="","",VLOOKUP(G253,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="254" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H254" t="str">
         <f>IF(G254="","",VLOOKUP(G254,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="255" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H255" t="str">
         <f>IF(G255="","",VLOOKUP(G255,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="256" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H256" t="str">
         <f>IF(G256="","",VLOOKUP(G256,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="257" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H257" t="str">
         <f>IF(G257="","",VLOOKUP(G257,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="258" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H258" t="str">
         <f>IF(G258="","",VLOOKUP(G258,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="259" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H259" t="str">
         <f>IF(G259="","",VLOOKUP(G259,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="260" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H260" t="str">
         <f>IF(G260="","",VLOOKUP(G260,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="261" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H261" t="str">
         <f>IF(G261="","",VLOOKUP(G261,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="262" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H262" t="str">
         <f>IF(G262="","",VLOOKUP(G262,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="263" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H263" t="str">
         <f>IF(G263="","",VLOOKUP(G263,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="264" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H264" t="str">
         <f>IF(G264="","",VLOOKUP(G264,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="265" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H265" t="str">
         <f>IF(G265="","",VLOOKUP(G265,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="266" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H266" t="str">
         <f>IF(G266="","",VLOOKUP(G266,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="267" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H267" t="str">
         <f>IF(G267="","",VLOOKUP(G267,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="268" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H268" t="str">
         <f>IF(G268="","",VLOOKUP(G268,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="269" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H269" t="str">
         <f>IF(G269="","",VLOOKUP(G269,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="270" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H270" t="str">
         <f>IF(G270="","",VLOOKUP(G270,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="271" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H271" t="str">
         <f>IF(G271="","",VLOOKUP(G271,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="272" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H272" t="str">
         <f>IF(G272="","",VLOOKUP(G272,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="273" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H273" t="str">
         <f>IF(G273="","",VLOOKUP(G273,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="274" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H274" t="str">
         <f>IF(G274="","",VLOOKUP(G274,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="275" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H275" t="str">
         <f>IF(G275="","",VLOOKUP(G275,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="276" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H276" t="str">
         <f>IF(G276="","",VLOOKUP(G276,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="277" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H277" t="str">
         <f>IF(G277="","",VLOOKUP(G277,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="278" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H278" t="str">
         <f>IF(G278="","",VLOOKUP(G278,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="279" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H279" t="str">
         <f>IF(G279="","",VLOOKUP(G279,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="280" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H280" t="str">
         <f>IF(G280="","",VLOOKUP(G280,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="281" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H281" t="str">
         <f>IF(G281="","",VLOOKUP(G281,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="282" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H282" t="str">
         <f>IF(G282="","",VLOOKUP(G282,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="283" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H283" t="str">
         <f>IF(G283="","",VLOOKUP(G283,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="284" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H284" t="str">
         <f>IF(G284="","",VLOOKUP(G284,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="285" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H285" t="str">
         <f>IF(G285="","",VLOOKUP(G285,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="286" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H286" t="str">
         <f>IF(G286="","",VLOOKUP(G286,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="287" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H287" t="str">
         <f>IF(G287="","",VLOOKUP(G287,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="288" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H288" t="str">
         <f>IF(G288="","",VLOOKUP(G288,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="289" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H289" t="str">
         <f>IF(G289="","",VLOOKUP(G289,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="290" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H290" t="str">
         <f>IF(G290="","",VLOOKUP(G290,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="291" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H291" t="str">
         <f>IF(G291="","",VLOOKUP(G291,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="292" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H292" t="str">
         <f>IF(G292="","",VLOOKUP(G292,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="293" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H293" t="str">
         <f>IF(G293="","",VLOOKUP(G293,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="294" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H294" t="str">
         <f>IF(G294="","",VLOOKUP(G294,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="295" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H295" t="str">
         <f>IF(G295="","",VLOOKUP(G295,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="296" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H296" t="str">
         <f>IF(G296="","",VLOOKUP(G296,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="297" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H297" t="str">
         <f>IF(G297="","",VLOOKUP(G297,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="298" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H298" t="str">
         <f>IF(G298="","",VLOOKUP(G298,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="299" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H299" t="str">
         <f>IF(G299="","",VLOOKUP(G299,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="300" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H300" t="str">
         <f>IF(G300="","",VLOOKUP(G300,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="301" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H301" t="str">
         <f>IF(G301="","",VLOOKUP(G301,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="302" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H302" t="str">
         <f>IF(G302="","",VLOOKUP(G302,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="303" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H303" t="str">
         <f>IF(G303="","",VLOOKUP(G303,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="304" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H304" t="str">
         <f>IF(G304="","",VLOOKUP(G304,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="305" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H305" t="str">
         <f>IF(G305="","",VLOOKUP(G305,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="306" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H306" t="str">
         <f>IF(G306="","",VLOOKUP(G306,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="307" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H307" t="str">
         <f>IF(G307="","",VLOOKUP(G307,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="308" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H308" t="str">
         <f>IF(G308="","",VLOOKUP(G308,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="309" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H309" t="str">
         <f>IF(G309="","",VLOOKUP(G309,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="310" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H310" t="str">
         <f>IF(G310="","",VLOOKUP(G310,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="311" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H311" t="str">
         <f>IF(G311="","",VLOOKUP(G311,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="312" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H312" t="str">
         <f>IF(G312="","",VLOOKUP(G312,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="313" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H313" t="str">
         <f>IF(G313="","",VLOOKUP(G313,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="314" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H314" t="str">
         <f>IF(G314="","",VLOOKUP(G314,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="315" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H315" t="str">
         <f>IF(G315="","",VLOOKUP(G315,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="316" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H316" t="str">
         <f>IF(G316="","",VLOOKUP(G316,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="317" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H317" t="str">
         <f>IF(G317="","",VLOOKUP(G317,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="318" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H318" t="str">
         <f>IF(G318="","",VLOOKUP(G318,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="319" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H319" t="str">
         <f>IF(G319="","",VLOOKUP(G319,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="320" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H320" t="str">
         <f>IF(G320="","",VLOOKUP(G320,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="321" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H321" t="str">
         <f>IF(G321="","",VLOOKUP(G321,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="322" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H322" t="str">
         <f>IF(G322="","",VLOOKUP(G322,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="323" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H323" t="str">
         <f>IF(G323="","",VLOOKUP(G323,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="324" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H324" t="str">
         <f>IF(G324="","",VLOOKUP(G324,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="325" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H325" t="str">
         <f>IF(G325="","",VLOOKUP(G325,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="326" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H326" t="str">
         <f>IF(G326="","",VLOOKUP(G326,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="327" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H327" t="str">
         <f>IF(G327="","",VLOOKUP(G327,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="328" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H328" t="str">
         <f>IF(G328="","",VLOOKUP(G328,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="329" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H329" t="str">
         <f>IF(G329="","",VLOOKUP(G329,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="330" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H330" t="str">
         <f>IF(G330="","",VLOOKUP(G330,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="331" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H331" t="str">
         <f>IF(G331="","",VLOOKUP(G331,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="332" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H332" t="str">
         <f>IF(G332="","",VLOOKUP(G332,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="333" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H333" t="str">
         <f>IF(G333="","",VLOOKUP(G333,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="334" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H334" t="str">
         <f>IF(G334="","",VLOOKUP(G334,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="335" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H335" t="str">
         <f>IF(G335="","",VLOOKUP(G335,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="336" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H336" t="str">
         <f>IF(G336="","",VLOOKUP(G336,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="337" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H337" t="str">
         <f>IF(G337="","",VLOOKUP(G337,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="338" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H338" t="str">
         <f>IF(G338="","",VLOOKUP(G338,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="339" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H339" t="str">
         <f>IF(G339="","",VLOOKUP(G339,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="340" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H340" t="str">
         <f>IF(G340="","",VLOOKUP(G340,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H341" t="str">
         <f>IF(G341="","",VLOOKUP(G341,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H342" t="str">
         <f>IF(G342="","",VLOOKUP(G342,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="343" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H343" t="str">
         <f>IF(G343="","",VLOOKUP(G343,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="344" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H344" t="str">
         <f>IF(G344="","",VLOOKUP(G344,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="345" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H345" t="str">
         <f>IF(G345="","",VLOOKUP(G345,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="346" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H346" t="str">
         <f>IF(G346="","",VLOOKUP(G346,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="347" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H347" t="str">
         <f>IF(G347="","",VLOOKUP(G347,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="348" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H348" t="str">
         <f>IF(G348="","",VLOOKUP(G348,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="349" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H349" t="str">
         <f>IF(G349="","",VLOOKUP(G349,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="350" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H350" t="str">
         <f>IF(G350="","",VLOOKUP(G350,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="351" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H351" t="str">
         <f>IF(G351="","",VLOOKUP(G351,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="352" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H352" t="str">
         <f>IF(G352="","",VLOOKUP(G352,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="353" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H353" t="str">
         <f>IF(G353="","",VLOOKUP(G353,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="354" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H354" t="str">
         <f>IF(G354="","",VLOOKUP(G354,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="355" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H355" t="str">
         <f>IF(G355="","",VLOOKUP(G355,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="356" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H356" t="str">
         <f>IF(G356="","",VLOOKUP(G356,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="357" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H357" t="str">
         <f>IF(G357="","",VLOOKUP(G357,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="358" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H358" t="str">
         <f>IF(G358="","",VLOOKUP(G358,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="359" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H359" t="str">
         <f>IF(G359="","",VLOOKUP(G359,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="360" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H360" t="str">
         <f>IF(G360="","",VLOOKUP(G360,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="361" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H361" t="str">
         <f>IF(G361="","",VLOOKUP(G361,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="362" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H362" t="str">
         <f>IF(G362="","",VLOOKUP(G362,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="363" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H363" t="str">
         <f>IF(G363="","",VLOOKUP(G363,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="364" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H364" t="str">
         <f>IF(G364="","",VLOOKUP(G364,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="365" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H365" t="str">
         <f>IF(G365="","",VLOOKUP(G365,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="366" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H366" t="str">
         <f>IF(G366="","",VLOOKUP(G366,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="367" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H367" t="str">
         <f>IF(G367="","",VLOOKUP(G367,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="368" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H368" t="str">
         <f>IF(G368="","",VLOOKUP(G368,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="369" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H369" t="str">
         <f>IF(G369="","",VLOOKUP(G369,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="370" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H370" t="str">
         <f>IF(G370="","",VLOOKUP(G370,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="371" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H371" t="str">
         <f>IF(G371="","",VLOOKUP(G371,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="372" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="372" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H372" t="str">
         <f>IF(G372="","",VLOOKUP(G372,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="373" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H373" t="str">
         <f>IF(G373="","",VLOOKUP(G373,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="374" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H374" t="str">
         <f>IF(G374="","",VLOOKUP(G374,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="375" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H375" t="str">
         <f>IF(G375="","",VLOOKUP(G375,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="376" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="376" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H376" t="str">
         <f>IF(G376="","",VLOOKUP(G376,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="377" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="377" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H377" t="str">
         <f>IF(G377="","",VLOOKUP(G377,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="378" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="378" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H378" t="str">
         <f>IF(G378="","",VLOOKUP(G378,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="379" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="379" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H379" t="str">
         <f>IF(G379="","",VLOOKUP(G379,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="380" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="380" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H380" t="str">
         <f>IF(G380="","",VLOOKUP(G380,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="381" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="381" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H381" t="str">
         <f>IF(G381="","",VLOOKUP(G381,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="382" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H382" t="str">
         <f>IF(G382="","",VLOOKUP(G382,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="383" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="383" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H383" t="str">
         <f>IF(G383="","",VLOOKUP(G383,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="384" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="384" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H384" t="str">
         <f>IF(G384="","",VLOOKUP(G384,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="385" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H385" t="str">
         <f>IF(G385="","",VLOOKUP(G385,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="386" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="386" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H386" t="str">
         <f>IF(G386="","",VLOOKUP(G386,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="387" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="387" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H387" t="str">
         <f>IF(G387="","",VLOOKUP(G387,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="388" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="388" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H388" t="str">
         <f>IF(G388="","",VLOOKUP(G388,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="389" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H389" t="str">
         <f>IF(G389="","",VLOOKUP(G389,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="390" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H390" t="str">
         <f>IF(G390="","",VLOOKUP(G390,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="391" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H391" t="str">
         <f>IF(G391="","",VLOOKUP(G391,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="392" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="392" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H392" t="str">
         <f>IF(G392="","",VLOOKUP(G392,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="393" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H393" t="str">
         <f>IF(G393="","",VLOOKUP(G393,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="394" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="394" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H394" t="str">
         <f>IF(G394="","",VLOOKUP(G394,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="395" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H395" t="str">
         <f>IF(G395="","",VLOOKUP(G395,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="396" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H396" t="str">
         <f>IF(G396="","",VLOOKUP(G396,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="397" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H397" t="str">
         <f>IF(G397="","",VLOOKUP(G397,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="398" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H398" t="str">
         <f>IF(G398="","",VLOOKUP(G398,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="399" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H399" t="str">
         <f>IF(G399="","",VLOOKUP(G399,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="400" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="400" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H400" t="str">
         <f>IF(G400="","",VLOOKUP(G400,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="401" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="401" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H401" t="str">
         <f>IF(G401="","",VLOOKUP(G401,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="402" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="402" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H402" t="str">
         <f>IF(G402="","",VLOOKUP(G402,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="403" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="403" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H403" t="str">
         <f>IF(G403="","",VLOOKUP(G403,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="404" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="404" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H404" t="str">
         <f>IF(G404="","",VLOOKUP(G404,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="405" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="405" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H405" t="str">
         <f>IF(G405="","",VLOOKUP(G405,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="406" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="406" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H406" t="str">
         <f>IF(G406="","",VLOOKUP(G406,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="407" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="407" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H407" t="str">
         <f>IF(G407="","",VLOOKUP(G407,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="408" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="408" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H408" t="str">
         <f>IF(G408="","",VLOOKUP(G408,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="409" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="409" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H409" t="str">
         <f>IF(G409="","",VLOOKUP(G409,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="410" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="410" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H410" t="str">
         <f>IF(G410="","",VLOOKUP(G410,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="411" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="411" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H411" t="str">
         <f>IF(G411="","",VLOOKUP(G411,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="412" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="412" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H412" t="str">
         <f>IF(G412="","",VLOOKUP(G412,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="413" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="413" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H413" t="str">
         <f>IF(G413="","",VLOOKUP(G413,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="414" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="414" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H414" t="str">
         <f>IF(G414="","",VLOOKUP(G414,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="415" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="415" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H415" t="str">
         <f>IF(G415="","",VLOOKUP(G415,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="416" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="416" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H416" t="str">
         <f>IF(G416="","",VLOOKUP(G416,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="417" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="417" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H417" t="str">
         <f>IF(G417="","",VLOOKUP(G417,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="418" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="418" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H418" t="str">
         <f>IF(G418="","",VLOOKUP(G418,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="419" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="419" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H419" t="str">
         <f>IF(G419="","",VLOOKUP(G419,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="420" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="420" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H420" t="str">
         <f>IF(G420="","",VLOOKUP(G420,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="421" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="421" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H421" t="str">
         <f>IF(G421="","",VLOOKUP(G421,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="422" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="422" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H422" t="str">
         <f>IF(G422="","",VLOOKUP(G422,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="423" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="423" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H423" t="str">
         <f>IF(G423="","",VLOOKUP(G423,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="424" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="424" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H424" t="str">
         <f>IF(G424="","",VLOOKUP(G424,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="425" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="425" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H425" t="str">
         <f>IF(G425="","",VLOOKUP(G425,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="426" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="426" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H426" t="str">
         <f>IF(G426="","",VLOOKUP(G426,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="427" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="427" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H427" t="str">
         <f>IF(G427="","",VLOOKUP(G427,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="428" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="428" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H428" t="str">
         <f>IF(G428="","",VLOOKUP(G428,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="429" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="429" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H429" t="str">
         <f>IF(G429="","",VLOOKUP(G429,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="430" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="430" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H430" t="str">
         <f>IF(G430="","",VLOOKUP(G430,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="431" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="431" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H431" t="str">
         <f>IF(G431="","",VLOOKUP(G431,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="432" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="432" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H432" t="str">
         <f>IF(G432="","",VLOOKUP(G432,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="433" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="433" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H433" t="str">
         <f>IF(G433="","",VLOOKUP(G433,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="434" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="434" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H434" t="str">
         <f>IF(G434="","",VLOOKUP(G434,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="435" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="435" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H435" t="str">
         <f>IF(G435="","",VLOOKUP(G435,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="436" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="436" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H436" t="str">
         <f>IF(G436="","",VLOOKUP(G436,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="437" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="437" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H437" t="str">
         <f>IF(G437="","",VLOOKUP(G437,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="438" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="438" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H438" t="str">
         <f>IF(G438="","",VLOOKUP(G438,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="439" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="439" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H439" t="str">
         <f>IF(G439="","",VLOOKUP(G439,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="440" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="440" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H440" t="str">
         <f>IF(G440="","",VLOOKUP(G440,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="441" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="441" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H441" t="str">
         <f>IF(G441="","",VLOOKUP(G441,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="442" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="442" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H442" t="str">
         <f>IF(G442="","",VLOOKUP(G442,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="443" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="443" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H443" t="str">
         <f>IF(G443="","",VLOOKUP(G443,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="444" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="444" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H444" t="str">
         <f>IF(G444="","",VLOOKUP(G444,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="445" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="445" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H445" t="str">
         <f>IF(G445="","",VLOOKUP(G445,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="446" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="446" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H446" t="str">
         <f>IF(G446="","",VLOOKUP(G446,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="447" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="447" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H447" t="str">
         <f>IF(G447="","",VLOOKUP(G447,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="448" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="448" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H448" t="str">
         <f>IF(G448="","",VLOOKUP(G448,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="449" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="449" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H449" t="str">
         <f>IF(G449="","",VLOOKUP(G449,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="450" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="450" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H450" t="str">
         <f>IF(G450="","",VLOOKUP(G450,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="451" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="451" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H451" t="str">
         <f>IF(G451="","",VLOOKUP(G451,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="452" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="452" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H452" t="str">
         <f>IF(G452="","",VLOOKUP(G452,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="453" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="453" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H453" t="str">
         <f>IF(G453="","",VLOOKUP(G453,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="454" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="454" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H454" t="str">
         <f>IF(G454="","",VLOOKUP(G454,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="455" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="455" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H455" t="str">
         <f>IF(G455="","",VLOOKUP(G455,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="456" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="456" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H456" t="str">
         <f>IF(G456="","",VLOOKUP(G456,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="457" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="457" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H457" t="str">
         <f>IF(G457="","",VLOOKUP(G457,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="458" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="458" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H458" t="str">
         <f>IF(G458="","",VLOOKUP(G458,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="459" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="459" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H459" t="str">
         <f>IF(G459="","",VLOOKUP(G459,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="460" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="460" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H460" t="str">
         <f>IF(G460="","",VLOOKUP(G460,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="461" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="461" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H461" t="str">
         <f>IF(G461="","",VLOOKUP(G461,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="462" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="462" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H462" t="str">
         <f>IF(G462="","",VLOOKUP(G462,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="463" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="463" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H463" t="str">
         <f>IF(G463="","",VLOOKUP(G463,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="464" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="464" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H464" t="str">
         <f>IF(G464="","",VLOOKUP(G464,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="465" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="465" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H465" t="str">
         <f>IF(G465="","",VLOOKUP(G465,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="466" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="466" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H466" t="str">
         <f>IF(G466="","",VLOOKUP(G466,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="467" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="467" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H467" t="str">
         <f>IF(G467="","",VLOOKUP(G467,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="468" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="468" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H468" t="str">
         <f>IF(G468="","",VLOOKUP(G468,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="469" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="469" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H469" t="str">
         <f>IF(G469="","",VLOOKUP(G469,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="470" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="470" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H470" t="str">
         <f>IF(G470="","",VLOOKUP(G470,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="471" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="471" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H471" t="str">
         <f>IF(G471="","",VLOOKUP(G471,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="472" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="472" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H472" t="str">
         <f>IF(G472="","",VLOOKUP(G472,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="473" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="473" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H473" t="str">
         <f>IF(G473="","",VLOOKUP(G473,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="474" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="474" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H474" t="str">
         <f>IF(G474="","",VLOOKUP(G474,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="475" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="475" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H475" t="str">
         <f>IF(G475="","",VLOOKUP(G475,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="476" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="476" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H476" t="str">
         <f>IF(G476="","",VLOOKUP(G476,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="477" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="477" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H477" t="str">
         <f>IF(G477="","",VLOOKUP(G477,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="478" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="478" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H478" t="str">
         <f>IF(G478="","",VLOOKUP(G478,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="479" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="479" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H479" t="str">
         <f>IF(G479="","",VLOOKUP(G479,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="480" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="480" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H480" t="str">
         <f>IF(G480="","",VLOOKUP(G480,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="481" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="481" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H481" t="str">
         <f>IF(G481="","",VLOOKUP(G481,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="482" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="482" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H482" t="str">
         <f>IF(G482="","",VLOOKUP(G482,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="483" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="483" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H483" t="str">
         <f>IF(G483="","",VLOOKUP(G483,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="484" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="484" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H484" t="str">
         <f>IF(G484="","",VLOOKUP(G484,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="485" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="485" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H485" t="str">
         <f>IF(G485="","",VLOOKUP(G485,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="486" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="486" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H486" t="str">
         <f>IF(G486="","",VLOOKUP(G486,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="487" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="487" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H487" t="str">
         <f>IF(G487="","",VLOOKUP(G487,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="488" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="488" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H488" t="str">
         <f>IF(G488="","",VLOOKUP(G488,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="489" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="489" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H489" t="str">
         <f>IF(G489="","",VLOOKUP(G489,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="490" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="490" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H490" t="str">
         <f>IF(G490="","",VLOOKUP(G490,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="491" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="491" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H491" t="str">
         <f>IF(G491="","",VLOOKUP(G491,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="492" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="492" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H492" t="str">
         <f>IF(G492="","",VLOOKUP(G492,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="493" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="493" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H493" t="str">
         <f>IF(G493="","",VLOOKUP(G493,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="494" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="494" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H494" t="str">
         <f>IF(G494="","",VLOOKUP(G494,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="495" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="495" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H495" t="str">
         <f>IF(G495="","",VLOOKUP(G495,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="496" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="496" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H496" t="str">
         <f>IF(G496="","",VLOOKUP(G496,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="497" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="497" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H497" t="str">
         <f>IF(G497="","",VLOOKUP(G497,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="498" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="498" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H498" t="str">
         <f>IF(G498="","",VLOOKUP(G498,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="499" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="499" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H499" t="str">
         <f>IF(G499="","",VLOOKUP(G499,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="500" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="500" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H500" t="str">
         <f>IF(G500="","",VLOOKUP(G500,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="501" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="501" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H501" t="str">
         <f>IF(G501="","",VLOOKUP(G501,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="502" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="502" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H502" t="str">
         <f>IF(G502="","",VLOOKUP(G502,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="503" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="503" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H503" t="str">
         <f>IF(G503="","",VLOOKUP(G503,REFERENCIA!$A$1:$B$14,2,0))</f>
         <v/>
@@ -18522,7 +18519,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B33:C42 B17:C17 C23 C12">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B33:C42 B17:C17 C23 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>22</formula1>
     </dataValidation>
   </dataValidations>
@@ -18532,7 +18529,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>REFERENCIA!$A$1:$A$14</xm:f>
           </x14:formula1>
@@ -18545,20 +18542,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -18566,7 +18563,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -18574,7 +18571,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -18582,7 +18579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -18590,7 +18587,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -18598,7 +18595,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -18606,7 +18603,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -18614,7 +18611,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -18622,7 +18619,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -18630,7 +18627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -18638,7 +18635,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -18646,7 +18643,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -18654,7 +18651,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.55" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -18662,7 +18659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>27</v>
       </c>
